--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -27,7 +27,7 @@
     <sheet name="Listas" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Atividades!$A$1:$K$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Atividades!$A$1:$L$1</definedName>
     <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">Diario_Mapeamento!$A$1:$L$1</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Documentos!$A$1:$J$1</definedName>
     <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">FAQ!$A$1:$D$1</definedName>
@@ -41,7 +41,7 @@
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">Repositorio!$A$1:$I$1</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Riscos!$A$1:$M$1</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Subprocessos!$A$1:$K$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tarefas!$A$1:$J$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tarefas!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="1427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="1428">
   <si>
     <t xml:space="preserve">Painel de Processos — Base de Dados (DADOS FICTÍCIOS)</t>
   </si>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">3. Vínculos</t>
   </si>
   <si>
-    <t xml:space="preserve">Hierarquia (CBOK 4.0): Macroprocesso → Processo de negócio (aba Processos) → Processo de trabalho (aba Subprocessos) → Atividade → Tarefa. Os relacionamentos usam os CÓDIGOS: Processos→Macroprocesso, Subprocessos→Processo, Atividades→Subprocesso, Tarefas→Atividade; Documentos/Riscos/Indicadores usam Vinculo_Nivel + Vinculo_Codigo; o Diário usa o código do Processo.</t>
+    <t xml:space="preserve">Hierarquia (CBOK 4.0): Macroprocesso → Processo de negócio (aba Processos) → Subprocesso → Atividade → Tarefa. Os relacionamentos usam os CÓDIGOS: Processos→Macroprocesso, Subprocessos→Processo, Atividades→Subprocesso, Tarefas→Atividade; Documentos/Riscos/Indicadores usam Vinculo_Nivel + Vinculo_Codigo; o Diário usa o código do Processo.</t>
   </si>
   <si>
     <t xml:space="preserve">Convenções de preenchimento</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Imagens Bizagi</t>
   </si>
   <si>
-    <t xml:space="preserve">Recomendado: publique a imagem exportada do Bizagi on-line (Drive público, intranet acessível etc.) e cole a URL na coluna Imagem_Bizagi — o painel exibe a imagem e o clique abre o link original. Links de compartilhamento do Google Drive são convertidos automaticamente para exibição. Caminhos relativos (img/diagramas/...) também funcionam.</t>
+    <t xml:space="preserve">O painel NÃO usa pasta local de imagens: publique a imagem exportada do Bizagi on-line (Drive público, intranet acessível etc.) e cole a URL na coluna Imagem_Bizagi de qualquer nível (macroprocesso a tarefa, onde for pertinente). O painel exibe a imagem e o clique abre o link original em nova aba; links de compartilhamento do Google Drive são convertidos automaticamente. As URLs atuais (placehold.co) são exemplos — substitua pelas suas.</t>
   </si>
   <si>
     <t xml:space="preserve">Células de fórmula</t>
@@ -142,13 +142,13 @@
     <t xml:space="preserve">Processos</t>
   </si>
   <si>
-    <t xml:space="preserve">2º nível — processos de negócio, com ficha completa: SIPOC (fornecedores, entradas, saídas, clientes), status e marcos do mapeamento (M1–M9), fase do ciclo BPM e dados do projeto.</t>
+    <t xml:space="preserve">2º nível — processos de negócio, com ficha completa: SIPOC (fornecedores, entradas, saídas, beneficiários), status e marcos do mapeamento (M1–M9), fase do ciclo BPM e dados do projeto.</t>
   </si>
   <si>
     <t xml:space="preserve">Subprocessos</t>
   </si>
   <si>
-    <t xml:space="preserve">3º nível — processos de trabalho, vinculados ao processo de negócio.</t>
+    <t xml:space="preserve">3º nível (CBOK): subprocessos do processo de negócio.</t>
   </si>
   <si>
     <t xml:space="preserve">Atividades</t>
@@ -346,7 +346,7 @@
     <t xml:space="preserve">Estatuto Social; Regimento Interno; Lei nº 13.303/2016</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-01</t>
   </si>
   <si>
     <t xml:space="preserve">MP-02</t>
@@ -382,7 +382,7 @@
     <t xml:space="preserve">Política de Gestão de Riscos (fictícia); IN Conjunta MP/CGU nº 01/2016</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-02.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-02</t>
   </si>
   <si>
     <t xml:space="preserve">MP-03</t>
@@ -421,7 +421,7 @@
     <t xml:space="preserve">Lei nº 14.133/2021; Portarias de transferências voluntárias</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-03.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-03</t>
   </si>
   <si>
     <t xml:space="preserve">MP-04</t>
@@ -457,7 +457,7 @@
     <t xml:space="preserve">Lei nº 12.787/2013 (Política Nacional de Irrigação)</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-04.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-04</t>
   </si>
   <si>
     <t xml:space="preserve">MP-05</t>
@@ -493,7 +493,7 @@
     <t xml:space="preserve">Legislação ambiental aplicável</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-05.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-05</t>
   </si>
   <si>
     <t xml:space="preserve">MP-06</t>
@@ -532,7 +532,7 @@
     <t xml:space="preserve">Lei nº 14.133/2021; Lei nº 13.303/2016; IN SEGES nº 65/2021; NI-027/2024 (fictícia)</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-06.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-06</t>
   </si>
   <si>
     <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
@@ -571,7 +571,7 @@
     <t xml:space="preserve">CLT; Normas internas de pessoal</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-07.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-07</t>
   </si>
   <si>
     <t xml:space="preserve">MP-08</t>
@@ -607,7 +607,7 @@
     <t xml:space="preserve">IN SGD nº 94/2022; Política de Segurança da Informação (fictícia)</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/mp-08.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-08</t>
   </si>
   <si>
     <t xml:space="preserve">Macroprocesso</t>
@@ -649,7 +649,7 @@
     <t xml:space="preserve">Saidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Clientes</t>
+    <t xml:space="preserve">Beneficiarios</t>
   </si>
   <si>
     <t xml:space="preserve">Normativos_Relacionados</t>
@@ -742,7 +742,7 @@
     <t xml:space="preserve">59500.000123/2026-11</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-06-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-01</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -793,7 +793,7 @@
     <t xml:space="preserve">59500.000456/2026-22</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-06-02.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-02</t>
   </si>
   <si>
     <t xml:space="preserve">Não</t>
@@ -838,7 +838,7 @@
     <t xml:space="preserve">59500.000789/2026-33</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-06-03.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-03</t>
   </si>
   <si>
     <t xml:space="preserve">Concluir modelagem AS-IS das medições e pagamentos.</t>
@@ -880,7 +880,7 @@
     <t xml:space="preserve">59500.000901/2026-44</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-04-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-04-01</t>
   </si>
   <si>
     <t xml:space="preserve">Agendar oficina de validação do AS-IS com o distrito.</t>
@@ -919,7 +919,7 @@
     <t xml:space="preserve">Comunidades; Órgãos ambientais</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-05-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-05-01</t>
   </si>
   <si>
     <t xml:space="preserve">Enviar formulário de levantamento à área (previsto ago/2026).</t>
@@ -964,7 +964,7 @@
     <t xml:space="preserve">59500.000015/2025-77</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-01-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-01-01</t>
   </si>
   <si>
     <t xml:space="preserve">Ciclo de monitoramento trimestral (próximo: set/2026).</t>
@@ -1000,7 +1000,7 @@
     <t xml:space="preserve">Novos empregados; Unidades de lotação</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/p-07-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-07-01</t>
   </si>
   <si>
     <t xml:space="preserve">Aguardando priorização no ciclo 2027.</t>
@@ -1027,7 +1027,7 @@
     <t xml:space="preserve">ETP aprovado no SEI</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/sp-06-01-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/007d4e/ffffff?text=Diagrama+BPMN+SP-06-01-01</t>
   </si>
   <si>
     <t xml:space="preserve">SP-06.01.02</t>
@@ -1048,7 +1048,7 @@
     <t xml:space="preserve">SEI</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/sp-06-01-02.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/007d4e/ffffff?text=Diagrama+BPMN+SP-06-01-02</t>
   </si>
   <si>
     <t xml:space="preserve">SP-06.01.03</t>
@@ -1069,7 +1069,7 @@
     <t xml:space="preserve">Painel de Preços; PNCP; SEI</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/sp-06-01-03.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/007d4e/ffffff?text=Diagrama+BPMN+SP-06-01-03</t>
   </si>
   <si>
     <t xml:space="preserve">SP-06.02.01</t>
@@ -1090,7 +1090,7 @@
     <t xml:space="preserve">Compras.gov.br</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/sp-06-02-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/007d4e/ffffff?text=Diagrama+BPMN+SP-06-02-01</t>
   </si>
   <si>
     <t xml:space="preserve">SP-04.01.01</t>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">SIG-Irrigação (fictício)</t>
   </si>
   <si>
-    <t xml:space="preserve">img/diagramas/sp-04-01-01.svg</t>
+    <t xml:space="preserve">https://placehold.co/960x420/007d4e/ffffff?text=Diagrama+BPMN+SP-04-01-01</t>
   </si>
   <si>
     <t xml:space="preserve">Subprocesso</t>
@@ -1150,6 +1150,9 @@
     <t xml:space="preserve">NI-027/2024 (fictícia)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://placehold.co/960x420/155bcb/ffffff?text=Diagrama+BPMN+A-06.01.01.01</t>
+  </si>
+  <si>
     <t xml:space="preserve">A-06.01.01.02</t>
   </si>
   <si>
@@ -2134,7 +2137,7 @@
     <t xml:space="preserve">Diagrama BPMN AS-IS v0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagrama AS-IS v0.1|img/diagramas/p-06-01.svg</t>
+    <t xml:space="preserve">Diagrama AS-IS v0.1|https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-01</t>
   </si>
   <si>
     <t xml:space="preserve">Identificados 3 retrabalhos e 2 handoffs desnecessários (princípios de desenho do CBOK).</t>
@@ -2161,7 +2164,7 @@
     <t xml:space="preserve">Diagrama AS-IS v1.0 validado</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagrama AS-IS v1.0|img/diagramas/p-06-01.svg;Ata de validação|https://exemplo.codevasf.gov.br/sei/ata-validacao-asis</t>
+    <t xml:space="preserve">Diagrama AS-IS v1.0|https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-01;Ata de validação|https://exemplo.codevasf.gov.br/sei/ata-validacao-asis</t>
   </si>
   <si>
     <t xml:space="preserve">REG-006</t>
@@ -2317,7 +2320,7 @@
     <t xml:space="preserve">Diagrama AS-IS parcial v0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagrama parcial|img/diagramas/p-06-02.svg</t>
+    <t xml:space="preserve">Diagrama parcial|https://placehold.co/960x420/005ca8/ffffff?text=Diagrama+BPMN+P-06-02</t>
   </si>
   <si>
     <t xml:space="preserve">Fluxo de recursos administrativos ainda pendente de detalhamento com a área.</t>
@@ -3823,13 +3826,13 @@
     <t xml:space="preserve">Processo de Trabalho</t>
   </si>
   <si>
-    <t xml:space="preserve">Nível da hierarquia entre o processo de negócio e as atividades: recorte executável do processo, sob responsabilidade de uma unidade — também tratado como subprocesso. Na planilha deste painel, corresponde à aba Subprocessos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metodologia Codevasf / CBOK 4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processo de Negócio; Subprocesso; Atividade</t>
+    <t xml:space="preserve">Expressão usual na administração pública brasileira para o conjunto de atividades executadas por uma unidade. Não é um nível da hierarquia do CBOK 4.0, que adota processo de negócio → subprocesso → atividade → tarefa — nomenclatura seguida por este painel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adm. Pública / CBOK 4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processo de Negócio; Subprocesso; Atividade; Tarefa</t>
   </si>
   <si>
     <t xml:space="preserve">Visão completa do processo, do primeiro evento desencadeador até a entrega final ao cliente, atravessando todas as áreas envolvidas.</t>
@@ -3952,7 +3955,7 @@
     <t xml:space="preserve">Processo de Negócio; Atividade</t>
   </si>
   <si>
-    <t xml:space="preserve">Ferramenta visual que descreve um processo em alto nível por meio de cinco elementos: Suppliers (Fornecedores), Inputs (Entradas), Process (Processo), Outputs (Saídas) e Customers (Clientes).</t>
+    <t xml:space="preserve">Ferramenta visual que descreve um processo em alto nível por meio de cinco elementos: Fornecedores (Suppliers), Entradas (Inputs), Processo, Saídas (Outputs) e Beneficiários (Customers).</t>
   </si>
   <si>
     <t xml:space="preserve">Six Sigma / CBOK</t>
@@ -4105,7 +4108,7 @@
     <t xml:space="preserve">O que é SIPOC e como ler a ficha de um processo?</t>
   </si>
   <si>
-    <t xml:space="preserve">SIPOC é a visão de alto nível do processo em cinco colunas: Fornecedores, Entradas, Processo, Saídas e Clientes. Na ficha de cada processo deste painel, o SIPOC aparece logo após os dados gerais, seguido dos marcos M1–M9, indicadores, riscos, documentos e do diário de mapeamento.</t>
+    <t xml:space="preserve">SIPOC é a visão de alto nível do processo em cinco colunas: Fornecedores, Entradas, Processo, Saídas e Beneficiários. Na ficha de cada processo deste painel, o SIPOC aparece logo após os dados gerais, seguido dos marcos M1–M9, indicadores, riscos, documentos e do diário de mapeamento.</t>
   </si>
   <si>
     <t xml:space="preserve">O que é AS-IS e TO-BE?</t>
@@ -4980,7 +4983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
         <v>19</v>
       </c>
@@ -5322,45 +5325,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>317</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>213</v>
@@ -5369,36 +5372,36 @@
         <v>46027</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>213</v>
@@ -5407,36 +5410,36 @@
         <v>46034</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>213</v>
@@ -5445,34 +5448,34 @@
         <v>46048</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>213</v>
@@ -5481,36 +5484,36 @@
         <v>46062</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>213</v>
@@ -5519,34 +5522,34 @@
         <v>46083</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>213</v>
@@ -5555,36 +5558,36 @@
         <v>46097</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>213</v>
@@ -5593,34 +5596,34 @@
         <v>46125</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>213</v>
@@ -5629,34 +5632,34 @@
         <v>46146</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>213</v>
@@ -5665,36 +5668,36 @@
         <v>46160</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>213</v>
@@ -5703,34 +5706,34 @@
         <v>46188</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="L11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>232</v>
@@ -5739,34 +5742,34 @@
         <v>46175</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>232</v>
@@ -5775,36 +5778,36 @@
         <v>46203</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>263</v>
@@ -5813,28 +5816,28 @@
         <v>46213</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L14" s="12"/>
     </row>
@@ -5880,28 +5883,28 @@
         <v>73</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5909,28 +5912,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5938,28 +5941,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5967,28 +5970,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5996,28 +5999,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6025,28 +6028,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6054,28 +6057,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6083,28 +6086,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6112,28 +6115,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -6176,28 +6179,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>73</v>
@@ -6205,26 +6208,26 @@
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I2" s="11" t="n">
         <v>1</v>
@@ -6232,26 +6235,26 @@
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I3" s="11" t="n">
         <v>2</v>
@@ -6259,26 +6262,26 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="12" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I4" s="11" t="n">
         <v>3</v>
@@ -6286,26 +6289,26 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="12" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I5" s="11" t="n">
         <v>4</v>
@@ -6313,26 +6316,26 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I6" s="11" t="n">
         <v>5</v>
@@ -6340,26 +6343,26 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="12" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>6</v>
@@ -6367,26 +6370,26 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="12" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="I8" s="11" t="n">
         <v>7</v>
@@ -6394,26 +6397,26 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="12" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>8</v>
@@ -6421,28 +6424,28 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>9</v>
@@ -6450,28 +6453,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>10</v>
@@ -6479,28 +6482,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I12" s="11" t="n">
         <v>11</v>
@@ -6508,28 +6511,28 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>12</v>
@@ -6537,28 +6540,28 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>13</v>
@@ -6566,28 +6569,28 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>14</v>
@@ -6595,28 +6598,28 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I16" s="11" t="n">
         <v>15</v>
@@ -6624,28 +6627,28 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>16</v>
@@ -6653,28 +6656,28 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>17</v>
@@ -6682,26 +6685,26 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="12" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I19" s="11" t="n">
         <v>18</v>
@@ -6709,26 +6712,26 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="12" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I20" s="11" t="n">
         <v>19</v>
@@ -6736,26 +6739,26 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="12" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I21" s="11" t="n">
         <v>20</v>
@@ -6763,26 +6766,26 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="12" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="I22" s="11" t="n">
         <v>21</v>
@@ -6790,24 +6793,24 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="12" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="I23" s="11" t="n">
         <v>22</v>
@@ -6815,24 +6818,24 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="12" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I24" s="11" t="n">
         <v>23</v>
@@ -6840,24 +6843,24 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="12" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="I25" s="11" t="n">
         <v>24</v>
@@ -6865,26 +6868,26 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="12" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="I26" s="11" t="n">
         <v>25</v>
@@ -6892,26 +6895,26 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="12" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="I27" s="11" t="n">
         <v>26</v>
@@ -6919,28 +6922,28 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="I28" s="11" t="n">
         <v>27</v>
@@ -6948,28 +6951,28 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="I29" s="11" t="n">
         <v>28</v>
@@ -6977,26 +6980,26 @@
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I30" s="11" t="n">
         <v>29</v>
@@ -7004,26 +7007,26 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="I31" s="11" t="n">
         <v>30</v>
@@ -7031,26 +7034,26 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="I32" s="11" t="n">
         <v>31</v>
@@ -7058,26 +7061,26 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="12" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="I33" s="11" t="n">
         <v>32</v>
@@ -7131,19 +7134,19 @@
         <v>71</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7151,22 +7154,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7174,22 +7177,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,22 +7200,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>177</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,22 +7223,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7243,22 +7246,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7266,22 +7269,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7289,22 +7292,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7312,22 +7315,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>90</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7335,22 +7338,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>152</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7358,22 +7361,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
@@ -7406,914 +7409,914 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>1057</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>1056</v>
-      </c>
       <c r="E15" s="12" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>68</v>
@@ -8322,19 +8325,19 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8342,322 +8345,322 @@
         <v>185</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8665,30 +8668,30 @@
         <v>68</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>68</v>
@@ -8696,138 +8699,138 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8835,271 +8838,271 @@
         <v>353</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>68</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
   </sheetData>
@@ -9143,10 +9146,10 @@
         <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9154,13 +9157,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9168,13 +9171,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9182,13 +9185,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9196,13 +9199,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9210,13 +9213,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9224,13 +9227,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9238,13 +9241,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9252,13 +9255,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9266,13 +9269,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9280,13 +9283,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9294,13 +9297,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9308,13 +9311,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9322,13 +9325,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,13 +9339,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9350,13 +9353,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9364,13 +9367,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9378,13 +9381,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9392,13 +9395,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9406,13 +9409,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9420,13 +9423,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9434,13 +9437,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9448,13 +9451,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9462,13 +9465,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9476,13 +9479,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
@@ -9518,50 +9521,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>
@@ -9609,7 +9612,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>190</v>
@@ -9624,52 +9627,52 @@
         <v>189</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9695,46 +9698,46 @@
         <v>185</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="U2" s="16" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9760,46 +9763,46 @@
         <v>317</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9810,7 +9813,7 @@
         <v>220</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>310</v>
@@ -9822,87 +9825,87 @@
         <v>353</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Q4" s="16" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="S5" s="16" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9910,75 +9913,75 @@
         <v>221</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="U6" s="16" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="16" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="16" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="16" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="16" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -11642,7 +11645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -11655,6 +11658,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11691,6 +11695,9 @@
       <c r="K1" s="9" t="s">
         <v>356</v>
       </c>
+      <c r="L1" s="9" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
@@ -11726,10 +11733,13 @@
       <c r="K2" s="12" t="s">
         <v>364</v>
       </c>
+      <c r="L2" s="10" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>319</v>
@@ -11738,33 +11748,33 @@
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>319</v>
@@ -11773,19 +11783,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>330</v>
@@ -11797,7 +11807,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>319</v>
@@ -11806,33 +11816,33 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>258</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>325</v>
@@ -11841,33 +11851,33 @@
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>330</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>325</v>
@@ -11876,33 +11886,33 @@
         <v>2</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>330</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>332</v>
@@ -11911,33 +11921,33 @@
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>332</v>
@@ -11946,33 +11956,33 @@
         <v>2</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>330</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>339</v>
@@ -11981,33 +11991,33 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>339</v>
@@ -12016,33 +12026,33 @@
         <v>2</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>344</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>346</v>
@@ -12051,31 +12061,31 @@
         <v>1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>351</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>346</v>
@@ -12084,30 +12094,30 @@
         <v>2</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>351</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K13" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:L1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12124,7 +12134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -12137,6 +12147,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12144,7 +12155,7 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>73</v>
@@ -12156,24 +12167,27 @@
         <v>74</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="K1" s="9" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>357</v>
@@ -12182,13 +12196,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>360</v>
@@ -12197,13 +12211,13 @@
         <v>330</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>357</v>
@@ -12212,13 +12226,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>360</v>
@@ -12227,15 +12241,15 @@
         <v>330</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>357</v>
@@ -12244,13 +12258,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>360</v>
@@ -12259,224 +12273,224 @@
         <v>330</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>330</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>344</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>344</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>351</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J11" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F300" type="list">
       <formula1>Listas!$H$2:$H$4</formula1>
@@ -12516,31 +12530,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>84</v>
@@ -12548,7 +12562,7 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>317</v>
@@ -12557,30 +12571,30 @@
         <v>213</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>46160</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>317</v>
@@ -12589,30 +12603,30 @@
         <v>213</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>46083</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>229</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>317</v>
@@ -12621,28 +12635,28 @@
         <v>213</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>46146</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>317</v>
@@ -12651,30 +12665,30 @@
         <v>213</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>46034</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>317</v>
@@ -12683,28 +12697,28 @@
         <v>213</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>46125</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>353</v>
@@ -12713,28 +12727,28 @@
         <v>319</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>46063</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>353</v>
@@ -12743,28 +12757,28 @@
         <v>332</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>46139</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>185</v>
@@ -12773,28 +12787,28 @@
         <v>147</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>45616</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>185</v>
@@ -12803,28 +12817,28 @@
         <v>147</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>45883</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>317</v>
@@ -12833,28 +12847,28 @@
         <v>232</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>46175</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>317</v>
@@ -12863,60 +12877,60 @@
         <v>263</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>46211</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>275</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>357</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>46065</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>317</v>
@@ -12925,28 +12939,28 @@
         <v>290</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>46112</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>317</v>
@@ -12955,22 +12969,22 @@
         <v>213</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>46148</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -13026,48 +13040,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>72</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>317</v>
@@ -13076,10 +13090,10 @@
         <v>213</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>4</v>
@@ -13096,21 +13110,21 @@
         <v>Alto</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>217</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>317</v>
@@ -13119,10 +13133,10 @@
         <v>213</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>3</v>
@@ -13139,21 +13153,21 @@
         <v>Alto</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>217</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>317</v>
@@ -13162,10 +13176,10 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>3</v>
@@ -13182,21 +13196,21 @@
         <v>Alto</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>217</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>353</v>
@@ -13205,10 +13219,10 @@
         <v>319</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>4</v>
@@ -13225,21 +13239,21 @@
         <v>Alto</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>309</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>317</v>
@@ -13248,10 +13262,10 @@
         <v>263</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2</v>
@@ -13268,21 +13282,21 @@
         <v>Moderado</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>267</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>317</v>
@@ -13291,10 +13305,10 @@
         <v>232</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>2</v>
@@ -13311,21 +13325,21 @@
         <v>Moderado</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>185</v>
@@ -13334,10 +13348,10 @@
         <v>147</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>4</v>
@@ -13354,33 +13368,33 @@
         <v>Moderado</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>2</v>
@@ -13397,21 +13411,21 @@
         <v>Moderado</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>317</v>
@@ -13420,10 +13434,10 @@
         <v>213</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>3</v>
@@ -13440,16 +13454,16 @@
         <v>Moderado</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -13508,48 +13522,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>185</v>
@@ -13558,16 +13572,16 @@
         <v>147</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H2" s="11" t="n">
         <v>120</v>
@@ -13580,7 +13594,7 @@
         <v>Acima da meta</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L2" s="12" t="s">
         <v>344</v>
@@ -13591,7 +13605,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>317</v>
@@ -13600,16 +13614,16 @@
         <v>213</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H3" s="11" t="n">
         <v>30</v>
@@ -13622,7 +13636,7 @@
         <v>Meta atingida</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>330</v>
@@ -13633,7 +13647,7 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>317</v>
@@ -13642,16 +13656,16 @@
         <v>232</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>1</v>
@@ -13664,7 +13678,7 @@
         <v>Meta atingida</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L4" s="12" t="s">
         <v>344</v>
@@ -13675,7 +13689,7 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>317</v>
@@ -13684,16 +13698,16 @@
         <v>250</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>100</v>
@@ -13706,7 +13720,7 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L5" s="12" t="s">
         <v>330</v>
@@ -13717,7 +13731,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>317</v>
@@ -13726,16 +13740,16 @@
         <v>263</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>75</v>
@@ -13748,7 +13762,7 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L6" s="12" t="s">
         <v>351</v>
@@ -13759,7 +13773,7 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>185</v>
@@ -13768,16 +13782,16 @@
         <v>147</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H7" s="11" t="n">
         <v>100</v>
@@ -13790,10 +13804,10 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M7" s="14" t="n">
         <v>46203</v>
@@ -13801,7 +13815,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>317</v>
@@ -13810,16 +13824,16 @@
         <v>290</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>95</v>
@@ -13832,10 +13846,10 @@
         <v>Meta atingida</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>46203</v>
@@ -13843,7 +13857,7 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>353</v>
@@ -13852,16 +13866,16 @@
         <v>332</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>100</v>
@@ -13874,7 +13888,7 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>330</v>
@@ -13885,7 +13899,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>185</v>
@@ -13894,16 +13908,16 @@
         <v>135</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>120</v>
@@ -13914,10 +13928,10 @@
         <v>Sem medição</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M10" s="14"/>
     </row>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -32,13 +32,13 @@
     <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">Glossario!$A$1:$E$1</definedName>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Indicadores!$A$1:$M$1</definedName>
     <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">Jornada!$A$1:$I$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Macroprocessos!$A$1:$O$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Macroprocessos!$A$1:$P$1</definedName>
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">NUGEP!$A$1:$G$1</definedName>
     <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">Parametros!$A$1:$B$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Processos!$A$1:$AK$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Processos!$A$1:$AL$1</definedName>
     <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">Repositorio!$A$1:$I$1</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Riscos!$A$1:$M$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Subprocessos!$A$1:$K$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Subprocessos!$A$1:$L$1</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Tarefas!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1262">
   <si>
     <t xml:space="preserve">Painel de Processos — Base de Dados (DADOS FICTÍCIOS)</t>
   </si>
@@ -107,7 +107,13 @@
     <t xml:space="preserve">Imagens Bizagi</t>
   </si>
   <si>
-    <t xml:space="preserve">O painel NÃO usa pasta local de imagens: publique a imagem exportada do Bizagi on-line (Drive público, intranet acessível etc.) e cole a URL na coluna Imagem_Bizagi de qualquer nível (macroprocesso a tarefa, onde for pertinente). O painel exibe a imagem e o clique abre o link original em nova aba; links de compartilhamento do Google Drive são convertidos automaticamente. As URLs atuais (placehold.co) são exemplos — substitua pelas suas.</t>
+    <t xml:space="preserve">O painel NÃO usa pasta local de imagens: publique a imagem exportada do Bizagi on-line (Drive público, intranet acessível etc.) e cole a URL na coluna Imagem_Bizagi de Macroprocessos, Processos ou Subprocessos (única forma disponível para Atividades e Tarefas, que não têm diagrama). O painel exibe a imagem e o clique abre o link original em nova aba; links de compartilhamento do Google Drive são convertidos automaticamente. As URLs atuais (placehold.co) são exemplos — substitua pelas suas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagrama interativo (Bizagi Web)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se o processo tiver uma publicação web do Bizagi (Bizagi Modeler → Publish → Web), cole a URL da publicação em Imagem_Bizagi e marque Diagrama_Interativo = Sim: o painel passa a incorporar o diagrama por iframe (com pan/zoom e clique nos subprocessos), em vez de mostrar uma imagem estática — o mesmo padrão já usado na Base de Conhecimento da Codevasf (AA/GTI) para o Gerenciamento de Incidentes de TI. Exige que o servidor que hospeda a publicação permita ser incorporado por outra origem (o painel roda no GitHub Pages).</t>
   </si>
   <si>
     <t xml:space="preserve">Células de fórmula</t>
@@ -290,6 +296,9 @@
     <t xml:space="preserve">Imagem_Bizagi</t>
   </si>
   <si>
+    <t xml:space="preserve">Diagrama_Interativo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observacoes</t>
   </si>
   <si>
@@ -330,6 +339,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://placehold.co/960x420/222b54/ffffff?text=Diagrama+BPMN+MP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">MP-02</t>
@@ -4377,7 +4389,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C54"/>
+  <dimension ref="B2:C55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4459,7 +4471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
@@ -4467,7 +4479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
@@ -4475,7 +4487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
         <v>21</v>
       </c>
@@ -4483,20 +4495,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="6" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
         <v>26</v>
       </c>
@@ -4504,7 +4516,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
         <v>28</v>
       </c>
@@ -4512,7 +4524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
         <v>30</v>
       </c>
@@ -4560,7 +4572,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
@@ -4568,7 +4580,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
         <v>44</v>
       </c>
@@ -4608,18 +4620,17 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="4" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <f aca="false">COUNTA(Macroprocessos!$A$2:$A$500)</f>
-        <v>8</v>
+      <c r="C36" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4627,8 +4638,8 @@
         <v>26</v>
       </c>
       <c r="C39" s="8" t="n">
-        <f aca="false">COUNTA(Processos!$A$2:$A$500)</f>
-        <v>7</v>
+        <f aca="false">COUNTA(Macroprocessos!$A$2:$A$500)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4636,8 +4647,8 @@
         <v>28</v>
       </c>
       <c r="C40" s="8" t="n">
-        <f aca="false">COUNTA(Subprocessos!$A$2:$A$500)</f>
-        <v>6</v>
+        <f aca="false">COUNTA(Processos!$A$2:$A$500)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4645,8 +4656,8 @@
         <v>30</v>
       </c>
       <c r="C41" s="8" t="n">
-        <f aca="false">COUNTA(Atividades!$A$2:$A$500)</f>
-        <v>13</v>
+        <f aca="false">COUNTA(Subprocessos!$A$2:$A$500)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4654,8 +4665,8 @@
         <v>32</v>
       </c>
       <c r="C42" s="8" t="n">
-        <f aca="false">COUNTA(Tarefas!$A$2:$A$500)</f>
-        <v>10</v>
+        <f aca="false">COUNTA(Atividades!$A$2:$A$500)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4663,8 +4674,8 @@
         <v>34</v>
       </c>
       <c r="C43" s="8" t="n">
-        <f aca="false">COUNTA(Documentos!$A$2:$A$500)</f>
-        <v>14</v>
+        <f aca="false">COUNTA(Tarefas!$A$2:$A$500)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4672,8 +4683,8 @@
         <v>36</v>
       </c>
       <c r="C44" s="8" t="n">
-        <f aca="false">COUNTA(Riscos!$A$2:$A$500)</f>
-        <v>9</v>
+        <f aca="false">COUNTA(Documentos!$A$2:$A$500)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4681,65 +4692,66 @@
         <v>38</v>
       </c>
       <c r="C45" s="8" t="n">
+        <f aca="false">COUNTA(Riscos!$A$2:$A$500)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="8" t="n">
         <f aca="false">COUNTA(Indicadores!$A$2:$A$500)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="8" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="8" t="n">
         <f aca="false">COUNTA(Jornada!$A$2:$A$500)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="8" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="8" t="n">
         <f aca="false">COUNTA(Repositorio!$A$2:$A$500)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="8" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="8" t="n">
         <f aca="false">COUNTA(NUGEP!$A$2:$A$500)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="8" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="8" t="n">
         <f aca="false">COUNTA(Glossario!$A$2:$A$500)</f>
         <v>99</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="8" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="8" t="n">
         <f aca="false">COUNTA(FAQ!$A$2:$A$500)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="6" t="s">
+    <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="4" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4749,6 +4761,14 @@
       </c>
       <c r="C54" s="6" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4782,31 +4802,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="D1" s="9" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4814,28 +4834,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4843,28 +4863,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4872,28 +4892,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4901,28 +4921,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4930,28 +4950,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4959,28 +4979,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4988,28 +5008,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5017,28 +5037,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -5081,55 +5101,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="I2" s="11" t="n">
         <v>1</v>
@@ -5137,26 +5157,26 @@
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>736</v>
-      </c>
       <c r="H3" s="12" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="I3" s="11" t="n">
         <v>2</v>
@@ -5164,26 +5184,26 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="12" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="I4" s="11" t="n">
         <v>5</v>
@@ -5191,26 +5211,26 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="12" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="I5" s="11" t="n">
         <v>6</v>
@@ -5218,28 +5238,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="I6" s="11" t="n">
         <v>11</v>
@@ -5247,28 +5267,28 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>12</v>
@@ -5276,28 +5296,28 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="I8" s="11" t="n">
         <v>13</v>
@@ -5305,28 +5325,28 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>14</v>
@@ -5334,28 +5354,28 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="I10" s="11" t="n">
         <v>15</v>
@@ -5363,28 +5383,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>16</v>
@@ -5392,28 +5412,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="I12" s="11" t="n">
         <v>17</v>
@@ -5421,26 +5441,26 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="12" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>18</v>
@@ -5448,24 +5468,24 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="12" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="I14" s="11" t="n">
         <v>22</v>
@@ -5473,26 +5493,26 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="12" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="I15" s="11" t="n">
         <v>25</v>
@@ -5540,25 +5560,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="C1" s="9" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5566,22 +5586,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,22 +5609,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5612,22 +5632,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5635,22 +5655,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,22 +5678,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5681,22 +5701,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5704,22 +5724,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>816</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5727,22 +5747,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5750,22 +5770,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5773,22 +5793,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -5821,1700 +5841,1700 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>929</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>930</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>939</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>888</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>940</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>941</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
     </row>
   </sheetData>
@@ -7552,16 +7572,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7569,13 +7589,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7583,13 +7603,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7597,13 +7617,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7611,13 +7631,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7625,13 +7645,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7639,13 +7659,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7653,13 +7673,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7667,13 +7687,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,13 +7701,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7695,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,13 +7729,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7723,13 +7743,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7737,13 +7757,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7751,13 +7771,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7765,13 +7785,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7779,13 +7799,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,13 +7813,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7807,13 +7827,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7821,13 +7841,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7835,13 +7855,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,13 +7869,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7863,13 +7883,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7877,13 +7897,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7891,13 +7911,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
   </sheetData>
@@ -7933,50 +7953,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -8024,376 +8044,376 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="R2" s="16" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="U2" s="16" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="Q4" s="16" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="S5" s="16" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="16" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="S6" s="16" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="U6" s="16" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="16" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="16" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="16" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="16" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
     </row>
   </sheetData>
@@ -8412,7 +8432,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -8427,423 +8447,455 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="O2" s="12"/>
+        <v>95</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="O4" s="12"/>
+        <v>121</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="O5" s="12"/>
+        <v>133</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="O6" s="12"/>
+        <v>145</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="O8" s="12"/>
+        <v>171</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="O9" s="12"/>
+        <v>183</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:P1"/>
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C300" type="list">
       <formula1>Listas!$A$2:$A$4</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O300" type="list">
+      <formula1>Listas!$F$2:$F$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -8863,7 +8915,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -8885,164 +8937,168 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="25" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="26" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L1" s="9" t="s">
         <v>13</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AB1" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AC1" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG1" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AH1" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AI1" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AJ1" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AK1" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
+      </c>
+      <c r="AL1" s="9" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N2" s="14" t="n">
         <v>46027</v>
@@ -9054,106 +9110,109 @@
         <v>46160</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AH2" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="14" t="n">
         <v>46213</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L3" s="13" t="n">
         <v>0.6</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="N3" s="14" t="n">
         <v>46174</v>
@@ -9163,108 +9222,111 @@
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="12" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="X3" s="10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF3" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI3" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
+      </c>
+      <c r="AI3" s="11" t="s">
+        <v>247</v>
       </c>
       <c r="AJ3" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="AK3" s="14" t="n">
+        <v>248</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="AL3" s="14" t="n">
         <v>46218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L4" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="N4" s="14" t="n">
         <v>46188</v>
@@ -9274,106 +9336,109 @@
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="W4" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="X4" s="10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AC4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI4" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="14" t="n">
+        <v>247</v>
+      </c>
+      <c r="AI4" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="14" t="n">
         <v>46223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L5" s="13" t="n">
         <v>0.45</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="N5" s="14" t="n">
         <v>46146</v>
@@ -9383,106 +9448,109 @@
       </c>
       <c r="P5" s="14"/>
       <c r="Q5" s="12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="W5" s="10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="X5" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AB5" s="11" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG5" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI5" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="14" t="n">
+        <v>247</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AJ5" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="14" t="n">
         <v>46215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="L6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N6" s="14"/>
       <c r="O6" s="14" t="n">
@@ -9490,104 +9558,107 @@
       </c>
       <c r="P6" s="14"/>
       <c r="Q6" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="U6" s="12" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="V6" s="12" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="W6" s="10"/>
       <c r="X6" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Y6" s="11" t="s">
-        <v>243</v>
+        <v>96</v>
       </c>
       <c r="Z6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AA6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AB6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AC6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AD6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AE6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG6" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH6" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI6" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="14" t="n">
+        <v>247</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AJ6" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="14" t="n">
         <v>46204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L7" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N7" s="14" t="n">
         <v>45901</v>
@@ -9599,106 +9670,109 @@
         <v>46073</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="X7" s="10" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Y7" s="11" t="s">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="Z7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AA7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AB7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AC7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AD7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AE7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AF7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AG7" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AH7" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI7" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ7" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="14" t="n">
         <v>46203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="14" t="n">
@@ -9706,68 +9780,71 @@
       </c>
       <c r="P8" s="14"/>
       <c r="Q8" s="12" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="V8" s="12" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="W8" s="10"/>
       <c r="X8" s="10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Y8" s="11" t="s">
-        <v>243</v>
+        <v>96</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AA8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AB8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AC8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AD8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AE8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AF8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG8" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AH8" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI8" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="14" t="n">
+        <v>247</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="AJ8" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="14" t="n">
         <v>46188</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK1"/>
-  <dataValidations count="14">
+  <autoFilter ref="A1:AL1"/>
+  <dataValidations count="15">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I300" type="list">
       <formula1>Listas!$D$2:$D$4</formula1>
       <formula2>0</formula2>
@@ -9824,6 +9901,10 @@
       <formula1>Listas!$F$2:$F$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="AI2:AI300" type="list">
+      <formula1>Listas!$F$2:$F$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9841,7 +9922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
@@ -9854,255 +9935,283 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>320</v>
+        <v>324</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>327</v>
+        <v>331</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>334</v>
+        <v>338</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>341</v>
+        <v>345</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>348</v>
+        <v>352</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>355</v>
+        <v>359</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:L1"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L300" type="list">
+      <formula1>Listas!$F$2:$F$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10137,492 +10246,492 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="K4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>394</v>
-      </c>
       <c r="H7" s="12" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K14" s="12"/>
     </row>
@@ -10662,340 +10771,340 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E3" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>463</v>
-      </c>
       <c r="G3" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E6" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>476</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J11" s="12"/>
     </row>
@@ -11040,461 +11149,461 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>46160</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>46083</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>525</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>521</v>
-      </c>
       <c r="E4" s="12" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>46146</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="J4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>46034</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>46125</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>46063</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="J7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>46139</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>45616</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>45883</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>46175</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="J11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>46211</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>46065</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="J13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>46112</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="J14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>46148</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J15" s="12"/>
     </row>
@@ -11550,60 +11659,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>4</v>
@@ -11620,33 +11729,33 @@
         <v>Alto</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>3</v>
@@ -11663,33 +11772,33 @@
         <v>Alto</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K3" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>591</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>3</v>
@@ -11706,33 +11815,33 @@
         <v>Alto</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>4</v>
@@ -11749,33 +11858,33 @@
         <v>Alto</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2</v>
@@ -11792,33 +11901,33 @@
         <v>Moderado</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>2</v>
@@ -11835,33 +11944,33 @@
         <v>Moderado</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>4</v>
@@ -11878,33 +11987,33 @@
         <v>Moderado</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>2</v>
@@ -11921,33 +12030,33 @@
         <v>Moderado</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>3</v>
@@ -11964,16 +12073,16 @@
         <v>Moderado</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -12032,66 +12141,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H2" s="11" t="n">
         <v>120</v>
@@ -12104,10 +12213,10 @@
         <v>Acima da meta</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M2" s="14" t="n">
         <v>46203</v>
@@ -12115,25 +12224,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>635</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>636</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>632</v>
       </c>
       <c r="H3" s="11" t="n">
         <v>30</v>
@@ -12146,10 +12255,10 @@
         <v>Meta atingida</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M3" s="14" t="n">
         <v>46203</v>
@@ -12157,25 +12266,25 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>1</v>
@@ -12188,10 +12297,10 @@
         <v>Meta atingida</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M4" s="14" t="n">
         <v>46203</v>
@@ -12199,25 +12308,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>100</v>
@@ -12230,10 +12339,10 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M5" s="14" t="n">
         <v>46203</v>
@@ -12241,25 +12350,25 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E6" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>645</v>
-      </c>
       <c r="G6" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>75</v>
@@ -12272,10 +12381,10 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M6" s="14" t="n">
         <v>46203</v>
@@ -12283,25 +12392,25 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>650</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>652</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>645</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>646</v>
       </c>
       <c r="H7" s="11" t="n">
         <v>100</v>
@@ -12314,10 +12423,10 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="M7" s="14" t="n">
         <v>46203</v>
@@ -12325,25 +12434,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>95</v>
@@ -12356,10 +12465,10 @@
         <v>Meta atingida</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>46203</v>
@@ -12367,25 +12476,25 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>100</v>
@@ -12398,10 +12507,10 @@
         <v>Abaixo da meta</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>46203</v>
@@ -12409,25 +12518,25 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>120</v>
@@ -12438,10 +12547,10 @@
         <v>Sem medição</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="M10" s="14"/>
     </row>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="1253">
   <si>
     <t xml:space="preserve">Painel de Processos — Base de Dados (DADOS FICTÍCIOS)</t>
   </si>
@@ -2439,6 +2439,21 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.abpmp-br.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REP-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPMN 2.0 — Business Process Model and Notation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especificação oficial da notação usada nos diagramas (Bizagi e demais ferramentas de modelagem): símbolos, semântica de execução e serialização XML.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMG (Object Management Group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.omg.org/spec/BPMN/2.0/</t>
   </si>
   <si>
     <t xml:space="preserve">REP-025</t>
@@ -4685,7 +4700,7 @@
       </c>
       <c r="C47" s="8" t="n">
         <f aca="false">COUNTA(Repositorio!$A$2:$A$500)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5050,7 +5065,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -5456,16 +5471,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
         <v>796</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>739</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="12" t="s">
         <v>797</v>
@@ -5474,12 +5487,39 @@
         <v>798</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>799</v>
-      </c>
-      <c r="I15" s="11" t="n">
+      <c r="H16" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="I16" s="11" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5531,19 +5571,19 @@
         <v>66</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5554,19 +5594,19 @@
         <v>601</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5577,19 +5617,19 @@
         <v>605</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5600,19 +5640,19 @@
         <v>597</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>165</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5620,22 +5660,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5643,22 +5683,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>96</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5666,22 +5706,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5689,22 +5729,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5712,22 +5752,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>85</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,22 +5775,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>142</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5758,22 +5798,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -5806,19 +5846,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>616</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5826,16 +5866,16 @@
         <v>794</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>794</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5843,877 +5883,877 @@
         <v>440</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>854</v>
-      </c>
       <c r="C4" s="12" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>726</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="D20" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>920</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>930</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B38" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>891</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>972</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>973</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>726</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>765</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>63</v>
@@ -6722,19 +6762,19 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6742,67 +6782,67 @@
         <v>172</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6810,67 +6850,67 @@
         <v>613</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>765</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6878,186 +6918,186 @@
         <v>752</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>723</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>723</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>765</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7065,30 +7105,30 @@
         <v>63</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>63</v>
@@ -7096,138 +7136,138 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7235,78 +7275,78 @@
         <v>341</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>63</v>
@@ -7317,98 +7357,98 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>726</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>726</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>748</v>
@@ -7419,87 +7459,87 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>748</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>723</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
   </sheetData>
@@ -7543,7 +7583,7 @@
         <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>569</v>
@@ -7554,13 +7594,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7568,13 +7608,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7582,13 +7622,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7596,13 +7636,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7610,13 +7650,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7624,13 +7664,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7638,13 +7678,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7652,13 +7692,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7666,13 +7706,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7680,13 +7720,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7694,13 +7734,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7708,13 +7748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7722,13 +7762,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7736,13 +7776,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7750,13 +7790,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7764,13 +7804,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7778,13 +7818,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7792,13 +7832,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7806,13 +7846,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7820,13 +7860,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7834,13 +7874,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7848,13 +7888,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7862,13 +7902,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7876,13 +7916,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -7918,39 +7958,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>727</v>
@@ -7958,7 +7998,7 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>731</v>
@@ -8009,7 +8049,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>177</v>
@@ -8024,10 +8064,10 @@
         <v>176</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>441</v>
@@ -8036,16 +8076,16 @@
         <v>491</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="N1" s="9" t="s">
         <v>612</v>
@@ -8054,22 +8094,22 @@
         <v>615</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8119,7 +8159,7 @@
         <v>627</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="Q2" s="16" t="s">
         <v>662</v>
@@ -8128,13 +8168,13 @@
         <v>722</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="U2" s="16" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8172,7 +8212,7 @@
         <v>580</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="M3" s="16" t="s">
         <v>577</v>
@@ -8181,10 +8221,10 @@
         <v>622</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
       <c r="Q3" s="16" t="s">
         <v>670</v>
@@ -8196,10 +8236,10 @@
         <v>739</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,7 +8250,7 @@
         <v>207</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>292</v>
@@ -8234,7 +8274,7 @@
         <v>588</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="M4" s="16" t="s">
         <v>606</v>
@@ -8243,7 +8283,7 @@
         <v>623</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="Q4" s="16" t="s">
         <v>678</v>
@@ -8255,18 +8295,18 @@
         <v>734</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="16" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>440</v>
@@ -8275,19 +8315,19 @@
         <v>523</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>595</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="P5" s="16" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="Q5" s="16" t="s">
         <v>698</v>
@@ -8299,10 +8339,10 @@
         <v>773</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8310,19 +8350,19 @@
         <v>208</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>514</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="O6" s="16" t="s">
         <v>654</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="Q6" s="16" t="s">
         <v>706</v>
@@ -8334,10 +8374,10 @@
         <v>756</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="U6" s="16" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8345,19 +8385,19 @@
         <v>506</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="S7" s="16" t="s">
         <v>779</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="U7" s="16" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8365,7 +8405,7 @@
         <v>560</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8373,7 +8413,7 @@
         <v>519</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8383,7 +8423,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I11" s="16" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
     </row>
   </sheetData>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -99,6 +99,11 @@
           <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -164,6 +169,11 @@
           <t xml:space="preserve">Estatuto Social; Regimento Interno; Lei nº 13.303/2016</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT; AI/GOM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -229,6 +239,11 @@
           <t xml:space="preserve">Política de Gestão de Riscos (fictícia); IN Conjunta MP/CGU nº 01/2016</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM; AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -294,6 +309,11 @@
           <t xml:space="preserve">Lei nº 14.133/2021; Portarias de transferências voluntárias</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB; AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -359,6 +379,11 @@
           <t xml:space="preserve">Lei nº 12.787/2013 (Política Nacional de Irrigação)</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC; AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -424,6 +449,11 @@
           <t xml:space="preserve">Legislação ambiental aplicável</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP; AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -494,6 +524,11 @@
           <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI; AE/GPE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -559,6 +594,11 @@
           <t xml:space="preserve">CLT; Normas internas de pessoal</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE; AE/GAG</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -622,6 +662,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">IN SGD nº 94/2022; Política de Segurança da Informação (fictícia)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG; AR/GDT</t>
         </is>
       </c>
     </row>
@@ -5176,6 +5221,11 @@
           <t xml:space="preserve">Pendencia</t>
         </is>
       </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5348,7 +5398,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitorar indicadores do processo e revisar POP em 12 meses.</t>
+          <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG; AR/GDT</t>
         </is>
       </c>
     </row>
@@ -5521,6 +5576,11 @@
           <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
         </is>
       </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT; AI/GOM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5686,6 +5746,11 @@
           <t xml:space="preserve">Concluir modelagem AS-IS das medições e pagamentos.</t>
         </is>
       </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM; AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5851,6 +5916,11 @@
           <t xml:space="preserve">Agendar oficina de validação do AS-IS com o distrito.</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB; AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6006,6 +6076,11 @@
           <t xml:space="preserve">Enviar formulário de levantamento à área (previsto ago/2026).</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC; AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6176,6 +6251,11 @@
           <t xml:space="preserve">Ciclo de monitoramento trimestral (próximo: set/2026).</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP; AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6329,6 +6409,11 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t xml:space="preserve">Aguardando priorização no ciclo 2027.</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI; AE/GPE</t>
         </is>
       </c>
     </row>
@@ -6400,6 +6485,11 @@
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6455,6 +6545,11 @@
           <t xml:space="preserve">SEI; Compras.gov.br</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6510,6 +6605,11 @@
           <t xml:space="preserve">SEI</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6565,6 +6665,11 @@
           <t xml:space="preserve">Painel de Preços; PNCP; SEI</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6620,6 +6725,11 @@
           <t xml:space="preserve">Planilha padrão; SEI</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6675,6 +6785,11 @@
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6728,6 +6843,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
     </row>
@@ -6804,6 +6924,16 @@
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Executor</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6869,6 +6999,16 @@
           <t xml:space="preserve">https://placehold.co/960x420/155bcb/ffffff?text=Diagrama+BPMN+A-06.01.01.01</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6929,6 +7069,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021, art. 18</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6984,6 +7134,16 @@
           <t xml:space="preserve">5 dias úteis</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7044,6 +7204,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021, art. 18</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7104,6 +7274,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021, art. 6º, XXIII</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7164,6 +7344,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021, art. 53</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7224,6 +7414,16 @@
           <t xml:space="preserve">IN SEGES nº 65/2021</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7284,6 +7484,16 @@
           <t xml:space="preserve">IN SEGES nº 65/2021, art. 6º</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7344,6 +7554,16 @@
           <t xml:space="preserve">IN SEGES nº 65/2021, art. 6º, §3º</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7404,6 +7624,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021, art. 54</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7464,6 +7694,16 @@
           <t xml:space="preserve">Lei nº 14.133/2021</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7519,6 +7759,16 @@
           <t xml:space="preserve">Semanal</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7572,6 +7822,16 @@
       <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Diário</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
     </row>
@@ -7643,6 +7903,11 @@
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7693,6 +7958,11 @@
           <t xml:space="preserve">0,5 dia</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7748,6 +8018,11 @@
           <t xml:space="preserve">Modelo DOC-006/DOC-012.</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7798,6 +8073,11 @@
           <t xml:space="preserve">1 dia</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7848,6 +8128,11 @@
           <t xml:space="preserve">0,5 dia</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7898,6 +8183,11 @@
           <t xml:space="preserve">0,5 dia</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7953,6 +8243,11 @@
           <t xml:space="preserve">Mínimo de 3 fontes (IN 65/2021).</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8003,6 +8298,11 @@
           <t xml:space="preserve">0,5 dia</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8053,6 +8353,11 @@
           <t xml:space="preserve">0,5 dia</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8103,6 +8408,11 @@
           <t xml:space="preserve">Imediato</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8151,6 +8461,11 @@
       <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dia</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
     </row>
@@ -8231,12 +8546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimento Operacional (POP)</t>
+          <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POP 06.01 — Planejamento da Contratação</t>
+          <t xml:space="preserve">PRO 06.01 — Planejamento da Contratação</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8528,7 +8843,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimento Operacional (POP)</t>
+          <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9242,7 +9557,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publicar POP, treinar substitutos e revezar a equipe de planejamento.</t>
+          <t xml:space="preserve">Publicar o PRO, treinar substitutos e revezar a equipe de planejamento.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -9425,7 +9740,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoramento normativo mensal (resenha) e revisão programada dos POPs.</t>
+          <t xml:space="preserve">Monitoramento normativo mensal (resenha) e revisão programada dos PROs.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -1785,8 +1785,9 @@
           <t xml:space="preserve">AE</t>
         </is>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="7" t="str">
         <f>IF(D2="","",IFERROR(VLOOKUP(D2,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Área de Gestão Estratégica</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1830,8 +1831,9 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="7" t="str">
         <f>IF(D3="","",IFERROR(VLOOKUP(D3,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Planejamento Estratégico</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -1875,8 +1877,9 @@
           <t xml:space="preserve">AE/GPE/UNP</t>
         </is>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="7" t="str">
         <f>IF(D4="","",IFERROR(VLOOKUP(D4,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Unidade de Gestão Normativa e de Processos</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1920,8 +1923,9 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="7" t="str">
         <f>IF(D5="","",IFERROR(VLOOKUP(D5,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Planejamento Estratégico</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1965,8 +1969,9 @@
           <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="7" t="str">
         <f>IF(D6="","",IFERROR(VLOOKUP(D6,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Tecnologia da Informação</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2010,8 +2015,9 @@
           <t xml:space="preserve">AR/GPR</t>
         </is>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="7" t="str">
         <f>IF(D7="","",IFERROR(VLOOKUP(D7,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Projetos de Revitalização</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -2055,8 +2061,9 @@
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="7" t="str">
         <f>IF(D8="","",IFERROR(VLOOKUP(D8,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Auditoria e Governança</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2100,8 +2107,9 @@
           <t xml:space="preserve">AE/GPE/UNP</t>
         </is>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="7" t="str">
         <f>IF(D9="","",IFERROR(VLOOKUP(D9,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Unidade de Gestão Normativa e de Processos</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -2145,8 +2153,9 @@
           <t xml:space="preserve">AE/GPE/UNP</t>
         </is>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="7" t="str">
         <f>IF(D10="","",IFERROR(VLOOKUP(D10,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Unidade de Gestão Normativa e de Processos</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2190,8 +2199,9 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="7" t="str">
         <f>IF(D11="","",IFERROR(VLOOKUP(D11,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Planejamento Estratégico</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -2235,8 +2245,9 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="7" t="str">
         <f>IF(D12="","",IFERROR(VLOOKUP(D12,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Gerência de Licitações e Contratos</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2280,8 +2291,9 @@
           <t xml:space="preserve">PR/ASCOM</t>
         </is>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="7" t="str">
         <f>IF(D13="","",IFERROR(VLOOKUP(D13,Listas!$V$2:$W$40,2,FALSE),""))</f>
+        <v>Assessoria de Comunicação</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -7444,8 +7456,9 @@
           <t xml:space="preserve">P-06.01</t>
         </is>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="7" t="str">
         <f>IF(A2="","",IF(LEFT(A2,2)="P-","MP-"&amp;MID(A2,3,2),""))</f>
+        <v>MP-06</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -7494,6 +7507,7 @@
       </c>
       <c r="L2" s="7">
         <f>IF(COUNTIF(Y2:AH2,"Sim")+COUNTIF(Y2:AH2,"Não")=0,"",ROUND(COUNTIF(Y2:AH2,"Sim")/(COUNTIF(Y2:AH2,"Sim")+COUNTIF(Y2:AH2,"Não")),4))</f>
+        <v>1</v>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
@@ -7622,8 +7636,9 @@
           <t xml:space="preserve">P-06.02</t>
         </is>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="7" t="str">
         <f>IF(A3="","",IF(LEFT(A3,2)="P-","MP-"&amp;MID(A3,3,2),""))</f>
+        <v>MP-06</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -7672,6 +7687,7 @@
       </c>
       <c r="L3" s="7">
         <f>IF(COUNTIF(Y3:AH3,"Sim")+COUNTIF(Y3:AH3,"Não")=0,"",ROUND(COUNTIF(Y3:AH3,"Sim")/(COUNTIF(Y3:AH3,"Sim")+COUNTIF(Y3:AH3,"Não")),4))</f>
+        <v>0.4</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -7795,8 +7811,9 @@
           <t xml:space="preserve">P-06.03</t>
         </is>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="7" t="str">
         <f>IF(A4="","",IF(LEFT(A4,2)="P-","MP-"&amp;MID(A4,3,2),""))</f>
+        <v>MP-06</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -7845,6 +7862,7 @@
       </c>
       <c r="L4" s="7">
         <f>IF(COUNTIF(Y4:AH4,"Sim")+COUNTIF(Y4:AH4,"Não")=0,"",ROUND(COUNTIF(Y4:AH4,"Sim")/(COUNTIF(Y4:AH4,"Sim")+COUNTIF(Y4:AH4,"Não")),4))</f>
+        <v>0.2</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -7963,8 +7981,9 @@
           <t xml:space="preserve">P-04.01</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="7" t="str">
         <f>IF(A5="","",IF(LEFT(A5,2)="P-","MP-"&amp;MID(A5,3,2),""))</f>
+        <v>MP-04</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -8013,6 +8032,7 @@
       </c>
       <c r="L5" s="7">
         <f>IF(COUNTIF(Y5:AH5,"Sim")+COUNTIF(Y5:AH5,"Não")=0,"",ROUND(COUNTIF(Y5:AH5,"Sim")/(COUNTIF(Y5:AH5,"Sim")+COUNTIF(Y5:AH5,"Não")),4))</f>
+        <v>0.3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -8131,8 +8151,9 @@
           <t xml:space="preserve">P-05.01</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="7" t="str">
         <f>IF(A6="","",IF(LEFT(A6,2)="P-","MP-"&amp;MID(A6,3,2),""))</f>
+        <v>MP-05</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -8181,6 +8202,7 @@
       </c>
       <c r="L6" s="7">
         <f>IF(COUNTIF(Y6:AH6,"Sim")+COUNTIF(Y6:AH6,"Não")=0,"",ROUND(COUNTIF(Y6:AH6,"Sim")/(COUNTIF(Y6:AH6,"Sim")+COUNTIF(Y6:AH6,"Não")),4))</f>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -8289,8 +8311,9 @@
           <t xml:space="preserve">P-01.01</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="7" t="str">
         <f>IF(A7="","",IF(LEFT(A7,2)="P-","MP-"&amp;MID(A7,3,2),""))</f>
+        <v>MP-01</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -8339,6 +8362,7 @@
       </c>
       <c r="L7" s="7">
         <f>IF(COUNTIF(Y7:AH7,"Sim")+COUNTIF(Y7:AH7,"Não")=0,"",ROUND(COUNTIF(Y7:AH7,"Sim")/(COUNTIF(Y7:AH7,"Sim")+COUNTIF(Y7:AH7,"Não")),4))</f>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -8462,8 +8486,9 @@
           <t xml:space="preserve">P-07.01</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="7" t="str">
         <f>IF(A8="","",IF(LEFT(A8,2)="P-","MP-"&amp;MID(A8,3,2),""))</f>
+        <v>MP-07</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -8512,6 +8537,7 @@
       </c>
       <c r="L8" s="7">
         <f>IF(COUNTIF(Y8:AH8,"Sim")+COUNTIF(Y8:AH8,"Não")=0,"",ROUND(COUNTIF(Y8:AH8,"Sim")/(COUNTIF(Y8:AH8,"Sim")+COUNTIF(Y8:AH8,"Não")),4))</f>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -10931,8 +10957,9 @@
           <t xml:space="preserve">DOC-001</t>
         </is>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="7" t="str">
         <f>IF(C2="","",IF(LEFT(C2,3)="MP-","Macroprocesso",IF(LEFT(C2,3)="SP-","Subprocesso",IF(LEFT(C2,2)="P-","Processo",IF(LEFT(C2,2)="A-","Atividade",IF(LEFT(C2,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -10981,8 +11008,9 @@
           <t xml:space="preserve">DOC-002</t>
         </is>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="7" t="str">
         <f>IF(C3="","",IF(LEFT(C3,3)="MP-","Macroprocesso",IF(LEFT(C3,3)="SP-","Subprocesso",IF(LEFT(C3,2)="P-","Processo",IF(LEFT(C3,2)="A-","Atividade",IF(LEFT(C3,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -11031,8 +11059,9 @@
           <t xml:space="preserve">DOC-003</t>
         </is>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="7" t="str">
         <f>IF(C4="","",IF(LEFT(C4,3)="MP-","Macroprocesso",IF(LEFT(C4,3)="SP-","Subprocesso",IF(LEFT(C4,2)="P-","Processo",IF(LEFT(C4,2)="A-","Atividade",IF(LEFT(C4,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -11076,8 +11105,9 @@
           <t xml:space="preserve">DOC-004</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="7" t="str">
         <f>IF(C5="","",IF(LEFT(C5,3)="MP-","Macroprocesso",IF(LEFT(C5,3)="SP-","Subprocesso",IF(LEFT(C5,2)="P-","Processo",IF(LEFT(C5,2)="A-","Atividade",IF(LEFT(C5,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -11126,8 +11156,9 @@
           <t xml:space="preserve">DOC-005</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="7" t="str">
         <f>IF(C6="","",IF(LEFT(C6,3)="MP-","Macroprocesso",IF(LEFT(C6,3)="SP-","Subprocesso",IF(LEFT(C6,2)="P-","Processo",IF(LEFT(C6,2)="A-","Atividade",IF(LEFT(C6,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -11171,8 +11202,9 @@
           <t xml:space="preserve">DOC-006</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="7" t="str">
         <f>IF(C7="","",IF(LEFT(C7,3)="MP-","Macroprocesso",IF(LEFT(C7,3)="SP-","Subprocesso",IF(LEFT(C7,2)="P-","Processo",IF(LEFT(C7,2)="A-","Atividade",IF(LEFT(C7,2)="T-","Tarefa",""))))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -11216,8 +11248,9 @@
           <t xml:space="preserve">DOC-007</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="7" t="str">
         <f>IF(C8="","",IF(LEFT(C8,3)="MP-","Macroprocesso",IF(LEFT(C8,3)="SP-","Subprocesso",IF(LEFT(C8,2)="P-","Processo",IF(LEFT(C8,2)="A-","Atividade",IF(LEFT(C8,2)="T-","Tarefa",""))))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -11261,8 +11294,9 @@
           <t xml:space="preserve">DOC-008</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="7" t="str">
         <f>IF(C9="","",IF(LEFT(C9,3)="MP-","Macroprocesso",IF(LEFT(C9,3)="SP-","Subprocesso",IF(LEFT(C9,2)="P-","Processo",IF(LEFT(C9,2)="A-","Atividade",IF(LEFT(C9,2)="T-","Tarefa",""))))))</f>
+        <v>Macroprocesso</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -11306,8 +11340,9 @@
           <t xml:space="preserve">DOC-009</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="7" t="str">
         <f>IF(C10="","",IF(LEFT(C10,3)="MP-","Macroprocesso",IF(LEFT(C10,3)="SP-","Subprocesso",IF(LEFT(C10,2)="P-","Processo",IF(LEFT(C10,2)="A-","Atividade",IF(LEFT(C10,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -11351,8 +11386,9 @@
           <t xml:space="preserve">DOC-010</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="7" t="str">
         <f>IF(C11="","",IF(LEFT(C11,3)="MP-","Macroprocesso",IF(LEFT(C11,3)="SP-","Subprocesso",IF(LEFT(C11,2)="P-","Processo",IF(LEFT(C11,2)="A-","Atividade",IF(LEFT(C11,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -11396,8 +11432,9 @@
           <t xml:space="preserve">DOC-011</t>
         </is>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="7" t="str">
         <f>IF(C12="","",IF(LEFT(C12,3)="MP-","Macroprocesso",IF(LEFT(C12,3)="SP-","Subprocesso",IF(LEFT(C12,2)="P-","Processo",IF(LEFT(C12,2)="A-","Atividade",IF(LEFT(C12,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -11441,8 +11478,9 @@
           <t xml:space="preserve">DOC-012</t>
         </is>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="7" t="str">
         <f>IF(C13="","",IF(LEFT(C13,3)="MP-","Macroprocesso",IF(LEFT(C13,3)="SP-","Subprocesso",IF(LEFT(C13,2)="P-","Processo",IF(LEFT(C13,2)="A-","Atividade",IF(LEFT(C13,2)="T-","Tarefa",""))))))</f>
+        <v>Atividade</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -11486,8 +11524,9 @@
           <t xml:space="preserve">DOC-013</t>
         </is>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="7" t="str">
         <f>IF(C14="","",IF(LEFT(C14,3)="MP-","Macroprocesso",IF(LEFT(C14,3)="SP-","Subprocesso",IF(LEFT(C14,2)="P-","Processo",IF(LEFT(C14,2)="A-","Atividade",IF(LEFT(C14,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -11531,8 +11570,9 @@
           <t xml:space="preserve">DOC-014</t>
         </is>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="7" t="str">
         <f>IF(C15="","",IF(LEFT(C15,3)="MP-","Macroprocesso",IF(LEFT(C15,3)="SP-","Subprocesso",IF(LEFT(C15,2)="P-","Processo",IF(LEFT(C15,2)="A-","Atividade",IF(LEFT(C15,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -11576,8 +11616,9 @@
           <t xml:space="preserve">DOC-015</t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="7" t="str">
         <f>IF(C16="","",IF(LEFT(C16,3)="MP-","Macroprocesso",IF(LEFT(C16,3)="SP-","Subprocesso",IF(LEFT(C16,2)="P-","Processo",IF(LEFT(C16,2)="A-","Atividade",IF(LEFT(C16,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -11728,11 +11769,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-001</t>
-        </is>
-      </c>
-      <c r="B2" s="7">
+          <t xml:space="preserve">RIS-001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="str">
         <f>IF(C2="","",IF(LEFT(C2,3)="MP-","Macroprocesso",IF(LEFT(C2,3)="SP-","Subprocesso",IF(LEFT(C2,2)="P-","Processo",IF(LEFT(C2,2)="A-","Atividade",IF(LEFT(C2,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -11761,9 +11803,11 @@
       </c>
       <c r="H2" s="7">
         <f>IF(OR(F2="",G2=""),"",F2*G2)</f>
-      </c>
-      <c r="I2" s="7">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="str">
         <f>IF(H2="","",IF(H2&gt;=20,"Extremo",IF(H2&gt;=12,"Alto",IF(H2&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Alto</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -11789,11 +11833,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-002</t>
-        </is>
-      </c>
-      <c r="B3" s="7">
+          <t xml:space="preserve">RIS-002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="str">
         <f>IF(C3="","",IF(LEFT(C3,3)="MP-","Macroprocesso",IF(LEFT(C3,3)="SP-","Subprocesso",IF(LEFT(C3,2)="P-","Processo",IF(LEFT(C3,2)="A-","Atividade",IF(LEFT(C3,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -11822,9 +11867,11 @@
       </c>
       <c r="H3" s="7">
         <f>IF(OR(F3="",G3=""),"",F3*G3)</f>
-      </c>
-      <c r="I3" s="7">
+        <v>12</v>
+      </c>
+      <c r="I3" s="7" t="str">
         <f>IF(H3="","",IF(H3&gt;=20,"Extremo",IF(H3&gt;=12,"Alto",IF(H3&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Alto</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -11850,11 +11897,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-003</t>
-        </is>
-      </c>
-      <c r="B4" s="7">
+          <t xml:space="preserve">RIS-003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="str">
         <f>IF(C4="","",IF(LEFT(C4,3)="MP-","Macroprocesso",IF(LEFT(C4,3)="SP-","Subprocesso",IF(LEFT(C4,2)="P-","Processo",IF(LEFT(C4,2)="A-","Atividade",IF(LEFT(C4,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -11883,9 +11931,11 @@
       </c>
       <c r="H4" s="7">
         <f>IF(OR(F4="",G4=""),"",F4*G4)</f>
-      </c>
-      <c r="I4" s="7">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7" t="str">
         <f>IF(H4="","",IF(H4&gt;=20,"Extremo",IF(H4&gt;=12,"Alto",IF(H4&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Alto</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -11911,11 +11961,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-004</t>
-        </is>
-      </c>
-      <c r="B5" s="7">
+          <t xml:space="preserve">RIS-004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="str">
         <f>IF(C5="","",IF(LEFT(C5,3)="MP-","Macroprocesso",IF(LEFT(C5,3)="SP-","Subprocesso",IF(LEFT(C5,2)="P-","Processo",IF(LEFT(C5,2)="A-","Atividade",IF(LEFT(C5,2)="T-","Tarefa",""))))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -11944,9 +11995,11 @@
       </c>
       <c r="H5" s="7">
         <f>IF(OR(F5="",G5=""),"",F5*G5)</f>
-      </c>
-      <c r="I5" s="7">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="str">
         <f>IF(H5="","",IF(H5&gt;=20,"Extremo",IF(H5&gt;=12,"Alto",IF(H5&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Alto</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -11972,11 +12025,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-005</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
+          <t xml:space="preserve">RIS-005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="str">
         <f>IF(C6="","",IF(LEFT(C6,3)="MP-","Macroprocesso",IF(LEFT(C6,3)="SP-","Subprocesso",IF(LEFT(C6,2)="P-","Processo",IF(LEFT(C6,2)="A-","Atividade",IF(LEFT(C6,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -12005,9 +12059,11 @@
       </c>
       <c r="H6" s="7">
         <f>IF(OR(F6="",G6=""),"",F6*G6)</f>
-      </c>
-      <c r="I6" s="7">
+        <v>10</v>
+      </c>
+      <c r="I6" s="7" t="str">
         <f>IF(H6="","",IF(H6&gt;=20,"Extremo",IF(H6&gt;=12,"Alto",IF(H6&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Moderado</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -12033,11 +12089,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-006</t>
-        </is>
-      </c>
-      <c r="B7" s="7">
+          <t xml:space="preserve">RIS-006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="str">
         <f>IF(C7="","",IF(LEFT(C7,3)="MP-","Macroprocesso",IF(LEFT(C7,3)="SP-","Subprocesso",IF(LEFT(C7,2)="P-","Processo",IF(LEFT(C7,2)="A-","Atividade",IF(LEFT(C7,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -12066,9 +12123,11 @@
       </c>
       <c r="H7" s="7">
         <f>IF(OR(F7="",G7=""),"",F7*G7)</f>
-      </c>
-      <c r="I7" s="7">
+        <v>8</v>
+      </c>
+      <c r="I7" s="7" t="str">
         <f>IF(H7="","",IF(H7&gt;=20,"Extremo",IF(H7&gt;=12,"Alto",IF(H7&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Moderado</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -12094,11 +12153,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-007</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
+          <t xml:space="preserve">RIS-007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="str">
         <f>IF(C8="","",IF(LEFT(C8,3)="MP-","Macroprocesso",IF(LEFT(C8,3)="SP-","Subprocesso",IF(LEFT(C8,2)="P-","Processo",IF(LEFT(C8,2)="A-","Atividade",IF(LEFT(C8,2)="T-","Tarefa",""))))))</f>
+        <v>Macroprocesso</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -12127,9 +12187,11 @@
       </c>
       <c r="H8" s="7">
         <f>IF(OR(F8="",G8=""),"",F8*G8)</f>
-      </c>
-      <c r="I8" s="7">
+        <v>8</v>
+      </c>
+      <c r="I8" s="7" t="str">
         <f>IF(H8="","",IF(H8&gt;=20,"Extremo",IF(H8&gt;=12,"Alto",IF(H8&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Moderado</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -12155,11 +12217,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-008</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
+          <t xml:space="preserve">RIS-008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="str">
         <f>IF(C9="","",IF(LEFT(C9,3)="MP-","Macroprocesso",IF(LEFT(C9,3)="SP-","Subprocesso",IF(LEFT(C9,2)="P-","Processo",IF(LEFT(C9,2)="A-","Atividade",IF(LEFT(C9,2)="T-","Tarefa",""))))))</f>
+        <v>Atividade</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -12188,9 +12251,11 @@
       </c>
       <c r="H9" s="7">
         <f>IF(OR(F9="",G9=""),"",F9*G9)</f>
-      </c>
-      <c r="I9" s="7">
+        <v>6</v>
+      </c>
+      <c r="I9" s="7" t="str">
         <f>IF(H9="","",IF(H9&gt;=20,"Extremo",IF(H9&gt;=12,"Alto",IF(H9&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Moderado</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -12216,11 +12281,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R-009</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
+          <t xml:space="preserve">RIS-009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="str">
         <f>IF(C10="","",IF(LEFT(C10,3)="MP-","Macroprocesso",IF(LEFT(C10,3)="SP-","Subprocesso",IF(LEFT(C10,2)="P-","Processo",IF(LEFT(C10,2)="A-","Atividade",IF(LEFT(C10,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -12249,9 +12315,11 @@
       </c>
       <c r="H10" s="7">
         <f>IF(OR(F10="",G10=""),"",F10*G10)</f>
-      </c>
-      <c r="I10" s="7">
+        <v>9</v>
+      </c>
+      <c r="I10" s="7" t="str">
         <f>IF(H10="","",IF(H10&gt;=20,"Extremo",IF(H10&gt;=12,"Alto",IF(H10&gt;=5,"Moderado","Baixo"))))</f>
+        <v>Moderado</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -12388,8 +12456,9 @@
           <t xml:space="preserve">IND-001</t>
         </is>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="7" t="str">
         <f>IF(C2="","",IF(LEFT(C2,3)="MP-","Macroprocesso",IF(LEFT(C2,3)="SP-","Subprocesso",IF(LEFT(C2,2)="P-","Processo",IF(LEFT(C2,2)="A-","Atividade",IF(LEFT(C2,2)="T-","Tarefa",""))))))</f>
+        <v>Macroprocesso</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -12426,8 +12495,9 @@
           <t xml:space="preserve">148</t>
         </is>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="7" t="str">
         <f>IF(I2="","Sem medição",IF(H2="","Sem meta",IF(LEFT(G2,5)="Maior",IF(I2&gt;=H2,"Meta atingida","Abaixo da meta"),IF(I2&lt;=H2,"Meta atingida","Acima da meta"))))</f>
+        <v>Acima da meta</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -12451,8 +12521,9 @@
           <t xml:space="preserve">IND-002</t>
         </is>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="7" t="str">
         <f>IF(C3="","",IF(LEFT(C3,3)="MP-","Macroprocesso",IF(LEFT(C3,3)="SP-","Subprocesso",IF(LEFT(C3,2)="P-","Processo",IF(LEFT(C3,2)="A-","Atividade",IF(LEFT(C3,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -12489,8 +12560,9 @@
           <t xml:space="preserve">26</t>
         </is>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="7" t="str">
         <f>IF(I3="","Sem medição",IF(H3="","Sem meta",IF(LEFT(G3,5)="Maior",IF(I3&gt;=H3,"Meta atingida","Abaixo da meta"),IF(I3&lt;=H3,"Meta atingida","Acima da meta"))))</f>
+        <v>Meta atingida</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -12514,8 +12586,9 @@
           <t xml:space="preserve">IND-003</t>
         </is>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="7" t="str">
         <f>IF(C4="","",IF(LEFT(C4,3)="MP-","Macroprocesso",IF(LEFT(C4,3)="SP-","Subprocesso",IF(LEFT(C4,2)="P-","Processo",IF(LEFT(C4,2)="A-","Atividade",IF(LEFT(C4,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -12552,8 +12625,9 @@
           <t xml:space="preserve">0.8</t>
         </is>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="7" t="str">
         <f>IF(I4="","Sem medição",IF(H4="","Sem meta",IF(LEFT(G4,5)="Maior",IF(I4&gt;=H4,"Meta atingida","Abaixo da meta"),IF(I4&lt;=H4,"Meta atingida","Acima da meta"))))</f>
+        <v>Meta atingida</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -12577,8 +12651,9 @@
           <t xml:space="preserve">IND-004</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="7" t="str">
         <f>IF(C5="","",IF(LEFT(C5,3)="MP-","Macroprocesso",IF(LEFT(C5,3)="SP-","Subprocesso",IF(LEFT(C5,2)="P-","Processo",IF(LEFT(C5,2)="A-","Atividade",IF(LEFT(C5,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -12615,8 +12690,9 @@
           <t xml:space="preserve">92</t>
         </is>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="7" t="str">
         <f>IF(I5="","Sem medição",IF(H5="","Sem meta",IF(LEFT(G5,5)="Maior",IF(I5&gt;=H5,"Meta atingida","Abaixo da meta"),IF(I5&lt;=H5,"Meta atingida","Acima da meta"))))</f>
+        <v>Abaixo da meta</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -12640,8 +12716,9 @@
           <t xml:space="preserve">IND-005</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="7" t="str">
         <f>IF(C6="","",IF(LEFT(C6,3)="MP-","Macroprocesso",IF(LEFT(C6,3)="SP-","Subprocesso",IF(LEFT(C6,2)="P-","Processo",IF(LEFT(C6,2)="A-","Atividade",IF(LEFT(C6,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -12678,8 +12755,9 @@
           <t xml:space="preserve">71</t>
         </is>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="7" t="str">
         <f>IF(I6="","Sem medição",IF(H6="","Sem meta",IF(LEFT(G6,5)="Maior",IF(I6&gt;=H6,"Meta atingida","Abaixo da meta"),IF(I6&lt;=H6,"Meta atingida","Acima da meta"))))</f>
+        <v>Abaixo da meta</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -12703,8 +12781,9 @@
           <t xml:space="preserve">IND-006</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="7" t="str">
         <f>IF(C7="","",IF(LEFT(C7,3)="MP-","Macroprocesso",IF(LEFT(C7,3)="SP-","Subprocesso",IF(LEFT(C7,2)="P-","Processo",IF(LEFT(C7,2)="A-","Atividade",IF(LEFT(C7,2)="T-","Tarefa",""))))))</f>
+        <v>Macroprocesso</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -12741,8 +12820,9 @@
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="7" t="str">
         <f>IF(I7="","Sem medição",IF(H7="","Sem meta",IF(LEFT(G7,5)="Maior",IF(I7&gt;=H7,"Meta atingida","Abaixo da meta"),IF(I7&lt;=H7,"Meta atingida","Acima da meta"))))</f>
+        <v>Abaixo da meta</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -12766,8 +12846,9 @@
           <t xml:space="preserve">IND-007</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="7" t="str">
         <f>IF(C8="","",IF(LEFT(C8,3)="MP-","Macroprocesso",IF(LEFT(C8,3)="SP-","Subprocesso",IF(LEFT(C8,2)="P-","Processo",IF(LEFT(C8,2)="A-","Atividade",IF(LEFT(C8,2)="T-","Tarefa",""))))))</f>
+        <v>Processo</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -12804,8 +12885,9 @@
           <t xml:space="preserve">97</t>
         </is>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="7" t="str">
         <f>IF(I8="","Sem medição",IF(H8="","Sem meta",IF(LEFT(G8,5)="Maior",IF(I8&gt;=H8,"Meta atingida","Abaixo da meta"),IF(I8&lt;=H8,"Meta atingida","Acima da meta"))))</f>
+        <v>Meta atingida</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -12829,8 +12911,9 @@
           <t xml:space="preserve">IND-008</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="7" t="str">
         <f>IF(C9="","",IF(LEFT(C9,3)="MP-","Macroprocesso",IF(LEFT(C9,3)="SP-","Subprocesso",IF(LEFT(C9,2)="P-","Processo",IF(LEFT(C9,2)="A-","Atividade",IF(LEFT(C9,2)="T-","Tarefa",""))))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -12867,8 +12950,9 @@
           <t xml:space="preserve">88</t>
         </is>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="7" t="str">
         <f>IF(I9="","Sem medição",IF(H9="","Sem meta",IF(LEFT(G9,5)="Maior",IF(I9&gt;=H9,"Meta atingida","Abaixo da meta"),IF(I9&lt;=H9,"Meta atingida","Acima da meta"))))</f>
+        <v>Abaixo da meta</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -12892,8 +12976,9 @@
           <t xml:space="preserve">IND-009</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="7" t="str">
         <f>IF(C10="","",IF(LEFT(C10,3)="MP-","Macroprocesso",IF(LEFT(C10,3)="SP-","Subprocesso",IF(LEFT(C10,2)="P-","Processo",IF(LEFT(C10,2)="A-","Atividade",IF(LEFT(C10,2)="T-","Tarefa",""))))))</f>
+        <v>Macroprocesso</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -12925,8 +13010,9 @@
           <t xml:space="preserve">120</t>
         </is>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="7" t="str">
         <f>IF(I10="","Sem medição",IF(H10="","Sem meta",IF(LEFT(G10,5)="Maior",IF(I10&gt;=H10,"Meta atingida","Abaixo da meta"),IF(I10&lt;=H10,"Meta atingida","Acima da meta"))))</f>
+        <v>Sem medição</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -16,6 +16,7 @@
     <sheet name="NUGEP" sheetId="12" r:id="rId12"/>
     <sheet name="Glossario" sheetId="13" r:id="rId13"/>
     <sheet name="FAQ" sheetId="14" r:id="rId14"/>
+    <sheet name="Siglas" sheetId="17" r:id="rId18"/>
     <sheet name="Parametros" sheetId="15" r:id="rId15"/>
     <sheet name="Listas" sheetId="16" r:id="rId16"/>
   </sheets>
@@ -702,7 +703,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workshops de modelagem com quem executa; Desenho BPMN no Bizagi (com anexação de evidências); Registro de hipóteses, dores e memória do mapeamento (no processo e-Codevasf/SEI); Identificação de riscos, gargalos e handoffs</t>
+          <t xml:space="preserve">Workshops de modelagem com quem executa; Desenho BPMN no Bizagi (com anexação de evidências); Registro de hipóteses, dores e memória do mapeamento (no processo e-Codevasf/e-Codevasf); Identificação de riscos, gargalos e handoffs</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1054,7 +1055,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponível na intranet/SEI).</t>
+          <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponível na intranet/e-Codevasf).</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1096,7 +1097,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guia prático que detalha etapas, papéis, artefatos e padrões do mapeamento (disponível na intranet/SEI).</t>
+          <t xml:space="preserve">Guia prático que detalha etapas, papéis, artefatos e padrões do mapeamento (disponível na intranet/e-Codevasf).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5252,7 +5253,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use o botão flutuante “Sugerir melhoria de processo” (que abre um e-mail para a UNP) ou procure o dono do processo indicado na ficha. Propostas aceitas abrem um novo ciclo de análise e redesenho, registrado no processo e-Codevasf/SEI correspondente.</t>
+          <t xml:space="preserve">Use o botão flutuante “Sugerir melhoria de processo” (que abre um e-mail para a UNP) ou procure o dono do processo indicado na ficha. Propostas aceitas abrem um novo ciclo de análise e redesenho, registrado no processo e-Codevasf/e-Codevasf correspondente.</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5605,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Na aba Repositório: a jornada de mapeamento, a Metodologia e o Guia de Gerenciamento de Processos (RES 031/2025, na intranet/SEI), os instrumentos por fase do ciclo BPM, os templates e as ferramentas de modelagem.</t>
+          <t xml:space="preserve">Na aba Repositório: a jornada de mapeamento, a Metodologia e o Guia de Gerenciamento de Processos (RES 031/2025, na intranet/e-Codevasf), os instrumentos por fase do ciclo BPM, os templates e as ferramentas de modelagem.</t>
         </is>
       </c>
     </row>
@@ -6513,6 +6514,5074 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF155BCB"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sigla</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/AJ</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/EAG</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Araguaína</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/GB</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/GGR</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/GTR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/SL</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/SR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/AJ</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GB</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GGR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GGR/UOF</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Orçamento e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GGR/UOF/SCO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GGR/URA</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRR</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/SL</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª/SR</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/AJ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/EMO</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Mossoró</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/GB</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/GGR</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/GTR</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/SL</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª/SR</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/AJ</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/EPT</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Patos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/GB</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/GGR</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/GTR</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/SL</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª/SR</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/AJ</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/ETA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Tauá</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/GB</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/GGR</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/GTR</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/SL</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª/SR</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/AJ</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/GB</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/GGR</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/GTR</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/SL</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª/SR</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/AJ</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/EPI</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Piumhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/GB</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/GGR</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/GTR</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Técnica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/SL</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª/SR</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/AJ</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/CIG</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Gorutuba</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/CIM</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Três Marias</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/EAL</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Almenara</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GB</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRA</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRD</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG/UFN/SCB</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRI</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRR</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRS</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/SL</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª/SR</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/AJ</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/CIX</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Xique-Xique</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/EGU</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Guanambi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/EIR</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Irecê</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GB</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRA</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRD</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG/UFN/SCB</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRI</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRR</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRS</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/SL</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/SR</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/UBA</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Descentralizada de Barreiras</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ª/UVC</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Descentralizada de Vitória da Conquista</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/AJ</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/CIB</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Bebedouro</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GB</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRA</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRD</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG/UFN/SCB</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRI</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRR</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRS</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/SL</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª/SR</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/AJ</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/CIT</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Betume</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/EPR</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Propriá</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GB</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRA</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRD</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRG</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRI</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRR</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRS</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/SL</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª/SR</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/AJ</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/CII</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro Integrado de Recursos Pesqueiros e Aquicultura de Itiúba</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/EPE</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Penedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GB</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRA</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRD</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRG</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRI</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRR</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRS</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/SL</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª/SR</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/AJ</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/ESA</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Representação de Salvador</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GB</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRA</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRD</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG/UFN/SCB</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRI</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRR</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRS</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/SL</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/SR</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ª/UPF</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Descentralizada de Paulo Afonso</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/AJ</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/EOE</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Oeiras</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/EPA</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Parnaíba</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/ERN</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de São Raimundo Nonato</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GB</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRA</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRD</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRD/UPS</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Projetos Especiais</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRG</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRI</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRI/UEI</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão dos Empreendimentos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRI/URP</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Apoio à Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRR</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRS</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/SL</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª/SR</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/AJ</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/EIM</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Imperatriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/EPD</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Apoio Técnico de Presidente Dutra</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GB</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GB/URC</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRA</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRA/UGP</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRA/USA</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRA/UTI</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRD</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRD/UPS</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Projetos Especiais</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRG</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRG/UCB</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRG/UFN</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Finanças e Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRG/UMC</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Monitoramento e de Controle de Contratos e Convênios</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRG/URO</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRR</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRS</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Suporte Integrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/GRS/ULF</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Licenciamento Ambiental e Administração Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/SL</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª/SR</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/AJ</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/Cogex</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Gestão Executiva da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GB</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GGR</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GGR/UOF</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Orçamento e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GGR/UOF/SCO</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GGR/URA</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRD</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRD/UEP</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRD/UIP</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Implantação e Acompanhamento de Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRR</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência Regional de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRR/UDT</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/GRR/UES</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Regional de Empreendimentos Socioambientais</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/SL</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Regional de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª/SR</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9ª Superintendência Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Administração e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GGP</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GGP/UBS</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Benefícios e Saúde Ocupacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GGP/UCP</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Cadastro e Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GGP/UDP</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Desenvolvimento de Pessoas</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GGP/URT</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Relações de Trabalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Patrimônio, Logística e Serviços Auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA/SBI</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA/SDP</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setor de Documentação e Protocolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA/UAL</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Administração Predial e Logística</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA/UCS</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Compras Administrativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GPA/UPM</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Patrimônio e Material</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GTI</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GTI/UIT</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Infraestrutura e Tecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GTI/UPC</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Conformidade e Controle de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GTI/USC</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Segurança Cibernética</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GTI/USI</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Sistemas de Informações</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Desenvolvimento e Infraestrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GEP</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Estudos e Projetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GEP/UPE</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Estudos e Projetos de Infraestrutura Urbana e Edificações</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GEP/UPH</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Estudos e Projetos de Infraestrutura Hídrica e Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GIM</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Implantação de Obras</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GIM/UOE</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Implantação de Obras de Infraestrutura Urbana e Edificações</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GIM/UOH</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Implantação de Obras de Infraestrutura Hídrica e Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GPI</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Parcerias e Investimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GQV</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Qualificação Viária</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GQV/UGV</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão e Controle de Projetos de Qualificação Viária</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/GQV/UIO</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Implantação de Obras de Qualificação Viária</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD/SE</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Executiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Estratégia e Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GCB</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Contabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GCB/UCC</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Conformidade Contábil</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GCB/UEC</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Execução Contábil</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GCB/UER</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Escrituração e Revisão Contábil</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GFN</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Finanças</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GFN/UCR</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão da Cobrança</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GFN/UEF</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Programação e Execução Financeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GGO</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GGO/UEO</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Execução Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GGO/UPO</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Programação Orçamentária</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Planejamento Estratégico</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UAT</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Acompanhamento de Transferências</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UNP</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão Normativa e de Processos</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UPL</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Planejamento Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Governança e Sustentabilidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GAF</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Administração Fundiária e Geotecnologia</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GAF/UDF</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Documentação Fundiária</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GAF/UGG</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão Geotecnológica</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GCT</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GCT/UCT</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Custos e Orçamentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GCT/UTR</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Procedimentos Técnicos Referenciais</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GMA</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Meio Ambiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GMA/UCA</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Conservação Ambiental</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GMA/ULA</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Licenciamento Ambiental</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/SE</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Executiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGE</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assembleia Geral</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Irrigação e Operações</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GAP</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Apoio à Produção Irrigada</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GAP/UGI</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão de Áreas Irrigadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GAP/UPI</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Apoio aos Projetos Públicos de Irrigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GEE</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Eficiência Energética</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GEE/UEE</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão de Energia e Apoio ao PISF</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GEE/USB</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão e Segurança de Barragens</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GGE</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Gestão de Empreendimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GGE/UGM</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão e Monitoramento de Empreendimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GGE/UOR</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Operação e Reabilitação de Empreendimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/SE</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Executiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Revitalização e Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Desenvolvimento Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT/UAP</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Desenvolvimento dos Arranjos Produtivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT/UPA</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Recursos Pesqueiros, Aquicultura e Beneficiamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GMT</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Mecanização e Modernização Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GMT/UCM</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Gestão e Controle da Modernização Territorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GMT/UME</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Aquisição de Máquinas e Equipamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GSA</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerência de Saneamento e Acesso à Água</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GSA/UAS</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Água e Saneamento Básico</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GSA/UEA</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Esgotamento Rural e Acesso a Água</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/SE</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria Executiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEC</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comissão de Ética da Codevasf</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coaud</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Auditoria Estatutário</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cogid</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Governança Interna e Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cogid/SPDP</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subcomitê de Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cogid/SSI</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subcomitê de Segurança da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cogid/STIC</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subcomitê de Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confis</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conselho Fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conselho de Administração</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/AUD</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auditoria Interna</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/AUD/UGE</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Acompanhamento e Avaliação da Gestão</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/AUD/UIN</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Apoio e Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/AUD/UPR</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Acompanhamento e Avaliação de Programas</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/COR</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corregedoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/COR/UIV</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Admissibilidade e Investigação</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/COR/UPJ</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Processos Acusatórios e Julgamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consad/OUV</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouvidoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copes</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comitê de Pessoas, Elegibilidade, Sucessão e Remuneração</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEX</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diretoria Executiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presidência</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AC</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria de Comunicação</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AC/UCE</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Cerimonial e Eventos</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AC/UIM</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Imagem e Promoção Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AJ</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AJ/UAA</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade de Assuntos Administrativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/AJ/UCO</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade do Contencioso</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/EBE</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escritório de Representação de Belém</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/GB</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabinete da Presidência</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SC</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria de Órgãos Colegiados</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SI</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria de Integridade</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SLC</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria de Licitações e Contratos</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SLC/UGC</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Gestão de Contratos</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SLC/UGL</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Gestão de Licitações</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SRC</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secretaria de Gestão de Riscos e Controle Interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR/SRC/UGR</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade Especial de Gerenciamento de Riscos Corporativos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
@@ -6678,7 +11747,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; SEI; Painéis de BI</t>
+          <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -6750,7 +11819,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; Sistema de gestão de riscos</t>
+          <t xml:space="preserve">e-Codevasf; Sistema de gestão de riscos</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -6822,7 +11891,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TransfereGov; SEI</t>
+          <t xml:space="preserve">TransfereGov; e-Codevasf</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -6894,7 +11963,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIG-Irrigação (fictício); SEI</t>
+          <t xml:space="preserve">SIG-Irrigação (fictício); e-Codevasf</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6966,7 +12035,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; GeoPortal (fictício)</t>
+          <t xml:space="preserve">e-Codevasf; GeoPortal (fictício)</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -7038,7 +12107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras.gov.br; PNCP; Painel de Preços; SEI</t>
+          <t xml:space="preserve">Compras.gov.br; PNCP; Painel de Preços; e-Codevasf</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7115,7 +12184,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIGEP (fictício); SEI</t>
+          <t xml:space="preserve">SIGEP (fictício); e-Codevasf</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -7371,7 +12440,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo_SEI</t>
+          <t xml:space="preserve">Processo_ECodevasf</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -7551,7 +12620,7 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; Compras.gov.br; Painel de Preços</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
@@ -7726,7 +12795,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras.gov.br; PNCP; SEI</t>
+          <t xml:space="preserve">Compras.gov.br; PNCP; e-Codevasf</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -7901,7 +12970,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; Compras.gov.br</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
@@ -8071,7 +13140,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIG-Irrigação (fictício); SEI</t>
+          <t xml:space="preserve">SIG-Irrigação (fictício); e-Codevasf</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -8236,7 +13305,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; GeoPortal (fictício)</t>
+          <t xml:space="preserve">e-Codevasf; GeoPortal (fictício)</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -8571,7 +13640,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIGEP (fictício); SEI</t>
+          <t xml:space="preserve">SIGEP (fictício); e-Codevasf</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
@@ -8709,6 +13778,8 @@
     <col min="11" max="11" width="28" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8777,6 +13848,16 @@
           <t xml:space="preserve">Unidades_Corresponsaveis</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reutilizavel</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reutilizado_Em</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -8826,12 +13907,12 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado no SEI</t>
+          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; Compras.gov.br</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -8893,7 +13974,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -8955,7 +14036,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Painel de Preços; PNCP; SEI</t>
+          <t xml:space="preserve">Painel de Preços; PNCP; e-Codevasf</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -9017,12 +14098,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planilha padrão; SEI</t>
+          <t xml:space="preserve">Planilha padrão; e-Codevasf</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P-06.02; P-04.01</t>
         </is>
       </c>
     </row>
@@ -9151,7 +14242,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:O1"/>
 </worksheet>
 </file>
 
@@ -9171,12 +14262,11 @@
     <col min="7" max="7" width="38" customWidth="1"/>
     <col min="8" max="8" width="38" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="44" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="30" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -9227,30 +14317,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prazo_Padrao</t>
+          <t xml:space="preserve">Base_Normativa</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base_Normativa</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Executor</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Executor</t>
+          <t xml:space="preserve">Unidades_Corresponsaveis</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidades_Corresponsaveis</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo</t>
         </is>
@@ -9294,40 +14379,35 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD assinado no SEI</t>
+          <t xml:space="preserve">DFD assinado no e-Codevasf</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 dias úteis</t>
+          <t xml:space="preserve">NI-027/2024 (fictícia)</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NI-027/2024 (fictícia)</t>
+          <t xml:space="preserve">https://placehold.co/960x420/155bcb/ffffff?text=Diagrama+BPMN+A-06.01.01.01</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://placehold.co/960x420/155bcb/ffffff?text=Diagrama+BPMN+A-06.01.01.01</t>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR/GRB</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Registrar formalmente a necessidade da contratação, alinhada ao Plano de Contratações Anual.</t>
         </is>
@@ -9381,25 +14461,20 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 dias úteis</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021, art. 18</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AA/GLC</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Identificar a solução mais adequada para atender à necessidade, considerando alternativas de mercado.</t>
         </is>
@@ -9448,30 +14523,25 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 dias úteis</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">A definir</t>
         </is>
       </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AG/GGP</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Dimensionar com precisão os quantitativos e os resultados esperados da contratação.</t>
         </is>
@@ -9520,30 +14590,25 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI; Compras.gov.br</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 dias úteis</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021, art. 18</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT/GTI</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consolidar e submeter o Estudo Técnico Preliminar à aprovação da autoridade competente.</t>
         </is>
@@ -9592,30 +14657,25 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 dias úteis</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021, art. 6º, XXIII</t>
         </is>
       </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AE/GPE</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Traduzir o ETP aprovado em um Termo de Referência claro e completo.</t>
         </is>
@@ -9664,30 +14724,25 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 dias úteis</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021, art. 53</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AE/GAG</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Assegurar a conformidade jurídica do Termo de Referência antes da publicação.</t>
         </is>
@@ -9741,25 +14796,20 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 dias úteis</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">IN SEGES nº 65/2021</t>
         </is>
       </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AR/GDT</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR/GDT</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Levantar parâmetros de preço confiáveis em fontes oficiais admitidas.</t>
         </is>
@@ -9808,30 +14858,25 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 dias úteis</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">IN SEGES nº 65/2021, art. 6º</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI/GOM</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Definir e justificar o valor estimado final da contratação.</t>
         </is>
@@ -9885,25 +14930,20 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 dia útil</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">IN SEGES nº 65/2021, art. 6º, §3º</t>
         </is>
       </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR/GRB</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Evitar que preços inexequíveis ou excessivos distorçam a estimativa de valor.</t>
         </is>
@@ -9957,25 +14997,20 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 dias úteis</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021, art. 54</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AA/GLC</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Dar publicidade ao certame, observando os prazos legais mínimos.</t>
         </is>
@@ -10029,25 +15064,20 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conforme edital</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">Lei nº 14.133/2021</t>
         </is>
       </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AG/GGP</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Selecionar a proposta mais vantajosa com transparência e celeridade.</t>
         </is>
@@ -10101,25 +15131,20 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semanal</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">A definir</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistente em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AT/GTI</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Equilibrar a demanda dos lotes com a disponibilidade hídrica do perímetro.</t>
         </is>
@@ -10173,32 +15198,27 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diário</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">A definir</t>
         </is>
       </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista em Desenvolvimento Regional</t>
+          <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AE/GPE</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">Executar a distribuição programada e manter o registro confiável dos volumes entregues.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:N1"/>
 </worksheet>
 </file>
 
@@ -10284,11 +15304,6 @@
           <t xml:space="preserve">Unidades_Corresponsaveis</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Objetivo</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -10328,22 +15343,15 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+          <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="I2" s="3">
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AA/GLC</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coletar, junto ao gestor da área, os elementos necessários para justificar a demanda.</t>
         </is>
       </c>
     </row>
@@ -10365,7 +15373,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preencher o formulário DFD no SEI</t>
+          <t xml:space="preserve">Preencher o formulário DFD no e-Codevasf</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -10385,13 +15393,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+          <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="I3" s="2">
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -10401,11 +15407,6 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AG/GGP</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Registrar formalmente a demanda no modelo padronizado do DFD.</t>
         </is>
       </c>
     </row>
@@ -10447,22 +15448,15 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 dia</t>
-        </is>
+          <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="I4" s="3">
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AT/GTI</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Validar formalmente o DFD perante a autoridade competente da unidade.</t>
         </is>
       </c>
     </row>
@@ -10507,19 +15501,12 @@
           <t xml:space="preserve">Painel de Preços</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+      <c r="I5" s="2">
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GPE</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obter parâmetros de preço de contratações públicas similares.</t>
         </is>
       </c>
     </row>
@@ -10564,19 +15551,12 @@
           <t xml:space="preserve">PNCP</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+      <c r="I6" s="3">
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GAG</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirmar preços praticados em contratos vigentes de objeto equivalente.</t>
         </is>
       </c>
     </row>
@@ -10618,13 +15598,11 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 dias</t>
-        </is>
+          <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="I7" s="2">
+        <v>24</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -10634,11 +15612,6 @@
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AR/GDT</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Complementar a amostra de preços quando as fontes oficiais forem insuficientes.</t>
         </is>
       </c>
     </row>
@@ -10683,19 +15656,12 @@
           <t xml:space="preserve">Planilha padrão</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+      <c r="I8" s="3">
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AI/GOM</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chegar a um valor de referência estatisticamente consistente.</t>
         </is>
       </c>
     </row>
@@ -10740,19 +15706,12 @@
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,5 dia</t>
-        </is>
+      <c r="I9" s="2">
+        <v>4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AR/GRB</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disponibilizar o edital e seus anexos no sistema de compras.</t>
         </is>
       </c>
     </row>
@@ -10797,19 +15756,12 @@
           <t xml:space="preserve">PNCP</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Imediato</t>
-        </is>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AA/GLC</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garantir a publicidade nacional do aviso de licitação.</t>
         </is>
       </c>
     </row>
@@ -10854,24 +15806,17 @@
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 dia</t>
-        </is>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reunir os pedidos de água por setor hidráulico antes da programação.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:L1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Valor fora da lista" error="Escolha uma das opções da seta ao lado da célula. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="F2:F300">
       <formula1>Listas!$H$2:$H$4</formula1>
@@ -11146,7 +16091,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI 59500.000123/2026-11.</t>
+          <t xml:space="preserve">e-Codevasf 59500.000123/2026-11.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +16439,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passo a passo do DFD no SEI</t>
+          <t xml:space="preserve">Passo a passo do DFD no e-Codevasf</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -11944,7 +16889,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Designação formal de fiscais, agenda de medições e alertas no SEI.</t>
+          <t xml:space="preserve">Designação formal de fiscais, agenda de medições e alertas no e-Codevasf.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -12328,7 +17273,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficinas de capacitação e modelo simplificado de DFD no SEI.</t>
+          <t xml:space="preserve">Oficinas de capacitação e modelo simplificado de DFD no e-Codevasf.</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -12571,7 +17516,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -12701,7 +17646,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -12961,7 +17906,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEI</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -55,19 +55,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0040B4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F8FC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,7 +136,7 @@
   <sheetPr>
     <tabColor rgb="FF0C326F"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
@@ -160,156 +157,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que é este arquivo</t>
+          <t xml:space="preserve">Sobre</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte única de dados do Painel de Processos da Codevasf, publicado no GitHub Pages. Todos os nomes, números, normativos internos e resultados são FICTÍCIOS — criados só para demonstrar o painel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Como o painel lê esta planilha</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O site busca este arquivo direto no navegador (SheetJS). Se não conseguir (aberto sem servidor, por exemplo), usa o fallback embutido em js/dados.js, gerado por scripts/planilha_para_js.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dicionário de dados</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Veja a aba Dicionario: toda coluna de toda aba, o que ela significa e um exemplo real já preenchido — comece por ali antes de editar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hierarquia e códigos</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Macroprocesso (MG-/MF-/MS- por tipo: Gerencial/Finalístico/Suporte) → Processo (PP-) → Subprocesso (SP-) → Atividade (AT-) → Tarefa (TR-). Os códigos são sequenciais dentro do próprio nível; quem liga um item ao outro são as colunas Macroprocesso/Vinculo_Pai/Atividade — não o texto do código.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Processo sem subprocesso</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quando um processo não tem subprocessos, ligue as atividades direto a ele: Atividades.Vinculo_Pai = o código do PROCESSO (PP-...), em vez de um subprocesso (SP-...). Exemplo real neste arquivo: PP-03, com as atividades AT-14 e AT-15 ligadas direto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Subprocesso dentro de subprocesso</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um subprocesso pode ser filho de outro subprocesso: Subprocessos.Vinculo_Pai aceita tanto um código de Processo (PP-) quanto de outro Subprocesso (SP-). Exemplo real: SP-04, cujo Vinculo_Pai é SP-03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Documentos, Riscos, Métricas, Papéis e Regras</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essas abas se vinculam a QUALQUER nível da hierarquia pelo par Vinculo_Nivel (calculado) + Vinculo_Codigo (você preenche, com o código de um Macroprocesso, Processo, Subprocesso, Atividade ou Tarefa). Aceitam mais de um código separado por ; quando o mesmo registro vale para vários itens do mesmo nível.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normativos e legislação</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não existe mais uma coluna de texto livre para "normativos aplicáveis": cada normativo (interno ou uma lei externa) vira uma linha própria na aba Documentos, com Link para o texto oficial — é isso que faz o painel mostrar um link clicável de verdade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Listas suspensas</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toda coluna com um conjunto fechado de respostas tem lista suspensa. As opções ficam na aba Listas (e os códigos de Macroprocessos/Processos/Subprocessos/Atividades/Siglas vêm direto das abas correspondentes) — para criar um código novo, cadastre-o primeiro na aba de origem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colunas cinzas</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fundo cinza = calculada por fórmula (Vinculo_Nivel, Processos.Percentual, Riscos.Nivel_PxI/Classificacao, NUGEP.Unidade_Nome). Não digite nelas — ao inserir uma linha, copie a fórmula da linha de cima.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Datas</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Formato dd/mm/aaaa, em todas as abas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Listas dentro da célula</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Separe múltiplos itens com ponto e vírgula — ex.: "e-Codevasf; Compras.gov.br; PNCP".</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preparação para virar banco de dados</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cada Codigo/ID é uma chave de negócio única dentro do seu nível; os vínculos entre abas (Macroprocesso, Vinculo_Pai, Atividade, Vinculo_Nivel+Vinculo_Codigo) já funcionam como chaves estrangeiras. Isso é o que permite migrar cada aba para uma tabela SQL no futuro sem redesenhar a estrutura.</t>
+          <t xml:space="preserve">Fonte única de dados do Painel de Processos, dados fictícios. Ver aba Dicionario.</t>
         </is>
       </c>
     </row>
@@ -1007,10 +860,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
-      <formula1>Listas!$X$2:$X$50</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="H2:H300">
       <formula1>Listas!$Q$2:$Q$3</formula1>
     </dataValidation>
@@ -1794,10 +1644,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
-      <formula1>Listas!$X$2:$X$50</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
       <formula1>Listas!$O$2:$O$5</formula1>
     </dataValidation>
@@ -2004,10 +1851,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
-      <formula1>Listas!$X$2:$X$50</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
       <formula1>Listas!$P$2:$P$5</formula1>
     </dataValidation>
@@ -2391,12 +2235,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
       <formula1>Listas!$T$2:$T$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="F2:F300">
-      <formula1>"PP-01,PP-02,PP-03,PP-04,PP-05,PP-06,PP-07"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -4279,7 +4120,7 @@
   <sheetPr>
     <tabColor rgb="FF0C326F"/>
   </sheetPr>
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D231"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -4322,7 +4163,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único do macroprocesso — MG-nn (Gerencial), MF-nn (Finalístico) ou MS-nn (Suporte), numerado dentro de cada tipo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -4344,7 +4185,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -4366,7 +4207,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo na cadeia de valor: Gerencial (direciona e controla), Finalístico (entrega valor à sociedade) ou Suporte (habilita os demais).</t>
+          <t xml:space="preserve">Classificação, lista fechada.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -4388,7 +4229,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
+          <t xml:space="preserve">Posição de exibição.</t>
         </is>
       </c>
       <c r="D5" s="3">
@@ -4408,7 +4249,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla da unidade orgânica dona do item — lista suspensa a partir da aba Siglas.</t>
+          <t xml:space="preserve">Sigla — lista suspensa a partir da aba Siglas.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -4430,7 +4271,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas das unidades que também respondem pelo item, separadas por ; . A validação apenas avisa (não bloqueia): o campo aceita mais de uma sigla.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -4452,7 +4293,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Explicação livre.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4474,7 +4315,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para que o item existe — o resultado que busca entregar.</t>
+          <t xml:space="preserve">Resultado que busca entregar.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -4496,7 +4337,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produtos e serviços que o macroprocesso entrega.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4518,7 +4359,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem recebe as entregas do macroprocesso.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -4540,7 +4381,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem tem interesse ou influência sobre o macroprocesso, além dos beneficiários diretos.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4562,7 +4403,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas usados na execução, separados por ; quando houver mais de um.</t>
+          <t xml:space="preserve">Separados por ; .</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -4584,12 +4425,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL da publicação web do diagrama (Bizagi Modeler → Publish → Web). Em branco, o painel avisa que o diagrama não foi publicado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ainda sem exemplo preenchido)</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4447,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">Nota livre.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -4618,22 +4459,22 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processos</t>
+          <t xml:space="preserve">Macroprocessos</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único do processo — PP-nn, sequencial (a hierarquia com o macroprocesso vem da coluna Macroprocesso, não do código).</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">MG-01</t>
         </is>
       </c>
     </row>
@@ -4645,17 +4486,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planejamento da Contratação</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -4667,17 +4508,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do macroprocesso ao qual este processo pertence — lista suspensa a partir da aba Macroprocessos.</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">Planejamento da Contratação</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4530,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Da identificação da necessidade (DFD) até a aprovação do ETP, TR e pesquisa de preços que instrue...</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -4711,17 +4552,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para que o item existe — o resultado que busca entregar.</t>
+          <t xml:space="preserve">Explicação livre.</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instruir as contratações com estudos e artefatos completos, reduzindo retrabalho e impugnações.</t>
+          <t xml:space="preserve">Da identificação da necessidade (DFD) até a aprovação do ETP, TR e pesquisa de preços que instrue...</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4574,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla da unidade orgânica dona do item — lista suspensa a partir da aba Siglas.</t>
+          <t xml:space="preserve">Resultado que busca entregar.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC</t>
+          <t xml:space="preserve">Instruir as contratações com estudos e artefatos completos, reduzindo retrabalho e impugnações.</t>
         </is>
       </c>
     </row>
@@ -4755,17 +4596,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ponto_Focal_Nugep</t>
+          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empregado que conduz e coordena o gerenciamento deste processo na própria unidade orgânica (RES 031/2025, item 3.5).</t>
+          <t xml:space="preserve">Sigla — lista suspensa a partir da aba Siglas.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4618,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+          <t xml:space="preserve">Ponto_Focal_Nugep</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas das unidades que também respondem pelo item, separadas por ; . A validação apenas avisa (não bloqueia): o campo aceita mais de uma sigla.</t>
+          <t xml:space="preserve">Lista suspensa a partir dos nomes da aba NUGEP.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AE/GAG; AR/GDT</t>
+          <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4640,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prioridade</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -4809,7 +4650,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alta</t>
+          <t xml:space="preserve">AE/GAG; AR/GDT</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4662,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complexidade</t>
+          <t xml:space="preserve">Prioridade</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4843,17 +4684,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maturidade</t>
+          <t xml:space="preserve">Complexidade</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estágio de maturidade da GESTÃO deste processo (escala CMM/PEMM): Inicial, Repetível, Definido, Gerenciado ou Otimizado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definido</t>
+          <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
@@ -4865,17 +4706,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status_Mapeamento</t>
+          <t xml:space="preserve">Maturidade</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estágio do TRABALHO DE MAPEAMENTO — diferente de Maturidade, que mede a gestão do processo já mapeado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concluído</t>
+          <t xml:space="preserve">Definido</t>
         </is>
       </c>
     </row>
@@ -4887,16 +4728,18 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Percentual</t>
+          <t xml:space="preserve">Status_Mapeamento</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Percentual de marcos (M1–M10) concluídos, ignorando os marcados "Não se aplica".</t>
-        </is>
-      </c>
-      <c r="D28" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concluído</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4907,7 +4750,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inicio_Mapeamento</t>
+          <t xml:space="preserve">Percentual</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4915,10 +4758,8 @@
           <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05/01/2026</t>
-        </is>
+      <c r="D29" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4929,7 +4770,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prazo_Previsto</t>
+          <t xml:space="preserve">Inicio_Mapeamento</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -4939,7 +4780,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/05/2026</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4792,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data_Conclusao</t>
+          <t xml:space="preserve">Prazo_Previsto</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4961,7 +4802,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/05/2026</t>
+          <t xml:space="preserve">29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4973,17 +4814,17 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultima_Atualizacao</t>
+          <t xml:space="preserve">Data_Conclusao</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data da última revisão de qualquer informação desta ficha.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/07/2026</t>
+          <t xml:space="preserve">18/05/2026</t>
         </is>
       </c>
     </row>
@@ -4995,17 +4836,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M1_Conhecer_Processo</t>
+          <t xml:space="preserve">Ultima_Atualizacao</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 1 do mapeamento (Sim/Não/Não se aplica). Primeira reunião com a área para conhecer o processo: apresentar a metodologia, entender o contexto e coletar o formulário de levantamento.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim</t>
+          <t xml:space="preserve">10/07/2026</t>
         </is>
       </c>
     </row>
@@ -5017,12 +4858,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M2_Processo_Modelado</t>
+          <t xml:space="preserve">M1_Conhecer_Processo</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 2 do mapeamento (Sim/Não/Não se aplica). Oficinas de modelagem do macroprocesso e do processo em BPMN, com a equipe de mapeamento e a área.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5039,12 +4880,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3_Subprocessos_Modelados</t>
+          <t xml:space="preserve">M2_Processo_Modelado</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 3 do mapeamento (Sim/Não/Não se aplica). Oficinas de modelagem dos subprocessos — pode aprofundar vários níveis. Marque "Não se aplica" se o processo não tiver subprocessos.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -5061,12 +4902,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4_ASIS_Modelado</t>
+          <t xml:space="preserve">M3_Subprocessos_Modelados</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 4 do mapeamento (Sim/Não/Não se aplica). O conjunto de diagramas AS-IS (macroprocesso, processo, subprocessos e atividades) está consolidado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5083,12 +4924,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M5_ASIS_Validado</t>
+          <t xml:space="preserve">M4_ASIS_Modelado</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 5 do mapeamento (Sim/Não/Não se aplica). O dono do processo validou formalmente o AS-IS como retrato da realidade atual.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5105,12 +4946,12 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6_Procedimento_Aprovado</t>
+          <t xml:space="preserve">M5_ASIS_Validado</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 6 do mapeamento (Sim/Não/Não se aplica). O procedimento (PRO) foi aprovado pela Diretoria Executiva (DEX).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -5127,12 +4968,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M7_Processo_Publicado</t>
+          <t xml:space="preserve">M6_Procedimento_Aprovado</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 7 do mapeamento (Sim/Não/Não se aplica). O processo, os diagramas e o PRO foram publicados no repositório institucional.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5149,12 +4990,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M8_TOBE_Elaborado</t>
+          <t xml:space="preserve">M7_Processo_Publicado</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 8 do mapeamento (Sim/Não/Não se aplica). O redesenho (TO-BE) foi elaborado, com melhorias, riscos residuais e indicadores propostos.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5171,12 +5012,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M9_TOBE_Aprovado</t>
+          <t xml:space="preserve">M8_TOBE_Elaborado</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 9 do mapeamento (Sim/Não/Não se aplica). O dono do processo validou o TO-BE, aprovado pela Diretoria Executiva (DEX).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5193,12 +5034,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M10_Processo_Transformado</t>
+          <t xml:space="preserve">M9_TOBE_Aprovado</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marco 10 do mapeamento (Sim/Não/Não se aplica). O redesenho aprovado foi implantado: o processo passou a ser executado na forma TO-BE.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -5215,17 +5056,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fornecedores</t>
+          <t xml:space="preserve">M10_Processo_Transformado</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem fornece as entradas do processo (SIPOC).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Áreas demandantes; Painel de Preços; Fornecedores (cotações)</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
@@ -5237,17 +5078,17 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Fornecedores</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que é necessário para executar o item. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD; Plano de Contratações Anual; Requisitos da área</t>
+          <t xml:space="preserve">Áreas demandantes; Painel de Preços; Fornecedores (cotações)</t>
         </is>
       </c>
     </row>
@@ -5259,17 +5100,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que o item produz ou entrega. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado; TR aprovado; Pesquisa de preços validada</t>
+          <t xml:space="preserve">DFD; Plano de Contratações Anual; Requisitos da área</t>
         </is>
       </c>
     </row>
@@ -5281,17 +5122,17 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beneficiarios</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem recebe as saídas do processo (SIPOC).</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC (Seleção do Fornecedor); Assessoria Jurídica</t>
+          <t xml:space="preserve">ETP aprovado; TR aprovado; Pesquisa de preços validada</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5144,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Beneficiarios</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas usados na execução, separados por ; quando houver mais de um.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
+          <t xml:space="preserve">AA/GLC (Seleção do Fornecedor); Assessoria Jurídica</t>
         </is>
       </c>
     </row>
@@ -5325,17 +5166,17 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo_ECodevasf</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número do processo administrativo no e-Codevasf (SEI) que instrui este trabalho.</t>
+          <t xml:space="preserve">Separados por ; .</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">59500.000123/2026-11</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
         </is>
       </c>
     </row>
@@ -5347,17 +5188,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Processo_ECodevasf</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL da publicação web do diagrama (Bizagi Modeler → Publish → Web). Em branco, o painel avisa que o diagrama não foi publicado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://fluxosti.codevasf.gov.br/incidentes/</t>
+          <t xml:space="preserve">59500.000123/2026-11</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5210,17 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias_Necessarias</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Habilidades e conhecimentos de RH necessários para EXECUTAR o processo (Guia de Modelagem, Anexo C) — diferente da aba Competencias (atribuições de governança).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração de estudos técnicos e termos de referência; Conhecimento da Lei nº 14.133/2021; Pesqui...</t>
+          <t xml:space="preserve">https://fluxosti.codevasf.gov.br/incidentes/</t>
         </is>
       </c>
     </row>
@@ -5391,17 +5232,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontes_Dados</t>
+          <t xml:space="preserve">Competencias_Necessarias</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas ou bases de onde vêm os dados usados para medir e acompanhar este processo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Painel de Preços; PNCP</t>
+          <t xml:space="preserve">Elaboração de estudos técnicos e termos de referência; Conhecimento da Lei nº 14.133/2021; Pesqui...</t>
         </is>
       </c>
     </row>
@@ -5413,17 +5254,17 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proxima_Acao</t>
+          <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Próximo passo previsto no gerenciamento deste processo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
+          <t xml:space="preserve">e-Codevasf; Painel de Preços; PNCP</t>
         </is>
       </c>
     </row>
@@ -5435,61 +5276,61 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendencia</t>
+          <t xml:space="preserve">Proxima_Acao</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que está travando o avanço, se houver.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
+          <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Pendencia</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único do subprocesso — SP-nn, sequencial.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">CALCULADA — não digite. Ex.: "MS-01 › PP-01".</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estudo Técnico Preliminar (ETP)</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5342,17 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Pai</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do processo (PP-) ou de outro subprocesso (SP-) do qual este é filho — lista suspensa combinando as duas abas. Um subprocesso pode conter outro, quantos níveis o processo exigir.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
@@ -5523,16 +5364,18 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D57" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Nome do item.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estudo Técnico Preliminar (ETP)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -5543,17 +5386,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Vinculo_Pai</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caracterização da necessidade, análise de soluções de mercado e demonstração da viabilidade da co...</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -5565,18 +5408,16 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para que o item existe — o resultado que busca entregar.</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fundamentar tecnicamente a melhor solução para a necessidade.</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5587,17 +5428,17 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla da unidade orgânica dona do item — lista suspensa a partir da aba Siglas.</t>
+          <t xml:space="preserve">Explicação livre.</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC</t>
+          <t xml:space="preserve">Caracterização da necessidade, análise de soluções de mercado e demonstração da viabilidade da co...</t>
         </is>
       </c>
     </row>
@@ -5609,17 +5450,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas das unidades que também respondem pelo item, separadas por ; . A validação apenas avisa (não bloqueia): o campo aceita mais de uma sigla.</t>
+          <t xml:space="preserve">Resultado que busca entregar.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI/GOM</t>
+          <t xml:space="preserve">Fundamentar tecnicamente a melhor solução para a necessidade.</t>
         </is>
       </c>
     </row>
@@ -5631,17 +5472,17 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reutilizavel</t>
+          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Sim" quando este subprocesso é chamado, de verdade, a partir de mais de um processo/subprocesso (Subprocesso Reutilizável do BPMN).</t>
+          <t xml:space="preserve">Sigla — lista suspensa a partir da aba Siglas.</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -5653,17 +5494,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reutilizado_Em</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Códigos dos OUTROS processos/subprocessos que também chamam este subprocesso, além do que está em Vinculo_Pai. Preencha só quando Reutilizavel = Sim.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-02; PP-04</t>
+          <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
     </row>
@@ -5675,17 +5516,17 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produto_Principal</t>
+          <t xml:space="preserve">Reutilizavel</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Principal produto ou resultado que este subprocesso entrega (Guia de Modelagem, Anexo B).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estudo Técnico Preliminar (ETP) aprovado</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
@@ -5697,17 +5538,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Reutilizado_Em</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que é necessário para executar o item. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
+          <t xml:space="preserve">PP-02; PP-04</t>
         </is>
       </c>
     </row>
@@ -5719,17 +5560,17 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que o item produz ou entrega. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
+          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
         </is>
       </c>
     </row>
@@ -5741,17 +5582,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas usados na execução, separados por ; quando houver mais de um.</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
+          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5604,17 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontes_Dados</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre.</t>
+          <t xml:space="preserve">Separados por ; .</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
     </row>
@@ -5785,61 +5626,61 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL da publicação web do diagrama (Bizagi Modeler → Publish → Web). Em branco, o painel avisa que o diagrama não foi publicado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ainda sem exemplo preenchido)</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único da atividade — AT-nn, sequencial.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AT-01</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formalizar a necessidade (DFD)</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01</t>
         </is>
       </c>
     </row>
@@ -5851,17 +5692,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Pai</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do subprocesso (SP-) do qual a atividade faz parte OU, quando o processo não tem subprocessos, o código do processo (PP-) direto.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">AT-01</t>
         </is>
       </c>
     </row>
@@ -5873,16 +5714,18 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D73" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Nome do item.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formalizar a necessidade (DFD)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5893,17 +5736,17 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Atividade</t>
+          <t xml:space="preserve">Vinculo_Pai</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação CBOK 3.1.7: Agregação de Valor (transforma algo para o beneficiário), Transferência (handoff entre áreas/sistemas) ou Controle (verificação/aprovação).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agregação de Valor</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
@@ -5915,18 +5758,16 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A área demandante registra a necessidade de contratação no Documento de Formalização da Demanda (...</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D75" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5937,17 +5778,17 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Tipo_Atividade</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que é necessário para executar o item. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Necessidade identificada; Plano de Contratações Anual</t>
+          <t xml:space="preserve">Agregação de Valor</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5800,17 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que o item produz ou entrega. Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Explicação livre.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD assinado no e-Codevasf</t>
+          <t xml:space="preserve">A área demandante registra a necessidade de contratação no Documento de Formalização da Demanda (...</t>
         </is>
       </c>
     </row>
@@ -5981,83 +5822,83 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas usados na execução, separados por ; quando houver mais de um.</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf</t>
+          <t xml:space="preserve">Necessidade identificada; Plano de Contratações Anual</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único da tarefa — TR-nn, sequencial.</t>
+          <t xml:space="preserve">Separe com ; quando houver mais de um.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR-01</t>
+          <t xml:space="preserve">DFD assinado no e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">Separados por ; .</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reunir informações da demanda</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividade</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código da atividade à qual esta tarefa pertence — lista suspensa a partir da aba Atividades.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AT-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
         </is>
       </c>
     </row>
@@ -6069,16 +5910,18 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D82" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TR-01</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -6089,17 +5932,17 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Tarefa</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual (pessoa), Automatizada (sistema) ou Regra de negócio (decisão aplicando critérios).</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual</t>
+          <t xml:space="preserve">Reunir informações da demanda</t>
         </is>
       </c>
     </row>
@@ -6111,17 +5954,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disparador</t>
+          <t xml:space="preserve">Atividade</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que dá início a esta tarefa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área demandante identifica necessidade de contratação</t>
+          <t xml:space="preserve">AT-01</t>
         </is>
       </c>
     </row>
@@ -6133,18 +5976,16 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passos</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sequência de passos para executar a tarefa, separados por ; — o painel exibe como lista numerada.</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Levantar justificativa da necessidade; Consultar o PCA vigente; Reunir quantitativos preliminares...</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D85" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -6155,17 +5996,17 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Principios</t>
+          <t xml:space="preserve">Tipo_Tarefa</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diretrizes a observar durante a execução, separadas por ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transparência; Economicidade</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
     </row>
@@ -6177,17 +6018,17 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criterios_Desempenho</t>
+          <t xml:space="preserve">Disparador</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Como saber se a tarefa foi bem executada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Informações completas e alinhadas ao PCA; prazo de até 3 dias úteis</t>
+          <t xml:space="preserve">Área demandante identifica necessidade de contratação</t>
         </is>
       </c>
     </row>
@@ -6199,17 +6040,17 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resultados_Esperados</t>
+          <t xml:space="preserve">Passos</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que deve existir depois da tarefa concluída.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justificativa e quantitativos preliminares documentados</t>
+          <t xml:space="preserve">Levantar justificativa da necessidade; Consultar o PCA vigente; Reunir quantitativos preliminares...</t>
         </is>
       </c>
     </row>
@@ -6221,17 +6062,17 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materiais_Ferramentas</t>
+          <t xml:space="preserve">Principios</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas, modelos ou materiais usados para executar a tarefa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Modelo de DFD</t>
+          <t xml:space="preserve">Transparência; Economicidade</t>
         </is>
       </c>
     </row>
@@ -6243,17 +6084,17 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pessoas_Consultar</t>
+          <t xml:space="preserve">Criterios_Desempenho</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem pode ser consultado em caso de dúvida.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestor da área demandante; Coordenador de orçamento</t>
+          <t xml:space="preserve">Informações completas e alinhadas ao PCA; prazo de até 3 dias úteis</t>
         </is>
       </c>
     </row>
@@ -6265,16 +6106,18 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duracao_Estimada</t>
+          <t xml:space="preserve">Resultados_Esperados</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duração em horas úteis (1 dia útil = 8h) — a partir daqui o painel soma a duração de atividades, subprocessos e processos.</t>
-        </is>
-      </c>
-      <c r="D91" s="3">
-        <v>4</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justificativa e quantitativos preliminares documentados</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -6285,17 +6128,17 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Materiais_Ferramentas</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelo DOC-006/DOC-012.</t>
+          <t xml:space="preserve">e-Codevasf; Modelo de DFD</t>
         </is>
       </c>
     </row>
@@ -6307,105 +6150,103 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+          <t xml:space="preserve">Pessoas_Consultar</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas das unidades que também respondem pelo item, separadas por ; . A validação apenas avisa (não bloqueia): o campo aceita mais de uma sigla.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC</t>
+          <t xml:space="preserve">Gestor da área demandante; Coordenador de orçamento</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Duracao_Estimada</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — DOC-nnn.</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOC-001</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D94" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titulo</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Título de exibição do item.</t>
+          <t xml:space="preserve">Nota livre.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRO 06.01 — Planejamento da Contratação</t>
+          <t xml:space="preserve">Modelo DOC-006/DOC-012.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Documento</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Natureza do documento.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimento (PRO)</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Mostra a que nível (Macroprocesso/Processo/Subprocesso/Atividade/Tarefa) este registro pertence, lido do prefixo de Vinculo_Codigo.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01 › TR-01</t>
         </is>
       </c>
     </row>
@@ -6417,17 +6258,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do item ao qual este registro se vincula, de qualquer nível da hierarquia. Aceita mais de um código separado por ; quando valem para vários itens do mesmo nível.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">DOC-001</t>
         </is>
       </c>
     </row>
@@ -6439,16 +6280,18 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Versao</t>
+          <t xml:space="preserve">Titulo</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador de versão do documento (ex.: 1.0, 2.3).</t>
-        </is>
-      </c>
-      <c r="D99" s="3">
-        <v>2</v>
+          <t xml:space="preserve">Título de exibição.</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRO 06.01 — Planejamento da Contratação</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -6459,17 +6302,17 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data</t>
+          <t xml:space="preserve">Tipo_Documento</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data no formato dd/mm/aaaa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/05/2026</t>
+          <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6324,17 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situacao</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigente, Em elaboração, Em revisão ou Revogado.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigente</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
@@ -6503,17 +6346,17 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ato_Aprovacao</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolução ou ato que aprovou o documento (N-000, item 3.1.1) — só se aplica a Norma interna, Procedimento e Manual.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolução nº 812, de 18/05/2026 (Diretoria Executiva)</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -6525,18 +6368,16 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Versao</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endereço (URL) de acesso — o painel gera um link clicável automaticamente.</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://exemplo.codevasf.gov.br/repositorio/pop-06-01.pdf</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D103" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -6547,105 +6388,105 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Data</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">dd/mm/aaaa.</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publicado após validação do TO-BE.</t>
+          <t xml:space="preserve">18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Situacao</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — RIS-nnn.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIS-001</t>
+          <t xml:space="preserve">Vigente</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Ato_Aprovacao</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Mostra a que nível (Macroprocesso/Processo/Subprocesso/Atividade/Tarefa) este registro pertence, lido do prefixo de Vinculo_Codigo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">Resolução nº 812, de 18/05/2026 (Diretoria Executiva)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do item ao qual este registro se vincula, de qualquer nível da hierarquia. Aceita mais de um código separado por ; quando valem para vários itens do mesmo nível.</t>
+          <t xml:space="preserve">URL de acesso.</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">https://exemplo.codevasf.gov.br/repositorio/pop-06-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao_Risco</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O evento de risco em si — o que pode acontecer.</t>
+          <t xml:space="preserve">Nota livre.</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimativas de preço defasadas gerando sobrepreço ou licitação deserta.</t>
+          <t xml:space="preserve">Publicado após validação do TO-BE.</t>
         </is>
       </c>
     </row>
@@ -6657,17 +6498,17 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação do item, numa lista fechada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">RIS-001</t>
         </is>
       </c>
     </row>
@@ -6679,17 +6520,17 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatores</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que pode acionar ou favorecer este risco.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ainda sem exemplo preenchido)</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
@@ -6701,17 +6542,17 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cronograma_Risco</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quando o risco tende a se concretizar.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ainda sem exemplo preenchido)</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -6723,17 +6564,17 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data_Identificacao</t>
+          <t xml:space="preserve">Descricao_Risco</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quando este risco foi identificado pela primeira vez.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
+          <t xml:space="preserve">Estimativas de preço defasadas gerando sobrepreço ou licitação deserta.</t>
         </is>
       </c>
     </row>
@@ -6745,16 +6586,18 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Probabilidade_1a5</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chance de concretização, de 1 (rara) a 5 (quase certa).</t>
-        </is>
-      </c>
-      <c r="D113" s="3">
-        <v>4</v>
+          <t xml:space="preserve">Classificação, lista fechada.</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6765,16 +6608,18 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impacto_1a5</t>
+          <t xml:space="preserve">Fatores</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravidade das consequências, de 1 (insignificante) a 5 (catastrófico).</t>
-        </is>
-      </c>
-      <c r="D114" s="6">
-        <v>4</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(sem exemplo)</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6785,16 +6630,18 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nivel_PxI</t>
+          <t xml:space="preserve">Cronograma_Risco</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Probabilidade × Impacto (1 a 25).</t>
-        </is>
-      </c>
-      <c r="D115" s="3">
-        <v>16</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(sem exemplo)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6805,17 +6652,17 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificacao</t>
+          <t xml:space="preserve">Data_Identificacao</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Baixo (até 4), Moderado (5–11), Alto (12–19) ou Extremo (20–25).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alto</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
     </row>
@@ -6827,18 +6674,16 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resposta</t>
+          <t xml:space="preserve">Probabilidade_1a5</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estratégia adotada: Mitigar, Aceitar, Transferir ou Evitar.</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mitigar</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D117" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -6849,18 +6694,16 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controles_Tratamento</t>
+          <t xml:space="preserve">Impacto_1a5</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que já existe ou será feito para tratar o risco.</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Roteiro de pesquisa com múltiplas fontes (Painel de Preços, PNCP) e revisão pela UNP.</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D118" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="119">
@@ -6871,18 +6714,16 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prazo_Tratamento</t>
+          <t xml:space="preserve">Nivel_PxI</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data-limite para concluir o tratamento de Controles_Tratamento.</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30/09/2026</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D119" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="120">
@@ -6893,7 +6734,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responsavel</t>
+          <t xml:space="preserve">Classificacao</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6903,7 +6744,7 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ricardo Nogueira</t>
+          <t xml:space="preserve">Alto</t>
         </is>
       </c>
     </row>
@@ -6915,105 +6756,105 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status</t>
+          <t xml:space="preserve">Resposta</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situação atual, escolhida numa lista fechada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em tratamento</t>
+          <t xml:space="preserve">Mitigar</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Controles_Tratamento</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — IND-nnn.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IND-001</t>
+          <t xml:space="preserve">Roteiro de pesquisa com múltiplas fontes (Painel de Preços, PNCP) e revisão pela UNP.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Prazo_Tratamento</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempo médio do ciclo de contratação</t>
+          <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Responsavel</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Mostra a que nível (Macroprocesso/Processo/Subprocesso/Atividade/Tarefa) este registro pertence, lido do prefixo de Vinculo_Codigo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Ricardo Nogueira</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Status</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do item ao qual este registro se vincula, de qualquer nível da hierarquia. Aceita mais de um código separado por ; quando valem para vários itens do mesmo nível.</t>
+          <t xml:space="preserve">Lista fechada.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">Em tratamento</t>
         </is>
       </c>
     </row>
@@ -7025,17 +6866,17 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação do item, numa lista fechada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">IND-001</t>
         </is>
       </c>
     </row>
@@ -7047,17 +6888,17 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao_Formula</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Como o valor é calculado.</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Média de dias entre o DFD e a homologação do certame.</t>
+          <t xml:space="preserve">Tempo médio do ciclo de contratação</t>
         </is>
       </c>
     </row>
@@ -7069,17 +6910,17 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade de medida do resultado.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dias</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
@@ -7091,17 +6932,17 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polaridade</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Maior melhor" ou "Menor melhor" — usada para calcular se a meta foi atingida.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menor melhor</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -7113,16 +6954,18 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meta</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor de referência a ser alcançado.</t>
-        </is>
-      </c>
-      <c r="D130" s="6">
-        <v>120</v>
+          <t xml:space="preserve">Classificação, lista fechada.</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -7133,17 +6976,17 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Periodicidade</t>
+          <t xml:space="preserve">Descricao_Formula</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">De quanto em quanto tempo a métrica é medida.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trimestral</t>
+          <t xml:space="preserve">Média de dias entre o DFD e a homologação do certame.</t>
         </is>
       </c>
     </row>
@@ -7155,17 +6998,17 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte</t>
+          <t xml:space="preserve">Unidade</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">De onde vem a informação ou quem a mantém atualizada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras.gov.br</t>
+          <t xml:space="preserve">dias</t>
         </is>
       </c>
     </row>
@@ -7177,104 +7020,104 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Polaridade</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordado com as áreas demandantes em 2026.</t>
+          <t xml:space="preserve">Menor melhor</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicoes</t>
+          <t xml:space="preserve">Metricas</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Meta</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — MED-nnn.</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MED-001</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D134" s="6">
+        <v>120</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicoes</t>
+          <t xml:space="preserve">Metricas</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metrica_ID</t>
+          <t xml:space="preserve">Periodicidade</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código da métrica medida — lista suspensa a partir da aba Metricas.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">IND-001</t>
+          <t xml:space="preserve">Trimestral</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicoes</t>
+          <t xml:space="preserve">Metricas</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data_Medicao</t>
+          <t xml:space="preserve">Fonte</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quando o valor foi apurado.</t>
+          <t xml:space="preserve">De onde vem a informação.</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/06/2026</t>
+          <t xml:space="preserve">Compras.gov.br</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicoes</t>
+          <t xml:space="preserve">Metricas</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valor</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resultado numérico apurado nesta medição.</t>
-        </is>
-      </c>
-      <c r="D137" s="3">
-        <v>148</v>
+          <t xml:space="preserve">Nota livre.</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acordado com as áreas demandantes em 2026.</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -7285,105 +7128,103 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primeira apuração do trimestre.</t>
+          <t xml:space="preserve">MED-001</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papeis</t>
+          <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Metrica_ID</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — PAP-nnn.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAP-001</t>
+          <t xml:space="preserve">IND-001</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papeis</t>
+          <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Data_Medicao</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Mostra a que nível (Macroprocesso/Processo/Subprocesso/Atividade/Tarefa) este registro pertence, lido do prefixo de Vinculo_Codigo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">30/06/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papeis</t>
+          <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Valor</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do item ao qual este registro se vincula, de qualquer nível da hierarquia. Aceita mais de um código separado por ; quando valem para vários itens do mesmo nível.</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PP-01</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D141" s="3">
+        <v>148</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papeis</t>
+          <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papel</t>
+          <t xml:space="preserve">Observacao</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do papel ou função.</t>
+          <t xml:space="preserve">Nota livre.</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gestor do processo</t>
+          <t xml:space="preserve">Primeira apuração do trimestre.</t>
         </is>
       </c>
     </row>
@@ -7395,17 +7236,17 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envolvimento</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RACI: Executa (R), Aprova (A), Consultado (C) ou Informado (I).</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aprova (A)</t>
+          <t xml:space="preserve">PAP-001</t>
         </is>
       </c>
     </row>
@@ -7417,105 +7258,105 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Pessoa</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade ou pessoa que ocupa este papel.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AE/GAG</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regras</t>
+          <t xml:space="preserve">Papeis</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — REG-nnn.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">REG-001</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regras</t>
+          <t xml:space="preserve">Papeis</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Papel</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alçada de aprovação por valor</t>
+          <t xml:space="preserve">Gestor do processo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regras</t>
+          <t xml:space="preserve">Papeis</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Envolvimento</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Mostra a que nível (Macroprocesso/Processo/Subprocesso/Atividade/Tarefa) este registro pertence, lido do prefixo de Vinculo_Codigo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Aprova (A)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regras</t>
+          <t xml:space="preserve">Papeis</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Unidade_Pessoa</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Código do item ao qual este registro se vincula, de qualquer nível da hierarquia. Aceita mais de um código separado por ; quando valem para vários itens do mesmo nível.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
     </row>
@@ -7527,17 +7368,17 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Regra</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Natureza da regra: Operação, Regulatória, Cálculo ou Restrição.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operação</t>
+          <t xml:space="preserve">REG-001</t>
         </is>
       </c>
     </row>
@@ -7549,17 +7390,17 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratações acima de R$ 50.000 exigem aprovação da autoridade competente.</t>
+          <t xml:space="preserve">Alçada de aprovação por valor</t>
         </is>
       </c>
     </row>
@@ -7571,103 +7412,105 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte_Normativa</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norma, lei ou instrução da qual a regra deriva.</t>
+          <t xml:space="preserve">CALCULADA — não digite.</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lei nº 14.133/2021</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cultura_Processos</t>
+          <t xml:space="preserve">Regras</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — CULT-nn.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CULT-01</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cultura_Processos</t>
+          <t xml:space="preserve">Regras</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Tipo_Regra</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D153" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operação</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cultura_Processos</t>
+          <t xml:space="preserve">Regras</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caracteristica</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Característica organizacional avaliada (CBOK 9.5.6) — autoavaliação da empresa, não de um processo específico.</t>
+          <t xml:space="preserve">Explicação livre.</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordo geral sobre o que são os processos de negócio</t>
+          <t xml:space="preserve">Contratações acima de R$ 50.000 exigem aprovação da autoridade competente.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cultura_Processos</t>
+          <t xml:space="preserve">Regras</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situacao</t>
+          <t xml:space="preserve">Fonte_Normativa</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se a característica já é realidade na Companhia: Sim, Não ou Não avaliado.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não avaliado</t>
+          <t xml:space="preserve">Lei nº 14.133/2021</t>
         </is>
       </c>
     </row>
@@ -7679,105 +7522,103 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nota livre, sem estrutura fixa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ainda sem exemplo preenchido)</t>
+          <t xml:space="preserve">CULT-01</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciativas</t>
+          <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador único — INI-nnn.</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INI-001</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D157" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciativas</t>
+          <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data</t>
+          <t xml:space="preserve">Caracteristica</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data no formato dd/mm/aaaa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20/05/2026</t>
+          <t xml:space="preserve">Acordo geral sobre o que são os processos de negócio</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciativas</t>
+          <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titulo</t>
+          <t xml:space="preserve">Situacao</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Título de exibição do item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automação da conferência de preços na pesquisa (PP-01)</t>
+          <t xml:space="preserve">Não avaliado</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciativas</t>
+          <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo</t>
+          <t xml:space="preserve">Observacao</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Natureza da iniciativa viabilizada pelo repositório.</t>
+          <t xml:space="preserve">Nota livre.</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automação</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -7789,17 +7630,17 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A equipe de TI usou o PRO e o roteiro de pesquisa de preços publicados no repositório (DOC-007) p...</t>
+          <t xml:space="preserve">INI-001</t>
         </is>
       </c>
     </row>
@@ -7811,108 +7652,112 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processos_Relacionados</t>
+          <t xml:space="preserve">Data</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Códigos dos processos envolvidos, separados por ; quando houver mais de um.</t>
+          <t xml:space="preserve">dd/mm/aaaa.</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">20/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias</t>
+          <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Titulo</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segue a ordem dos itens no normativo (3.1, 3.2...).</t>
-        </is>
-      </c>
-      <c r="D163" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Título de exibição.</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automação da conferência de preços na pesquisa (PP-01)</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias</t>
+          <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instancia</t>
+          <t xml:space="preserve">Tipo</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Órgão, unidade ou papel ao qual as atribuições se referem.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conselho de Administração</t>
+          <t xml:space="preserve">Automação</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias</t>
+          <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item_Normativo</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número do item da RES 031/2025 que define estas atribuições — permite conferir direto na norma.</t>
-        </is>
-      </c>
-      <c r="D165" s="3">
-        <v>3.1</v>
+          <t xml:space="preserve">Explicação livre.</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A equipe de TI usou o PRO e o roteiro de pesquisa de preços publicados no repositório (DOC-007) p...</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias</t>
+          <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atribuicoes</t>
+          <t xml:space="preserve">Processos_Relacionados</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de atribuições desta instância, separadas por ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garantir o apoio institucional para a gestão de processos.</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jornada</t>
+          <t xml:space="preserve">Competencias</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -7922,7 +7767,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
+          <t xml:space="preserve">Posição de exibição.</t>
         </is>
       </c>
       <c r="D167" s="3">
@@ -7932,66 +7777,64 @@
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jornada</t>
+          <t xml:space="preserve">Competencias</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fase</t>
+          <t xml:space="preserve">Instancia</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fase da jornada: Descobrir, Definir, Desenvolver, Entregar ou Evoluir.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descobrir</t>
+          <t xml:space="preserve">Conselho de Administração</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jornada</t>
+          <t xml:space="preserve">Competencias</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Item_Normativo</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Escuta e contextualização</t>
-        </is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D169" s="3">
+        <v>3.1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jornada</t>
+          <t xml:space="preserve">Competencias</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duracao</t>
+          <t xml:space="preserve">Atribuicoes</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempo estimado para esta etapa.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1–2 semanas</t>
+          <t xml:space="preserve">Garantir o apoio institucional para a gestão de processos.</t>
         </is>
       </c>
     </row>
@@ -8003,18 +7846,16 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Para que o item existe — o resultado que busca entregar.</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compreender a dor real, o contexto e as expectativas de quem executa e de quem se beneficia do pr...</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D171" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -8025,17 +7866,17 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades_Chave</t>
+          <t xml:space="preserve">Fase</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que se faz nesta etapa, separado por ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reunião de sensibilização com a unidade demandante; Entrevistas semiestruturadas com executores e...</t>
+          <t xml:space="preserve">Descobrir</t>
         </is>
       </c>
     </row>
@@ -8047,17 +7888,17 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quem_Faz</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papéis envolvidos, separados por ; .</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUGEP; Interlocutor da área; Dono do processo</t>
+          <t xml:space="preserve">Escuta e contextualização</t>
         </is>
       </c>
     </row>
@@ -8069,17 +7910,17 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entregaveis</t>
+          <t xml:space="preserve">Duracao</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que a etapa produz, separado por ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ata de reunião; Formulário preenchido; Mapa de partes interessadas</t>
+          <t xml:space="preserve">1–2 semanas</t>
         </is>
       </c>
     </row>
@@ -8091,29 +7932,29 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sentimento_Usuario</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Como quem vive o mapeamento costuma se sentir nesta etapa.</t>
+          <t xml:space="preserve">Resultado que busca entregar.</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curiosidade e ansiedade: “por que estão olhando meu trabalho?”</t>
+          <t xml:space="preserve">Compreender a dor real, o contexto e as expectativas de quem executa e de quem se beneficia do pr...</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repositorio</t>
+          <t xml:space="preserve">Jornada</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Atividades_Chave</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -8123,73 +7964,73 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">REP-001</t>
+          <t xml:space="preserve">Reunião de sensibilização com a unidade demandante; Entrevistas semiestruturadas com executores e...</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repositorio</t>
+          <t xml:space="preserve">Jornada</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">Quem_Faz</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de material: Documento oficial, Template, Instrumento, Ferramenta ou Referência.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documento oficial</t>
+          <t xml:space="preserve">NUGEP; Interlocutor da área; Dono do processo</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repositorio</t>
+          <t xml:space="preserve">Jornada</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fase_Ciclo</t>
+          <t xml:space="preserve">Entregaveis</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fase do ciclo BPM em que este material é mais útil.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desenho</t>
+          <t xml:space="preserve">Ata de reunião; Formulário preenchido; Mapa de partes interessadas</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repositorio</t>
+          <t xml:space="preserve">Jornada</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titulo</t>
+          <t xml:space="preserve">Sentimento_Usuario</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Título de exibição do item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metodologia de Gerenciamento de Processos da Codevasf</t>
+          <t xml:space="preserve">Curiosidade e ansiedade: “por que estão olhando meu trabalho?”</t>
         </is>
       </c>
     </row>
@@ -8201,17 +8042,17 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação livre do que é ou do que faz o item.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponí...</t>
+          <t xml:space="preserve">REP-001</t>
         </is>
       </c>
     </row>
@@ -8223,17 +8064,17 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">De onde vem a informação ou quem a mantém atualizada.</t>
+          <t xml:space="preserve">Classificação, lista fechada.</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codevasf</t>
+          <t xml:space="preserve">Documento oficial</t>
         </is>
       </c>
     </row>
@@ -8245,17 +8086,17 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Fase_Ciclo</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endereço (URL) de acesso — o painel gera um link clicável automaticamente.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://intraplone.codevasf.gov.br/documentos_normativos_referencia/governanca-e-gestao/copy_of_p...</t>
+          <t xml:space="preserve">Desenho</t>
         </is>
       </c>
     </row>
@@ -8267,102 +8108,104 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Titulo</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D183" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Título de exibição.</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metodologia de Gerenciamento de Processos da Codevasf</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUGEP</t>
+          <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
-        </is>
-      </c>
-      <c r="D184" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Explicação livre.</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponí...</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUGEP</t>
+          <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Fonte</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome do item, em texto livre.</t>
+          <t xml:space="preserve">De onde vem a informação.</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ricardo Nunes Vasconcelos</t>
+          <t xml:space="preserve">Codevasf</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUGEP</t>
+          <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papel</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Função exercida no núcleo ou na gestão de processos.</t>
+          <t xml:space="preserve">URL de acesso.</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerente-Executivo da Área de Gestão Estratégica</t>
+          <t xml:space="preserve">https://intraplone.codevasf.gov.br/documentos_normativos_referencia/governanca-e-gestao/copy_of_p...</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUGEP</t>
+          <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Sigla</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla da unidade orgânica da pessoa — lista suspensa a partir da aba Siglas.</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AE</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D187" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -8373,18 +8216,16 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Nome</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CALCULADA — não digite. Nome por extenso, buscado na aba Siglas a partir de Unidade_Sigla.</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Área de Gestão Estratégica</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D188" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8395,17 +8236,17 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre.</t>
+          <t xml:space="preserve">Nome do item.</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ricardo.vasconcelos@codevasf.gov.br</t>
+          <t xml:space="preserve">Ricardo Nunes Vasconcelos</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8258,7 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefone</t>
+          <t xml:space="preserve">Papel</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -8427,7 +8268,7 @@
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(61) 2028-4400</t>
+          <t xml:space="preserve">Gerente-Executivo da Área de Gestão Estratégica</t>
         </is>
       </c>
     </row>
@@ -8439,17 +8280,17 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foto</t>
+          <t xml:space="preserve">Unidade_Sigla</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL de uma imagem pública — aparece no avatar da pessoa no painel.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://randomuser.me/api/portraits/men/32.jpg</t>
+          <t xml:space="preserve">AE</t>
         </is>
       </c>
     </row>
@@ -8461,98 +8302,100 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hierarquia</t>
+          <t xml:space="preserve">Unidade_Nome</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 = Gerente-Executivo, 2 = Gerente, 3 = equipe da Unidade, 0 = ponto focal de outra área.</t>
-        </is>
-      </c>
-      <c r="D192" s="6">
-        <v>1</v>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área de Gestão Estratégica</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glossario</t>
+          <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo</t>
+          <t xml:space="preserve">Email</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palavra ou sigla definida.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABPMP</t>
+          <t xml:space="preserve">ricardo.vasconcelos@codevasf.gov.br</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glossario</t>
+          <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definicao</t>
+          <t xml:space="preserve">Telefone</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explicação do termo.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Association of Business Process Management Professionals — entidade internacional sem fins lucrat...</t>
+          <t xml:space="preserve">(61) 2028-4400</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glossario</t>
+          <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte</t>
+          <t xml:space="preserve">Foto</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">De onde vem a informação ou quem a mantém atualizada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABPMP</t>
+          <t xml:space="preserve">https://randomuser.me/api/portraits/men/32.jpg</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAQ</t>
+          <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Hierarquia</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Número que define a posição de exibição — valor menor aparece primeiro.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D196" s="6">
@@ -8562,154 +8405,768 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAQ</t>
+          <t xml:space="preserve">Glossario</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">Termo</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificação do item, numa lista fechada.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conceitos básicos</t>
+          <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAQ</t>
+          <t xml:space="preserve">Glossario</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta</t>
+          <t xml:space="preserve">Definicao</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pergunta exibida no painel.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que é Gestão de Processos (BPM)?</t>
+          <t xml:space="preserve">Association of Business Process Management Professionals — entidade internacional sem fins lucrat...</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAQ</t>
+          <t xml:space="preserve">Glossario</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resposta</t>
+          <t xml:space="preserve">Fonte</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resposta exibida ao expandir a pergunta.</t>
+          <t xml:space="preserve">De onde vem a informação.</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Process Management é uma disciplina gerencial integrada que combina técnicas, métodos e ...</t>
+          <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas</t>
+          <t xml:space="preserve">FAQ</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sigla oficial da unidade orgânica (Decisão da Presidência nº 601/2025).</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10ª/AJ</t>
-        </is>
+          <t xml:space="preserve">Posição de exibição.</t>
+        </is>
+      </c>
+      <c r="D200" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siglas</t>
+          <t xml:space="preserve">FAQ</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome por extenso da unidade.</t>
+          <t xml:space="preserve">Classificação, lista fechada.</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+          <t xml:space="preserve">Conceitos básicos</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parametros</t>
+          <t xml:space="preserve">FAQ</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chave</t>
+          <t xml:space="preserve">Pergunta</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador do parâmetro, lido pelo código do painel — não altere o nome da chave.</t>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contato_Unidade</t>
+          <t xml:space="preserve">O que é Gestão de Processos (BPM)?</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">FAQ</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resposta</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Process Management é uma disciplina gerencial integrada que combina técnicas, métodos e ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siglas</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sigla</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ª/AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siglas</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome do item.</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessoria Jurídica Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parametros</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chave</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contato_Unidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parametros</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Texto ou link exibido no lugar da chave correspondente.</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade de Gestão Normativa e de Processos (AE/GPE/UNP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_Macroprocesso</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status_Mapeamento</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não iniciado</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prioridade</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complexidade</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maturidade_Processo</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sim_Nao</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nivel_Vinculo</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macroprocesso</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_Atividade</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agregação de Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_Tarefa</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_Documento</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimento (PRO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Situacao_Documento</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vigente</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_Risco</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resposta_Risco</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mitigar</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status_Risco</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aberto</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Envolvimento_RACI</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Executa (R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_Regra</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operação</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polaridade</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maior melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodicidade</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Situacao_Cultura</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo_Iniciativa</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automação</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_Repositorio</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documento oficial</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fase_Instrumento</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planejamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_FAQ</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conceitos básicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK_Todos_Codigos</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre.</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MG-01</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16813,7 @@
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -16449,22 +16906,10 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subtitulo_Inicio</t>
+          <t xml:space="preserve">Titulo_Repositorio</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cadeia de valor, portfólio de processos e repositório de materiais da Companhia, num só lugar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Titulo_Repositorio</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositório de materiais e ferramentas</t>
         </is>
@@ -17478,7 +17923,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -17494,6 +17939,7 @@
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="30" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17567,6 +18013,11 @@
           <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trilha</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -17627,6 +18078,10 @@
           <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
         </is>
       </c>
+      <c r="O2" s="8" t="str">
+        <f>=A2</f>
+        <v>MG-01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -17687,6 +18142,10 @@
           <t xml:space="preserve">e-Codevasf; Sistema de gestão de riscos</t>
         </is>
       </c>
+      <c r="O3" s="8" t="str">
+        <f>=A3</f>
+        <v>MG-02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -17747,6 +18206,10 @@
           <t xml:space="preserve">TransfereGov; e-Codevasf</t>
         </is>
       </c>
+      <c r="O4" s="8" t="str">
+        <f>=A4</f>
+        <v>MF-01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -17807,6 +18270,10 @@
           <t xml:space="preserve">SIG-Irrigação (fictício); e-Codevasf</t>
         </is>
       </c>
+      <c r="O5" s="8" t="str">
+        <f>=A5</f>
+        <v>MF-02</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -17867,6 +18334,10 @@
           <t xml:space="preserve">e-Codevasf; GeoPortal (fictício)</t>
         </is>
       </c>
+      <c r="O6" s="8" t="str">
+        <f>=A6</f>
+        <v>MF-03</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -17932,6 +18403,10 @@
           <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
         </is>
       </c>
+      <c r="O7" s="8" t="str">
+        <f>=A7</f>
+        <v>MS-01</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -17992,6 +18467,10 @@
           <t xml:space="preserve">SIGEP (fictício); e-Codevasf</t>
         </is>
       </c>
+      <c r="O8" s="8" t="str">
+        <f>=A8</f>
+        <v>MS-02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -18052,17 +18531,18 @@
           <t xml:space="preserve">e-Codevasf; Service Desk</t>
         </is>
       </c>
+      <c r="O9" s="8" t="str">
+        <f>=A9</f>
+        <v>MS-03</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:O1"/>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>Listas!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
-      <formula1>Siglas!$A$2:$A$421</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="F2:F300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
   </dataValidations>
@@ -18074,7 +18554,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AM8"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -18114,6 +18594,7 @@
     <col min="36" max="36" width="30" customWidth="1"/>
     <col min="37" max="37" width="28" customWidth="1"/>
     <col min="38" max="38" width="24" customWidth="1"/>
+    <col min="39" max="39" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18307,6 +18788,11 @@
           <t xml:space="preserve">Pendencia</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trilha</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -18493,6 +18979,10 @@
           <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
         </is>
       </c>
+      <c r="AM2" s="8" t="str">
+        <f>=C2&amp;" › "&amp;A2</f>
+        <v>MS-01 › PP-01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -18674,6 +19164,10 @@
           <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
         </is>
       </c>
+      <c r="AM3" s="8" t="str">
+        <f>=C3&amp;" › "&amp;A3</f>
+        <v>MS-01 › PP-02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -18850,6 +19344,10 @@
           <t xml:space="preserve">Concluir modelagem AS-IS das medições e pagamentos.</t>
         </is>
       </c>
+      <c r="AM4" s="8" t="str">
+        <f>=C4&amp;" › "&amp;A4</f>
+        <v>MS-01 › PP-03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -19026,6 +19524,10 @@
           <t xml:space="preserve">Agendar oficina de validação do AS-IS com o distrito.</t>
         </is>
       </c>
+      <c r="AM5" s="8" t="str">
+        <f>=C5&amp;" › "&amp;A5</f>
+        <v>MF-02 › PP-04</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -19187,6 +19689,10 @@
           <t xml:space="preserve">Enviar formulário de levantamento à área (previsto ago/2026).</t>
         </is>
       </c>
+      <c r="AM6" s="8" t="str">
+        <f>=C6&amp;" › "&amp;A6</f>
+        <v>MF-03 › PP-05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -19363,6 +19869,10 @@
           <t xml:space="preserve">Ciclo de monitoramento trimestral (próximo: set/2026).</t>
         </is>
       </c>
+      <c r="AM7" s="8" t="str">
+        <f>=C7&amp;" › "&amp;A7</f>
+        <v>MG-01 › PP-06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -19524,9 +20034,13 @@
           <t xml:space="preserve">Aguardando priorização no ciclo 2027.</t>
         </is>
       </c>
+      <c r="AM8" s="8" t="str">
+        <f>=C8&amp;" › "&amp;A8</f>
+        <v>MS-02 › PP-07</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL1"/>
+  <autoFilter ref="A1:AM1"/>
   <dataValidations count="17">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>Macroprocessos!$A$2:$A$9</formula1>
@@ -19534,8 +20048,8 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="F2:F300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="H2:H300">
-      <formula1>Siglas!$A$2:$A$421</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="G2:G300">
+      <formula1>NUGEP!$B$2:$B$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>Listas!$C$2:$C$4</formula1>
@@ -19600,12 +20114,12 @@
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="11" max="11" width="36" customWidth="1"/>
     <col min="12" max="12" width="36" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="26" customWidth="1"/>
-    <col min="16" max="16" width="28" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19661,32 +20175,32 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produto_Principal</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontes_Dados</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
     </row>
@@ -19731,28 +20245,27 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estudo Técnico Preliminar (ETP) aprovado</t>
+          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
+          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
           <t xml:space="preserve">e-Codevasf</t>
         </is>
+      </c>
+      <c r="P2" s="8" t="str">
+        <f>=IF(LEFT(C2,2)="SP",VLOOKUP(C2,Subprocessos!$A:$P,16,0),VLOOKUP(C2,Processos!$A:$AM,39,0))&amp;" › "&amp;A2</f>
+        <v>MS-01 › PP-01 › SP-01</v>
       </c>
     </row>
     <row r="3">
@@ -19796,23 +20309,22 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo de Referência (TR) aprovado e validado juridicamente</t>
+          <t xml:space="preserve">ETP aprovado; Modelos padronizados de TR</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado; Modelos padronizados de TR</t>
+          <t xml:space="preserve">TR aprovado e validado juridicamente</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR aprovado e validado juridicamente</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">e-Codevasf</t>
         </is>
+      </c>
+      <c r="P3" s="8" t="str">
+        <f>=IF(LEFT(C3,2)="SP",VLOOKUP(C3,Subprocessos!$A:$P,16,0),VLOOKUP(C3,Processos!$A:$AM,39,0))&amp;" › "&amp;A3</f>
+        <v>MS-01 › PP-01 › SP-02</v>
       </c>
     </row>
     <row r="4">
@@ -19856,28 +20368,27 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relatório de pesquisa de preços com valor estimado consolidado</t>
+          <t xml:space="preserve">TR validado; Fontes de preços admitidas</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR validado; Fontes de preços admitidas</t>
+          <t xml:space="preserve">Relatório de pesquisa de preços; Mapa comparativo</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relatório de pesquisa de preços; Mapa comparativo</t>
+          <t xml:space="preserve">Painel de Preços; PNCP; e-Codevasf</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Painel de Preços; PNCP; e-Codevasf</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
           <t xml:space="preserve">Painel de Preços; PNCP</t>
         </is>
+      </c>
+      <c r="P4" s="8" t="str">
+        <f>=IF(LEFT(C4,2)="SP",VLOOKUP(C4,Subprocessos!$A:$P,16,0),VLOOKUP(C4,Processos!$A:$AM,39,0))&amp;" › "&amp;A4</f>
+        <v>MS-01 › PP-01 › SP-03</v>
       </c>
     </row>
     <row r="5">
@@ -19931,23 +20442,22 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amostra de preços tratada estatisticamente, com justificativa de exclusões</t>
+          <t xml:space="preserve">Amostra de preços coletados na pesquisa</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amostra de preços coletados na pesquisa</t>
+          <t xml:space="preserve">Valores discrepantes identificados e justificados</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valores discrepantes identificados e justificados</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">Planilha padrão; e-Codevasf</t>
         </is>
+      </c>
+      <c r="P5" s="8" t="str">
+        <f>=IF(LEFT(C5,2)="SP",VLOOKUP(C5,Subprocessos!$A:$P,16,0),VLOOKUP(C5,Processos!$A:$AM,39,0))&amp;" › "&amp;A5</f>
+        <v>MS-01 › PP-01 › SP-03 › SP-04</v>
       </c>
     </row>
     <row r="6">
@@ -19991,23 +20501,22 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ata da sessão pública com resultado do certame por item</t>
+          <t xml:space="preserve">Edital publicado; Propostas dos licitantes</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edital publicado; Propostas dos licitantes</t>
+          <t xml:space="preserve">Ata da sessão; Resultado por item</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ata da sessão; Resultado por item</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
+      </c>
+      <c r="P6" s="8" t="str">
+        <f>=IF(LEFT(C6,2)="SP",VLOOKUP(C6,Subprocessos!$A:$P,16,0),VLOOKUP(C6,Processos!$A:$AM,39,0))&amp;" › "&amp;A6</f>
+        <v>MS-01 › PP-02 › SP-05</v>
       </c>
     </row>
     <row r="7">
@@ -20051,42 +20560,35 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programação hídrica semanal executada e registrada</t>
+          <t xml:space="preserve">Outorga de uso; Demanda de irrigação</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outorga de uso; Demanda de irrigação</t>
+          <t xml:space="preserve">Programação hídrica executada; Registros de volume</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Programação hídrica executada; Registros de volume</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
+      </c>
+      <c r="P7" s="8" t="str">
+        <f>=IF(LEFT(C7,2)="SP",VLOOKUP(C7,Subprocessos!$A:$P,16,0),VLOOKUP(C7,Processos!$A:$AM,39,0))&amp;" › "&amp;A7</f>
+        <v>MF-02 › PP-04 › SP-06</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
-  <dataValidations count="5">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>"PP-01,PP-02,PP-03,PP-04,PP-05,PP-06,PP-07,SP-01,SP-02,SP-03,SP-04,SP-05,SP-06"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="G2:G300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="H2:H300">
-      <formula1>Siglas!$A$2:$A$421</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>Listas!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="J2:J300">
-      <formula1>"PP-01,PP-02,PP-03,PP-04,PP-05,PP-06,PP-07,SP-01,SP-02,SP-03,SP-04,SP-05,SP-06"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -20097,7 +20599,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -20108,6 +20610,7 @@
     <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20156,6 +20659,11 @@
           <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trilha</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -20201,6 +20709,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J2" s="8" t="str">
+        <f>=IF(LEFT(C2,2)="SP",VLOOKUP(C2,Subprocessos!$A:$P,16,0),VLOOKUP(C2,Processos!$A:$AM,39,0))&amp;" › "&amp;A2</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -20241,6 +20753,10 @@
           <t xml:space="preserve">PNCP; Compras.gov.br</t>
         </is>
       </c>
+      <c r="J3" s="8" t="str">
+        <f>=IF(LEFT(C3,2)="SP",VLOOKUP(C3,Subprocessos!$A:$P,16,0),VLOOKUP(C3,Processos!$A:$AM,39,0))&amp;" › "&amp;A3</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -20281,6 +20797,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J4" s="8" t="str">
+        <f>=IF(LEFT(C4,2)="SP",VLOOKUP(C4,Subprocessos!$A:$P,16,0),VLOOKUP(C4,Processos!$A:$AM,39,0))&amp;" › "&amp;A4</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -20326,6 +20846,10 @@
           <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
+      <c r="J5" s="8" t="str">
+        <f>=IF(LEFT(C5,2)="SP",VLOOKUP(C5,Subprocessos!$A:$P,16,0),VLOOKUP(C5,Processos!$A:$AM,39,0))&amp;" › "&amp;A5</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-04</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -20366,6 +20890,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J6" s="8" t="str">
+        <f>=IF(LEFT(C6,2)="SP",VLOOKUP(C6,Subprocessos!$A:$P,16,0),VLOOKUP(C6,Processos!$A:$AM,39,0))&amp;" › "&amp;A6</f>
+        <v>MS-01 › PP-01 › SP-02 › AT-05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -20411,6 +20939,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J7" s="8" t="str">
+        <f>=IF(LEFT(C7,2)="SP",VLOOKUP(C7,Subprocessos!$A:$P,16,0),VLOOKUP(C7,Processos!$A:$AM,39,0))&amp;" › "&amp;A7</f>
+        <v>MS-01 › PP-01 › SP-02 › AT-06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -20456,6 +20988,10 @@
           <t xml:space="preserve">Painel de Preços; PNCP</t>
         </is>
       </c>
+      <c r="J8" s="8" t="str">
+        <f>=IF(LEFT(C8,2)="SP",VLOOKUP(C8,Subprocessos!$A:$P,16,0),VLOOKUP(C8,Processos!$A:$AM,39,0))&amp;" › "&amp;A8</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -20496,6 +21032,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J9" s="8" t="str">
+        <f>=IF(LEFT(C9,2)="SP",VLOOKUP(C9,Subprocessos!$A:$P,16,0),VLOOKUP(C9,Processos!$A:$AM,39,0))&amp;" › "&amp;A9</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -20536,6 +21076,10 @@
           <t xml:space="preserve">Planilha padrão</t>
         </is>
       </c>
+      <c r="J10" s="8" t="str">
+        <f>=IF(LEFT(C10,2)="SP",VLOOKUP(C10,Subprocessos!$A:$P,16,0),VLOOKUP(C10,Processos!$A:$AM,39,0))&amp;" › "&amp;A10</f>
+        <v>MS-01 › PP-01 › SP-03 › SP-04 › AT-09</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -20581,6 +21125,10 @@
           <t xml:space="preserve">Compras.gov.br; PNCP</t>
         </is>
       </c>
+      <c r="J11" s="8" t="str">
+        <f>=IF(LEFT(C11,2)="SP",VLOOKUP(C11,Subprocessos!$A:$P,16,0),VLOOKUP(C11,Processos!$A:$AM,39,0))&amp;" › "&amp;A11</f>
+        <v>MS-01 › PP-02 › SP-05 › AT-10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -20621,6 +21169,10 @@
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
       </c>
+      <c r="J12" s="8" t="str">
+        <f>=IF(LEFT(C12,2)="SP",VLOOKUP(C12,Subprocessos!$A:$P,16,0),VLOOKUP(C12,Processos!$A:$AM,39,0))&amp;" › "&amp;A12</f>
+        <v>MS-01 › PP-02 › SP-05 › AT-11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -20666,6 +21218,10 @@
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
       </c>
+      <c r="J13" s="8" t="str">
+        <f>=IF(LEFT(C13,2)="SP",VLOOKUP(C13,Subprocessos!$A:$P,16,0),VLOOKUP(C13,Processos!$A:$AM,39,0))&amp;" › "&amp;A13</f>
+        <v>MF-02 › PP-04 › SP-06 › AT-12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -20711,6 +21267,10 @@
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
       </c>
+      <c r="J14" s="8" t="str">
+        <f>=IF(LEFT(C14,2)="SP",VLOOKUP(C14,Subprocessos!$A:$P,16,0),VLOOKUP(C14,Processos!$A:$AM,39,0))&amp;" › "&amp;A14</f>
+        <v>MF-02 › PP-04 › SP-06 › AT-13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -20756,6 +21316,10 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J15" s="8" t="str">
+        <f>=IF(LEFT(C15,2)="SP",VLOOKUP(C15,Subprocessos!$A:$P,16,0),VLOOKUP(C15,Processos!$A:$AM,39,0))&amp;" › "&amp;A15</f>
+        <v>MS-01 › PP-03 › AT-14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -20801,9 +21365,13 @@
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
+      <c r="J16" s="8" t="str">
+        <f>=IF(LEFT(C16,2)="SP",VLOOKUP(C16,Subprocessos!$A:$P,16,0),VLOOKUP(C16,Processos!$A:$AM,39,0))&amp;" › "&amp;A16</f>
+        <v>MS-01 › PP-03 › AT-15</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>"PP-01,PP-02,PP-03,PP-04,PP-05,PP-06,PP-07,SP-01,SP-02,SP-03,SP-04,SP-05,SP-06"</formula1>
@@ -20820,7 +21388,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -20837,6 +21405,7 @@
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
     <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20915,6 +21484,11 @@
           <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trilha</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -20983,6 +21557,10 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
+      <c r="P2" s="8" t="str">
+        <f>=VLOOKUP(C2,Atividades!$A:$J,10,0)&amp;" › "&amp;A2</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-01 › TR-01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -21021,6 +21599,10 @@
           <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
+      <c r="P3" s="8" t="str">
+        <f>=VLOOKUP(C3,Atividades!$A:$J,10,0)&amp;" › "&amp;A3</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-01 › TR-02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -21054,6 +21636,10 @@
           <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
+      <c r="P4" s="8" t="str">
+        <f>=VLOOKUP(C4,Atividades!$A:$J,10,0)&amp;" › "&amp;A4</f>
+        <v>MS-01 › PP-01 › SP-01 › AT-01 › TR-03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -21122,6 +21708,10 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
+      <c r="P5" s="8" t="str">
+        <f>=VLOOKUP(C5,Atividades!$A:$J,10,0)&amp;" › "&amp;A5</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-07 › TR-04</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -21155,6 +21745,10 @@
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
+      <c r="P6" s="8" t="str">
+        <f>=VLOOKUP(C6,Atividades!$A:$J,10,0)&amp;" › "&amp;A6</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-07 › TR-05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -21193,6 +21787,10 @@
           <t xml:space="preserve">AR/GDT</t>
         </is>
       </c>
+      <c r="P7" s="8" t="str">
+        <f>=VLOOKUP(C7,Atividades!$A:$J,10,0)&amp;" › "&amp;A7</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-07 › TR-06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -21226,6 +21824,10 @@
           <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
+      <c r="P8" s="8" t="str">
+        <f>=VLOOKUP(C8,Atividades!$A:$J,10,0)&amp;" › "&amp;A8</f>
+        <v>MS-01 › PP-01 › SP-03 › AT-07 › TR-07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -21259,6 +21861,10 @@
           <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
+      <c r="P9" s="8" t="str">
+        <f>=VLOOKUP(C9,Atividades!$A:$J,10,0)&amp;" › "&amp;A9</f>
+        <v>MS-01 › PP-02 › SP-05 › AT-10 › TR-08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -21292,6 +21898,10 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
+      <c r="P10" s="8" t="str">
+        <f>=VLOOKUP(C10,Atividades!$A:$J,10,0)&amp;" › "&amp;A10</f>
+        <v>MS-01 › PP-02 › SP-05 › AT-10 › TR-09</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -21325,6 +21935,10 @@
           <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
+      <c r="P11" s="8" t="str">
+        <f>=VLOOKUP(C11,Atividades!$A:$J,10,0)&amp;" › "&amp;A11</f>
+        <v>MF-02 › PP-04 › SP-06 › AT-12 › TR-10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -21368,6 +21982,10 @@
           <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
+      <c r="P12" s="8" t="str">
+        <f>=VLOOKUP(C12,Atividades!$A:$J,10,0)&amp;" › "&amp;A12</f>
+        <v>MS-01 › PP-03 › AT-15 › TR-11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -21411,6 +22029,10 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
+      <c r="P13" s="8" t="str">
+        <f>=VLOOKUP(C13,Atividades!$A:$J,10,0)&amp;" › "&amp;A13</f>
+        <v>MS-01 › PP-03 › AT-15 › TR-12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -21459,18 +22081,19 @@
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
+      <c r="P14" s="8" t="str">
+        <f>=VLOOKUP(C14,Atividades!$A:$J,10,0)&amp;" › "&amp;A14</f>
+        <v>MS-01 › PP-03 › AT-15 › TR-13</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:P1"/>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>Atividades!$A$2:$A$16</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
       <formula1>Listas!$I$2:$I$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="O2:O300">
-      <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -22605,12 +23228,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
       <formula1>Listas!$J$2:$J$12</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
-      <formula1>Listas!$X$2:$X$50</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="H2:H300">
       <formula1>Listas!$K$2:$K$5</formula1>
@@ -23354,10 +23974,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
-      <formula1>Listas!$X$2:$X$50</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
       <formula1>Listas!$L$2:$L$7</formula1>
     </dataValidation>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -26,6 +26,7 @@
     <sheet name="Siglas" sheetId="22" r:id="rId22"/>
     <sheet name="Parametros" sheetId="23" r:id="rId23"/>
     <sheet name="Listas" sheetId="24" r:id="rId24"/>
+    <sheet name="Equipe_Gerenciamento_Processos" sheetId="25" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -355,7 +356,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -409,7 +410,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-02</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -463,7 +464,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-03</t>
+          <t xml:space="preserve">MS-01 › PP-03</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -517,7 +518,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -625,7 +626,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -679,7 +680,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-03</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -787,7 +788,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -846,7 +847,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1281,7 +1282,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1312,7 +1313,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1343,7 +1344,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1374,7 +1375,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1405,7 +1406,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-03</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1436,7 +1437,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-03</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1467,7 +1468,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01/AT-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1498,7 +1499,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-02</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1529,7 +1530,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-03</t>
+          <t xml:space="preserve">MS-01 › PP-03</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1560,7 +1561,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MF-02 › PP-01</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1591,7 +1592,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MF-03 › PP-01</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1622,7 +1623,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MG-01 › PP-01</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1653,7 +1654,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-02 › PP-01</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1788,7 +1789,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1824,7 +1825,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-03</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1860,7 +1861,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01/AT-02</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-02</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2195,7 +2196,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2228,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2260,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01; MS-01/PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-01; MS-01 › PP-02</t>
         </is>
       </c>
     </row>
@@ -17625,585 +17626,807 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF155BCB"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordem</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telefone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade_Organica</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo Andrade Costa</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcelo.costa@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4710</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luciana Ferreira Dias</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">luciana.dias@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4820</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrícia Moreira Lopes</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patricia.lopes@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4430</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rodrigo Nascimento Farias</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodrigo.farias@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4900</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
+      <formula1>Siglas!$A$2:$A$421</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="26" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trilha</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Codigo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Organica_Responsavel</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Entregas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Beneficiarios</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Partes_Interessadas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trilha</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="str">
+        <f>=B2</f>
+        <v>MG-01</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MG-01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão Estratégica e Governança</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerencial</t>
         </is>
       </c>
-      <c r="D2" s="7">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Formulação, desdobramento e monitoramento da estratégia corporativa, da governança e do desempenho institucional.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Garantir que a atuação da Companhia esteja alinhada à estratégia, com decisões baseadas em evidências.</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Plano Estratégico; Plano de Ação Anual; Relatórios de desempenho</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Diretoria Executiva; Conselho de Administração; Unidades internas</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ministério supervisor; Órgãos de controle; Sociedade</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
         </is>
       </c>
-      <c r="N2" s="8" t="str">
-        <f>=A2</f>
-        <v>MG-01</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="str">
+        <f>=B3</f>
+        <v>MG-02</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MG-02</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão de Riscos, Integridade e Controles</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerencial</t>
         </is>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Identificação, avaliação e tratamento de riscos corporativos, integridade e controles internos (2ª linha).</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Assegurar razoável segurança para o alcance dos objetivos institucionais.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Política de Gestão de Riscos; Matriz de riscos corporativa; Plano de integridade</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta administração; Gestores de 1ª linha</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Auditoria interna; CGU; TCU</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Sistema de gestão de riscos</t>
         </is>
       </c>
-      <c r="N3" s="8" t="str">
-        <f>=A3</f>
-        <v>MG-02</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="str">
+        <f>=B4</f>
+        <v>MF-01</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MF-01</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Desenvolvimento Territorial e Estruturação Produtiva</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Finalístico</t>
         </is>
       </c>
-      <c r="D4" s="7">
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">AR/GDT</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Apoio a arranjos produtivos, inclusão socioeconômica e estruturação de cadeias produtivas nos vales.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Promover o desenvolvimento regional integrado e sustentável.</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Projetos de estruturação produtiva; Convênios e instrumentos de repasse</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Produtores rurais; Cooperativas; Municípios</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Parlamentares; Entes federados; Entidades parceiras</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">TransfereGov; e-Codevasf</t>
         </is>
       </c>
-      <c r="N4" s="8" t="str">
-        <f>=A4</f>
-        <v>MF-01</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="str">
+        <f>=B5</f>
+        <v>MF-02</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MF-02</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão de Empreendimentos de Irrigação</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Finalístico</t>
         </is>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Implantação, operação, manutenção e transferência de gestão de perímetros públicos de irrigação.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ampliar a área irrigada produtiva com sustentabilidade hídrica e econômica.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Perímetros em operação; Água distribuída; Relatórios de O&amp;M</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Irrigantes; Distritos de irrigação</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ANA; Agências estaduais; Associações de usuários</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício); e-Codevasf</t>
         </is>
       </c>
-      <c r="N5" s="8" t="str">
-        <f>=A5</f>
-        <v>MF-02</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="str">
+        <f>=B6</f>
+        <v>MF-03</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MF-03</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Revitalização de Bacias Hidrográficas</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Finalístico</t>
         </is>
       </c>
-      <c r="D6" s="7">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ações de recuperação hidroambiental, segurança hídrica e uso sustentável dos recursos naturais.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Contribuir para a revitalização das bacias dos rios São Francisco e Parnaíba.</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Nascentes recuperadas; Obras hidroambientais; Sistemas de abastecimento</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Comunidades ribeirinhas; Municípios</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Comitês de bacia; MMA; Órgãos ambientais</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; GeoPortal (fictício)</t>
         </is>
       </c>
-      <c r="N6" s="8" t="str">
-        <f>=A6</f>
-        <v>MF-03</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="str">
+        <f>=B7</f>
+        <v>MS-01</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-01</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão de Licitações e Contratos</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Suporte</t>
         </is>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" s="4">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Planejamento das contratações, seleção de fornecedores e gestão dos contratos administrativos da Companhia.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Prover contratações tempestivas, vantajosas e conformes à legislação.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Editais publicados; Contratos firmados; Atas de registro de preços</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Todas as unidades demandantes</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Fornecedores; Assessoria Jurídica; Órgãos de controle; PNCP</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br; PNCP; Painel de Preços; e-Codevasf</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
         </is>
       </c>
-      <c r="N7" s="8" t="str">
-        <f>=A7</f>
-        <v>MS-01</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="str">
+        <f>=B8</f>
+        <v>MS-02</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-02</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Suporte</t>
         </is>
       </c>
-      <c r="D8" s="7">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Provimento, desenvolvimento, remuneração e qualidade de vida do corpo funcional.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Assegurar pessoas qualificadas e engajadas para a missão institucional.</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Empregados admitidos e capacitados; Folha de pagamento</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Empregados; Gestores</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Sindicatos; SEST; Ministério supervisor</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGEP (fictício); e-Codevasf</t>
         </is>
       </c>
-      <c r="N8" s="8" t="str">
-        <f>=A8</f>
-        <v>MS-02</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="8" t="str">
+        <f>=B9</f>
+        <v>MS-03</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-03</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestão de Tecnologia da Informação</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Suporte</t>
         </is>
       </c>
-      <c r="D9" s="4">
+      <c r="E9" s="4">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Planejamento, desenvolvimento, sustentação e segurança dos serviços de TI.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Prover soluções digitais seguras que habilitem os processos de negócio.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sistemas em produção; Serviços de infraestrutura; Suporte ao usuário</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Todas as unidades</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SGD/MGI; Fornecedores de TI</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Service Desk</t>
         </is>
       </c>
-      <c r="N9" s="8" t="str">
-        <f>=A9</f>
-        <v>MS-03</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:O1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
       <formula1>Listas!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="F2:F300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
   </dataValidations>
@@ -18215,7 +18438,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:AM8"/>
+  <dimension ref="A1:AR8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -18224,17 +18447,17 @@
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
     <col min="19" max="19" width="9" customWidth="1"/>
     <col min="20" max="20" width="9" customWidth="1"/>
     <col min="21" max="21" width="9" customWidth="1"/>
@@ -18244,18 +18467,23 @@
     <col min="25" max="25" width="9" customWidth="1"/>
     <col min="26" max="26" width="9" customWidth="1"/>
     <col min="27" max="27" width="9" customWidth="1"/>
-    <col min="28" max="28" width="30" customWidth="1"/>
-    <col min="29" max="29" width="34" customWidth="1"/>
+    <col min="28" max="28" width="9" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
     <col min="30" max="30" width="34" customWidth="1"/>
-    <col min="31" max="31" width="28" customWidth="1"/>
+    <col min="31" max="31" width="34" customWidth="1"/>
     <col min="32" max="32" width="28" customWidth="1"/>
-    <col min="33" max="33" width="20" customWidth="1"/>
-    <col min="34" max="34" width="30" customWidth="1"/>
+    <col min="33" max="33" width="28" customWidth="1"/>
+    <col min="34" max="34" width="20" customWidth="1"/>
     <col min="35" max="35" width="30" customWidth="1"/>
-    <col min="36" max="36" width="40" customWidth="1"/>
-    <col min="37" max="37" width="30" customWidth="1"/>
-    <col min="38" max="38" width="28" customWidth="1"/>
-    <col min="39" max="39" width="24" customWidth="1"/>
+    <col min="36" max="36" width="30" customWidth="1"/>
+    <col min="37" max="37" width="40" customWidth="1"/>
+    <col min="38" max="38" width="30" customWidth="1"/>
+    <col min="39" max="39" width="28" customWidth="1"/>
+    <col min="40" max="40" width="24" customWidth="1"/>
+    <col min="41" max="41" width="24" customWidth="1"/>
+    <col min="42" max="42" width="30" customWidth="1"/>
+    <col min="43" max="43" width="16" customWidth="1"/>
+    <col min="44" max="44" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18296,162 +18524,187 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ponto_Focal_Nugep</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Prioridade</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Complexidade</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Maturidade</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Mapeamento</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Percentual</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicio_Mapeamento</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Prazo_Previsto</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Data_Conclusao</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ultima_Atualizacao</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M1_Conhecer_Processo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M2_Processo_Modelado</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M3_Subprocessos_Modelados</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M4_ASIS_Modelado</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M5_ASIS_Validado</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M6_Procedimento_Aprovado</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M7_Processo_Publicado</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M8_TOBE_Elaborado</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M9_TOBE_Aprovado</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M10_Processo_Transformado</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fornecedores</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Entradas</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Saidas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Beneficiarios</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Processo_ECodevasf</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Processo_ECodevasf_Link</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias_Necessarias</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Proxima_Acao</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pendencia</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gestor_Nome</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gestor_Email</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gestor_Telefone</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gestor_Unidade_Organica</t>
         </is>
       </c>
     </row>
@@ -18490,158 +18743,183 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Definido</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Concluído</t>
         </is>
       </c>
-      <c r="M2" s="9">
-        <f>=IF(COUNTIF(R2:AA2,"Sim")+COUNTIF(R2:AA2,"Em andamento")+COUNTIF(R2:AA2,"Não")=0,0,(COUNTIF(R2:AA2,"Sim")+COUNTIF(R2:AA2,"Em andamento")*0.5)/(COUNTIF(R2:AA2,"Sim")+COUNTIF(R2:AA2,"Em andamento")+COUNTIF(R2:AA2,"Não")))</f>
+      <c r="N2" s="9">
+        <f>=IF(COUNTIF(S2:AB2,"Sim")+COUNTIF(S2:AB2,"Em andamento")+COUNTIF(S2:AB2,"Não")=0,0,(COUNTIF(S2:AB2,"Sim")+COUNTIF(S2:AB2,"Em andamento")*0.5)/(COUNTIF(S2:AB2,"Sim")+COUNTIF(S2:AB2,"Em andamento")+COUNTIF(S2:AB2,"Não")))</f>
         <v>1</v>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">29/05/2026</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">18/05/2026</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10/07/2026</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
+      <c r="W2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="W2" s="7" t="inlineStr">
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="Y2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="inlineStr">
+      <c r="Z2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="Z2" s="7" t="inlineStr">
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="AA2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="AB2" s="6" t="inlineStr">
+      <c r="AC2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Áreas demandantes; Painel de Preços; Fornecedores (cotações)</t>
         </is>
       </c>
-      <c r="AC2" s="6" t="inlineStr">
+      <c r="AD2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DFD; Plano de Contratações Anual; Requisitos da área</t>
         </is>
       </c>
-      <c r="AD2" s="6" t="inlineStr">
+      <c r="AE2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ETP aprovado; TR aprovado; Pesquisa de preços validada</t>
         </is>
       </c>
-      <c r="AE2" s="6" t="inlineStr">
+      <c r="AF2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AA/GLC (Seleção do Fornecedor); Assessoria Jurídica</t>
         </is>
       </c>
-      <c r="AF2" s="6" t="inlineStr">
+      <c r="AG2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
         </is>
       </c>
-      <c r="AG2" s="7" t="inlineStr">
+      <c r="AH2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">59500.000123/2026-11</t>
         </is>
       </c>
-      <c r="AH2" s="6" t="inlineStr">
+      <c r="AI2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=59500000123202611</t>
         </is>
       </c>
-      <c r="AI2" s="6" t="inlineStr">
+      <c r="AJ2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://fluxosti.codevasf.gov.br/incidentes/</t>
         </is>
       </c>
-      <c r="AJ2" s="6" t="inlineStr">
+      <c r="AK2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Elaboração de estudos técnicos e termos de referência; Conhecimento da Lei nº 14.133/2021; Pesquisa e análise de preços de mercado</t>
         </is>
       </c>
-      <c r="AK2" s="6" t="inlineStr">
+      <c r="AL2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Painel de Preços; PNCP</t>
         </is>
       </c>
-      <c r="AL2" s="6" t="inlineStr">
+      <c r="AM2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
+        </is>
+      </c>
+      <c r="AO2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+      <c r="AP2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+      <c r="AR2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -18680,153 +18958,178 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Média</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repetível</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Em andamento</t>
         </is>
       </c>
-      <c r="M3" s="9">
-        <f>=IF(COUNTIF(R3:AA3,"Sim")+COUNTIF(R3:AA3,"Em andamento")+COUNTIF(R3:AA3,"Não")=0,0,(COUNTIF(R3:AA3,"Sim")+COUNTIF(R3:AA3,"Em andamento")*0.5)/(COUNTIF(R3:AA3,"Sim")+COUNTIF(R3:AA3,"Em andamento")+COUNTIF(R3:AA3,"Não")))</f>
+      <c r="N3" s="9">
+        <f>=IF(COUNTIF(S3:AB3,"Sim")+COUNTIF(S3:AB3,"Em andamento")+COUNTIF(S3:AB3,"Não")=0,0,(COUNTIF(S3:AB3,"Sim")+COUNTIF(S3:AB3,"Em andamento")*0.5)/(COUNTIF(S3:AB3,"Sim")+COUNTIF(S3:AB3,"Em andamento")+COUNTIF(S3:AB3,"Não")))</f>
         <v>0.45</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">01/06/2026</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">15/07/2026</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Em andamento</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">P-06.01 (artefatos); Compras.gov.br</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Edital minutado; Parecer jurídico; ETP/TR</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado homologado; Contrato/ata para assinatura</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidades demandantes; Fornecedores</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br; PNCP; e-Codevasf</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">59500.000456/2026-22</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=59500000456202622</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Condução de sessões públicas de licitação; Julgamento de propostas e habilitação; Uso de plataformas de compras governamentais</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Validar AS-IS com o dono do processo (reunião marcada).</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -18865,148 +19168,173 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bruna Souza (UNP)</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerenciado</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Em andamento</t>
         </is>
       </c>
-      <c r="M4" s="9">
-        <f>=IF(COUNTIF(R4:AA4,"Sim")+COUNTIF(R4:AA4,"Em andamento")+COUNTIF(R4:AA4,"Não")=0,0,(COUNTIF(R4:AA4,"Sim")+COUNTIF(R4:AA4,"Em andamento")*0.5)/(COUNTIF(R4:AA4,"Sim")+COUNTIF(R4:AA4,"Em andamento")+COUNTIF(R4:AA4,"Não")))</f>
+      <c r="N4" s="9">
+        <f>=IF(COUNTIF(S4:AB4,"Sim")+COUNTIF(S4:AB4,"Em andamento")+COUNTIF(S4:AB4,"Não")=0,0,(COUNTIF(S4:AB4,"Sim")+COUNTIF(S4:AB4,"Em andamento")*0.5)/(COUNTIF(S4:AB4,"Sim")+COUNTIF(S4:AB4,"Em andamento")+COUNTIF(S4:AB4,"Não")))</f>
         <v>0.2</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15/06/2026</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">30/11/2026</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20/07/2026</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="T4" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="V4" s="7" t="inlineStr">
+      <c r="W4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="W4" s="7" t="inlineStr">
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="X4" s="7" t="inlineStr">
+      <c r="Y4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Y4" s="7" t="inlineStr">
+      <c r="Z4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Z4" s="7" t="inlineStr">
+      <c r="AA4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AA4" s="7" t="inlineStr">
+      <c r="AB4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AB4" s="6" t="inlineStr">
+      <c r="AC4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">P-06.02 (contrato); Fornecedores contratados</t>
         </is>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Contrato assinado; Cronograma; Garantias</t>
         </is>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Objeto recebido; Pagamentos efetuados; Termo de encerramento</t>
         </is>
       </c>
-      <c r="AE4" s="6" t="inlineStr">
+      <c r="AF4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidades demandantes; Fornecedores</t>
         </is>
       </c>
-      <c r="AF4" s="6" t="inlineStr">
+      <c r="AG4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
-      <c r="AG4" s="7" t="inlineStr">
+      <c r="AH4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">59500.000789/2026-33</t>
         </is>
       </c>
-      <c r="AH4" s="6" t="inlineStr">
+      <c r="AI4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=59500000789202633</t>
         </is>
       </c>
-      <c r="AJ4" s="6" t="inlineStr">
+      <c r="AK4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Fiscalização técnica e administrativa de contratos; Gestão de medições e pagamentos; Aplicação de sanções administrativas</t>
         </is>
       </c>
-      <c r="AK4" s="6" t="inlineStr">
+      <c r="AL4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
-      <c r="AL4" s="6" t="inlineStr">
+      <c r="AM4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Concluir modelagem AS-IS das medições e pagamentos.</t>
+        </is>
+      </c>
+      <c r="AO4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+      <c r="AP4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+      <c r="AR4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -19045,148 +19373,173 @@
           <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Eduardo Martins (UNP)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Média</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicial</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Em andamento</t>
         </is>
       </c>
-      <c r="M5" s="9">
-        <f>=IF(COUNTIF(R5:AA5,"Sim")+COUNTIF(R5:AA5,"Em andamento")+COUNTIF(R5:AA5,"Não")=0,0,(COUNTIF(R5:AA5,"Sim")+COUNTIF(R5:AA5,"Em andamento")*0.5)/(COUNTIF(R5:AA5,"Sim")+COUNTIF(R5:AA5,"Em andamento")+COUNTIF(R5:AA5,"Não")))</f>
+      <c r="N5" s="9">
+        <f>=IF(COUNTIF(S5:AB5,"Sim")+COUNTIF(S5:AB5,"Em andamento")+COUNTIF(S5:AB5,"Não")=0,0,(COUNTIF(S5:AB5,"Sim")+COUNTIF(S5:AB5,"Em andamento")*0.5)/(COUNTIF(S5:AB5,"Sim")+COUNTIF(S5:AB5,"Em andamento")+COUNTIF(S5:AB5,"Não")))</f>
         <v>0.3</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">04/05/2026</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">30/10/2026</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">12/07/2026</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ANA (outorgas); Distritos de irrigação</t>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Outorga de uso; Demanda de irrigação; Plano de cultivo</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Água distribuída; Infraestrutura mantida; Relatórios de O&amp;M</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AF5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Irrigantes; Distritos</t>
         </is>
       </c>
-      <c r="AF5" s="3" t="inlineStr">
+      <c r="AG5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício); e-Codevasf</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">59500.000901/2026-44</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
+      <c r="AI5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=59500000901202644</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="inlineStr">
+      <c r="AK5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Operação de sistemas hidráulicos; Manutenção de infraestrutura de irrigação; Relacionamento com associações de irrigantes</t>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
       </c>
-      <c r="AL5" s="3" t="inlineStr">
+      <c r="AM5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Agendar oficina de validação do AS-IS com o distrito.</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcelo Andrade Costa</t>
+        </is>
+      </c>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcelo.costa@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4710</t>
+        </is>
+      </c>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
     </row>
@@ -19225,128 +19578,153 @@
           <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eduardo Martins (UNP)</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Média</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Média</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicial</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não iniciado</t>
         </is>
       </c>
-      <c r="M6" s="9">
-        <f>=IF(COUNTIF(R6:AA6,"Sim")+COUNTIF(R6:AA6,"Em andamento")+COUNTIF(R6:AA6,"Não")=0,0,(COUNTIF(R6:AA6,"Sim")+COUNTIF(R6:AA6,"Em andamento")*0.5)/(COUNTIF(R6:AA6,"Sim")+COUNTIF(R6:AA6,"Em andamento")+COUNTIF(R6:AA6,"Não")))</f>
+      <c r="N6" s="9">
+        <f>=IF(COUNTIF(S6:AB6,"Sim")+COUNTIF(S6:AB6,"Em andamento")+COUNTIF(S6:AB6,"Não")=0,0,(COUNTIF(S6:AB6,"Sim")+COUNTIF(S6:AB6,"Em andamento")*0.5)/(COUNTIF(S6:AB6,"Sim")+COUNTIF(S6:AB6,"Em andamento")+COUNTIF(S6:AB6,"Não")))</f>
         <v>0</v>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">31/03/2027</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">01/07/2026</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="T6" s="7" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="U6" s="7" t="inlineStr">
+      <c r="V6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="V6" s="7" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="Y6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Y6" s="7" t="inlineStr">
+      <c r="Z6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Z6" s="7" t="inlineStr">
+      <c r="AA6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AA6" s="7" t="inlineStr">
+      <c r="AB6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AB6" s="6" t="inlineStr">
+      <c r="AC6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Municípios; Comitês de bacia</t>
         </is>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Diagnóstico hidroambiental; Termos de cooperação</t>
         </is>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Nascentes recuperadas; Relatórios de monitoramento</t>
         </is>
       </c>
-      <c r="AE6" s="6" t="inlineStr">
+      <c r="AF6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Comunidades; Órgãos ambientais</t>
         </is>
       </c>
-      <c r="AF6" s="6" t="inlineStr">
+      <c r="AG6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; GeoPortal (fictício)</t>
         </is>
       </c>
-      <c r="AJ6" s="6" t="inlineStr">
+      <c r="AK6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Diagnóstico e recuperação de áreas degradadas; Noções de engenharia ambiental; Articulação com comunidades e órgãos ambientais</t>
         </is>
       </c>
-      <c r="AL6" s="6" t="inlineStr">
+      <c r="AM6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Enviar formulário de levantamento à área (previsto ago/2026).</t>
+        </is>
+      </c>
+      <c r="AO6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luciana Ferreira Dias</t>
+        </is>
+      </c>
+      <c r="AP6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">luciana.dias@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4820</t>
+        </is>
+      </c>
+      <c r="AR6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GRB</t>
         </is>
       </c>
     </row>
@@ -19385,148 +19763,173 @@
           <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gustavo Pereira (UNP)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Média</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Otimizado</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Concluído</t>
         </is>
       </c>
-      <c r="M7" s="9">
-        <f>=IF(COUNTIF(R7:AA7,"Sim")+COUNTIF(R7:AA7,"Em andamento")+COUNTIF(R7:AA7,"Não")=0,0,(COUNTIF(R7:AA7,"Sim")+COUNTIF(R7:AA7,"Em andamento")*0.5)/(COUNTIF(R7:AA7,"Sim")+COUNTIF(R7:AA7,"Em andamento")+COUNTIF(R7:AA7,"Não")))</f>
+      <c r="N7" s="9">
+        <f>=IF(COUNTIF(S7:AB7,"Sim")+COUNTIF(S7:AB7,"Em andamento")+COUNTIF(S7:AB7,"Não")=0,0,(COUNTIF(S7:AB7,"Sim")+COUNTIF(S7:AB7,"Em andamento")*0.5)/(COUNTIF(S7:AB7,"Sim")+COUNTIF(S7:AB7,"Em andamento")+COUNTIF(S7:AB7,"Não")))</f>
         <v>1</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">01/09/2025</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">27/02/2026</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20/02/2026</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">30/06/2026</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Diretoria; Unidades</t>
         </is>
       </c>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Diretrizes de governo; Diagnóstico institucional</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Plano Estratégico; Painel de indicadores; RAG</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AF7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Diretoria Executiva; Conselhos</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="inlineStr">
+      <c r="AG7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">59500.000015/2025-77</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
+      <c r="AI7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=59500000015202577</t>
         </is>
       </c>
-      <c r="AJ7" s="3" t="inlineStr">
+      <c r="AK7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Planejamento estratégico e gestão por indicadores; Facilitação de oficinas; Análise de dados institucionais</t>
         </is>
       </c>
-      <c r="AL7" s="3" t="inlineStr">
+      <c r="AM7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ciclo de monitoramento trimestral (próximo: set/2026).</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrícia Moreira Lopes</t>
+        </is>
+      </c>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patricia.lopes@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4430</t>
+        </is>
+      </c>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE</t>
         </is>
       </c>
     </row>
@@ -19565,157 +19968,179 @@
           <t xml:space="preserve">AG/GGP</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bruna Souza (UNP)</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Baixa</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Baixa</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicial</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não iniciado</t>
         </is>
       </c>
-      <c r="M8" s="9">
-        <f>=IF(COUNTIF(R8:AA8,"Sim")+COUNTIF(R8:AA8,"Em andamento")+COUNTIF(R8:AA8,"Não")=0,0,(COUNTIF(R8:AA8,"Sim")+COUNTIF(R8:AA8,"Em andamento")*0.5)/(COUNTIF(R8:AA8,"Sim")+COUNTIF(R8:AA8,"Em andamento")+COUNTIF(R8:AA8,"Não")))</f>
+      <c r="N8" s="9">
+        <f>=IF(COUNTIF(S8:AB8,"Sim")+COUNTIF(S8:AB8,"Em andamento")+COUNTIF(S8:AB8,"Não")=0,0,(COUNTIF(S8:AB8,"Sim")+COUNTIF(S8:AB8,"Em andamento")*0.5)/(COUNTIF(S8:AB8,"Sim")+COUNTIF(S8:AB8,"Em andamento")+COUNTIF(S8:AB8,"Não")))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">30/06/2027</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">15/06/2026</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="T8" s="7" t="inlineStr">
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="V8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="V8" s="7" t="inlineStr">
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="Y8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Y8" s="7" t="inlineStr">
+      <c r="Z8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="Z8" s="7" t="inlineStr">
+      <c r="AA8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AA8" s="7" t="inlineStr">
+      <c r="AB8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Não</t>
         </is>
       </c>
-      <c r="AB8" s="6" t="inlineStr">
+      <c r="AC8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Banca do concurso; Candidatos</t>
         </is>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Resultado homologado; Documentação do candidato</t>
         </is>
       </c>
-      <c r="AD8" s="6" t="inlineStr">
+      <c r="AE8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Empregado admitido e integrado</t>
         </is>
       </c>
-      <c r="AE8" s="6" t="inlineStr">
+      <c r="AF8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Novos empregados; Unidades de lotação</t>
         </is>
       </c>
-      <c r="AF8" s="6" t="inlineStr">
+      <c r="AG8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGEP (fictício); e-Codevasf</t>
         </is>
       </c>
-      <c r="AJ8" s="6" t="inlineStr">
+      <c r="AK8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Rotinas de admissão e legislação trabalhista (CLT); Condução de processos de integração; Uso de sistemas de gestão de pessoas</t>
         </is>
       </c>
-      <c r="AL8" s="6" t="inlineStr">
+      <c r="AM8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Aguardando priorização no ciclo 2027.</t>
         </is>
       </c>
+      <c r="AO8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rodrigo Nascimento Farias</t>
+        </is>
+      </c>
+      <c r="AP8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodrigo.farias@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="AQ8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4900</t>
+        </is>
+      </c>
+      <c r="AR8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AG/GGP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM1"/>
-  <dataValidations count="17">
+  <autoFilter ref="A1:AR1"/>
+  <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="B2:B300">
       <formula1>Macroprocessos!$A$2:$A$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="G2:G300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="H2:H300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>NUGEP!$B$2:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="J2:J300">
       <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="J2:J300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="K2:K300">
       <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="K2:K300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="L2:L300">
       <formula1>Listas!$E$2:$E$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="L2:L300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="M2:M300">
       <formula1>Listas!$B$2:$B$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="R2:R300">
-      <formula1>Listas!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="S2:S300">
       <formula1>Listas!$G$2:$G$5</formula1>
@@ -19744,6 +20169,12 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="AA2:AA300">
       <formula1>Listas!$G$2:$G$5</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="AB2:AB300">
+      <formula1>Listas!$G$2:$G$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="AR2:AR300">
+      <formula1>Siglas!$A$2:$A$421</formula1>
+    </dataValidation>
   </dataValidations>
 </worksheet>
 </file>
@@ -19753,7 +20184,7 @@
   <sheetPr>
     <tabColor rgb="FF0040B4"/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R7"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -19765,13 +20196,14 @@
     <col min="8" max="8" width="44" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
     <col min="14" max="14" width="36" customWidth="1"/>
-    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="15" max="15" width="36" customWidth="1"/>
     <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19827,35 +20259,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Reutilizavel</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Reutilizado_Em</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Entradas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Saidas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
@@ -19909,22 +20346,27 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
         </is>
@@ -19978,17 +20420,22 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ETP aprovado; Modelos padronizados de TR</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">TR aprovado e validado juridicamente</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
         </is>
@@ -20042,22 +20489,27 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">TR validado; Fontes de preços admitidas</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Relatório de pesquisa de preços; Mapa comparativo</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Painel de Preços; PNCP; e-Codevasf</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Painel de Preços; PNCP</t>
         </is>
@@ -20113,25 +20565,30 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MS-01/PP-02; MF-02/PP-01</t>
-        </is>
-      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">MS-01 › PP-02; MF-02 › PP-01</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Amostra de preços coletados na pesquisa</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Valores discrepantes identificados e justificados</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Planilha padrão; e-Codevasf</t>
         </is>
@@ -20185,17 +20642,22 @@
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Edital publicado; Propostas dos licitantes</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ata da sessão; Resultado por item</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br</t>
         </is>
@@ -20249,29 +20711,34 @@
           <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Outorga de uso; Demanda de irrigação</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Programação hídrica executada; Registros de volume</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="J2:J300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="K2:K300">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="L2:L300">
       <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -22094,7 +22561,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F2" s="7">
@@ -22148,7 +22615,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F3" s="4">
@@ -22197,7 +22664,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F4" s="7">
@@ -22241,7 +22708,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F5" s="4">
@@ -22290,7 +22757,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01; MS-01/PP-01/SP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01; MS-01 › PP-01 › SP-03</t>
         </is>
       </c>
       <c r="F6" s="7">
@@ -22334,7 +22801,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01</t>
         </is>
       </c>
       <c r="F7" s="4">
@@ -22378,7 +22845,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-03; MS-01/PP-01/SP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-03; MS-01 › PP-01 › SP-01</t>
         </is>
       </c>
       <c r="F8" s="7">
@@ -22476,7 +22943,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01; MS-01/PP-03</t>
+          <t xml:space="preserve">MS-01 › PP-01; MS-01 › PP-03</t>
         </is>
       </c>
       <c r="F10" s="7">
@@ -22525,7 +22992,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-02</t>
         </is>
       </c>
       <c r="F11" s="4">
@@ -22569,7 +23036,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F12" s="7">
@@ -22613,7 +23080,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01/AT-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
         </is>
       </c>
       <c r="F13" s="4">
@@ -22657,7 +23124,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F14" s="7">
@@ -22701,7 +23168,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F15" s="4">
@@ -22745,7 +23212,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="F16" s="7">
@@ -23260,7 +23727,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -23330,7 +23797,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -23400,7 +23867,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-03</t>
+          <t xml:space="preserve">MS-01 › PP-03</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -23470,7 +23937,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -23540,7 +24007,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -23605,7 +24072,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-02</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -23740,7 +24207,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01/SP-01/AT-01</t>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -23810,7 +24277,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -297,7 +297,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="str">
-        <f>=IF(LEFT(D2,2)="MG","Macroprocesso",IF(LEFT(D2,2)="MF","Macroprocesso",IF(LEFT(D2,2)="MS","Macroprocesso",IF(LEFT(D2,2)="PP","Processo",IF(OR(LEFT(D2,3)="SP-",ISNUMBER(SEARCH("/SP-",D2))),"Subprocesso",IF(LEFT(D2,2)="AT","Atividade",IF(LEFT(D2,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D2)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D2)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D2)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D2)),"Processo",IF(OR(LEFT(D2,2)="MG",LEFT(D2,2)="MF",LEFT(D2,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -351,8 +351,8 @@
         </is>
       </c>
       <c r="C3" s="8" t="str">
-        <f>=IF(LEFT(D3,2)="MG","Macroprocesso",IF(LEFT(D3,2)="MF","Macroprocesso",IF(LEFT(D3,2)="MS","Macroprocesso",IF(LEFT(D3,2)="PP","Processo",IF(OR(LEFT(D3,3)="SP-",ISNUMBER(SEARCH("/SP-",D3))),"Subprocesso",IF(LEFT(D3,2)="AT","Atividade",IF(LEFT(D3,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D3)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D3)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D3)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D3)),"Processo",IF(OR(LEFT(D3,2)="MG",LEFT(D3,2)="MF",LEFT(D3,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -405,8 +405,8 @@
         </is>
       </c>
       <c r="C4" s="8" t="str">
-        <f>=IF(LEFT(D4,2)="MG","Macroprocesso",IF(LEFT(D4,2)="MF","Macroprocesso",IF(LEFT(D4,2)="MS","Macroprocesso",IF(LEFT(D4,2)="PP","Processo",IF(OR(LEFT(D4,3)="SP-",ISNUMBER(SEARCH("/SP-",D4))),"Subprocesso",IF(LEFT(D4,2)="AT","Atividade",IF(LEFT(D4,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D4)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D4)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D4)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D4)),"Processo",IF(OR(LEFT(D4,2)="MG",LEFT(D4,2)="MF",LEFT(D4,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -459,8 +459,8 @@
         </is>
       </c>
       <c r="C5" s="8" t="str">
-        <f>=IF(LEFT(D5,2)="MG","Macroprocesso",IF(LEFT(D5,2)="MF","Macroprocesso",IF(LEFT(D5,2)="MS","Macroprocesso",IF(LEFT(D5,2)="PP","Processo",IF(OR(LEFT(D5,3)="SP-",ISNUMBER(SEARCH("/SP-",D5))),"Subprocesso",IF(LEFT(D5,2)="AT","Atividade",IF(LEFT(D5,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D5)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D5)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D5)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D5)),"Processo",IF(OR(LEFT(D5,2)="MG",LEFT(D5,2)="MF",LEFT(D5,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -513,8 +513,8 @@
         </is>
       </c>
       <c r="C6" s="8" t="str">
-        <f>=IF(LEFT(D6,2)="MG","Macroprocesso",IF(LEFT(D6,2)="MF","Macroprocesso",IF(LEFT(D6,2)="MS","Macroprocesso",IF(LEFT(D6,2)="PP","Processo",IF(OR(LEFT(D6,3)="SP-",ISNUMBER(SEARCH("/SP-",D6))),"Subprocesso",IF(LEFT(D6,2)="AT","Atividade",IF(LEFT(D6,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D6)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D6)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D6)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D6)),"Processo",IF(OR(LEFT(D6,2)="MG",LEFT(D6,2)="MF",LEFT(D6,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="str">
-        <f>=IF(LEFT(D7,2)="MG","Macroprocesso",IF(LEFT(D7,2)="MF","Macroprocesso",IF(LEFT(D7,2)="MS","Macroprocesso",IF(LEFT(D7,2)="PP","Processo",IF(OR(LEFT(D7,3)="SP-",ISNUMBER(SEARCH("/SP-",D7))),"Subprocesso",IF(LEFT(D7,2)="AT","Atividade",IF(LEFT(D7,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D7)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D7)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D7)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D7)),"Processo",IF(OR(LEFT(D7,2)="MG",LEFT(D7,2)="MF",LEFT(D7,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -621,8 +621,8 @@
         </is>
       </c>
       <c r="C8" s="8" t="str">
-        <f>=IF(LEFT(D8,2)="MG","Macroprocesso",IF(LEFT(D8,2)="MF","Macroprocesso",IF(LEFT(D8,2)="MS","Macroprocesso",IF(LEFT(D8,2)="PP","Processo",IF(OR(LEFT(D8,3)="SP-",ISNUMBER(SEARCH("/SP-",D8))),"Subprocesso",IF(LEFT(D8,2)="AT","Atividade",IF(LEFT(D8,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D8)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D8)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D8)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D8)),"Processo",IF(OR(LEFT(D8,2)="MG",LEFT(D8,2)="MF",LEFT(D8,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
@@ -675,8 +675,8 @@
         </is>
       </c>
       <c r="C9" s="8" t="str">
-        <f>=IF(LEFT(D9,2)="MG","Macroprocesso",IF(LEFT(D9,2)="MF","Macroprocesso",IF(LEFT(D9,2)="MS","Macroprocesso",IF(LEFT(D9,2)="PP","Processo",IF(OR(LEFT(D9,3)="SP-",ISNUMBER(SEARCH("/SP-",D9))),"Subprocesso",IF(LEFT(D9,2)="AT","Atividade",IF(LEFT(D9,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D9)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D9)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D9)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D9)),"Processo",IF(OR(LEFT(D9,2)="MG",LEFT(D9,2)="MF",LEFT(D9,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="str">
-        <f>=IF(LEFT(D10,2)="MG","Macroprocesso",IF(LEFT(D10,2)="MF","Macroprocesso",IF(LEFT(D10,2)="MS","Macroprocesso",IF(LEFT(D10,2)="PP","Processo",IF(OR(LEFT(D10,3)="SP-",ISNUMBER(SEARCH("/SP-",D10))),"Subprocesso",IF(LEFT(D10,2)="AT","Atividade",IF(LEFT(D10,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D10)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D10)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D10)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D10)),"Processo",IF(OR(LEFT(D10,2)="MG",LEFT(D10,2)="MF",LEFT(D10,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -783,8 +783,8 @@
         </is>
       </c>
       <c r="C11" s="8" t="str">
-        <f>=IF(LEFT(D11,2)="MG","Macroprocesso",IF(LEFT(D11,2)="MF","Macroprocesso",IF(LEFT(D11,2)="MS","Macroprocesso",IF(LEFT(D11,2)="PP","Processo",IF(OR(LEFT(D11,3)="SP-",ISNUMBER(SEARCH("/SP-",D11))),"Subprocesso",IF(LEFT(D11,2)="AT","Atividade",IF(LEFT(D11,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D11)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D11)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D11)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D11)),"Processo",IF(OR(LEFT(D11,2)="MG",LEFT(D11,2)="MF",LEFT(D11,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -842,8 +842,8 @@
         </is>
       </c>
       <c r="C12" s="8" t="str">
-        <f>=IF(LEFT(D12,2)="MG","Macroprocesso",IF(LEFT(D12,2)="MF","Macroprocesso",IF(LEFT(D12,2)="MS","Macroprocesso",IF(LEFT(D12,2)="PP","Processo",IF(OR(LEFT(D12,3)="SP-",ISNUMBER(SEARCH("/SP-",D12))),"Subprocesso",IF(LEFT(D12,2)="AT","Atividade",IF(LEFT(D12,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D12)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D12)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D12)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D12)),"Processo",IF(OR(LEFT(D12,2)="MG",LEFT(D12,2)="MF",LEFT(D12,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -1277,8 +1277,8 @@
         </is>
       </c>
       <c r="B2" s="8" t="str">
-        <f>=IF(LEFT(C2,2)="MG","Macroprocesso",IF(LEFT(C2,2)="MF","Macroprocesso",IF(LEFT(C2,2)="MS","Macroprocesso",IF(LEFT(C2,2)="PP","Processo",IF(OR(LEFT(C2,3)="SP-",ISNUMBER(SEARCH("/SP-",C2))),"Subprocesso",IF(LEFT(C2,2)="AT","Atividade",IF(LEFT(C2,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C2)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C2)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C2)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C2)),"Processo",IF(OR(LEFT(C2,2)="MG",LEFT(C2,2)="MF",LEFT(C2,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -1308,8 +1308,8 @@
         </is>
       </c>
       <c r="B3" s="8" t="str">
-        <f>=IF(LEFT(C3,2)="MG","Macroprocesso",IF(LEFT(C3,2)="MF","Macroprocesso",IF(LEFT(C3,2)="MS","Macroprocesso",IF(LEFT(C3,2)="PP","Processo",IF(OR(LEFT(C3,3)="SP-",ISNUMBER(SEARCH("/SP-",C3))),"Subprocesso",IF(LEFT(C3,2)="AT","Atividade",IF(LEFT(C3,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C3)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C3)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C3)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C3)),"Processo",IF(OR(LEFT(C3,2)="MG",LEFT(C3,2)="MF",LEFT(C3,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -1339,8 +1339,8 @@
         </is>
       </c>
       <c r="B4" s="8" t="str">
-        <f>=IF(LEFT(C4,2)="MG","Macroprocesso",IF(LEFT(C4,2)="MF","Macroprocesso",IF(LEFT(C4,2)="MS","Macroprocesso",IF(LEFT(C4,2)="PP","Processo",IF(OR(LEFT(C4,3)="SP-",ISNUMBER(SEARCH("/SP-",C4))),"Subprocesso",IF(LEFT(C4,2)="AT","Atividade",IF(LEFT(C4,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C4)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C4)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C4)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C4)),"Processo",IF(OR(LEFT(C4,2)="MG",LEFT(C4,2)="MF",LEFT(C4,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -1370,8 +1370,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="str">
-        <f>=IF(LEFT(C5,2)="MG","Macroprocesso",IF(LEFT(C5,2)="MF","Macroprocesso",IF(LEFT(C5,2)="MS","Macroprocesso",IF(LEFT(C5,2)="PP","Processo",IF(OR(LEFT(C5,3)="SP-",ISNUMBER(SEARCH("/SP-",C5))),"Subprocesso",IF(LEFT(C5,2)="AT","Atividade",IF(LEFT(C5,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C5)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C5)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C5)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C5)),"Processo",IF(OR(LEFT(C5,2)="MG",LEFT(C5,2)="MF",LEFT(C5,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -1401,8 +1401,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="str">
-        <f>=IF(LEFT(C6,2)="MG","Macroprocesso",IF(LEFT(C6,2)="MF","Macroprocesso",IF(LEFT(C6,2)="MS","Macroprocesso",IF(LEFT(C6,2)="PP","Processo",IF(OR(LEFT(C6,3)="SP-",ISNUMBER(SEARCH("/SP-",C6))),"Subprocesso",IF(LEFT(C6,2)="AT","Atividade",IF(LEFT(C6,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C6)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C6)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C6)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C6)),"Processo",IF(OR(LEFT(C6,2)="MG",LEFT(C6,2)="MF",LEFT(C6,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -1432,8 +1432,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="str">
-        <f>=IF(LEFT(C7,2)="MG","Macroprocesso",IF(LEFT(C7,2)="MF","Macroprocesso",IF(LEFT(C7,2)="MS","Macroprocesso",IF(LEFT(C7,2)="PP","Processo",IF(OR(LEFT(C7,3)="SP-",ISNUMBER(SEARCH("/SP-",C7))),"Subprocesso",IF(LEFT(C7,2)="AT","Atividade",IF(LEFT(C7,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C7)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C7)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C7)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C7)),"Processo",IF(OR(LEFT(C7,2)="MG",LEFT(C7,2)="MF",LEFT(C7,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -1463,8 +1463,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="str">
-        <f>=IF(LEFT(C8,2)="MG","Macroprocesso",IF(LEFT(C8,2)="MF","Macroprocesso",IF(LEFT(C8,2)="MS","Macroprocesso",IF(LEFT(C8,2)="PP","Processo",IF(OR(LEFT(C8,3)="SP-",ISNUMBER(SEARCH("/SP-",C8))),"Subprocesso",IF(LEFT(C8,2)="AT","Atividade",IF(LEFT(C8,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C8)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C8)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C8)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C8)),"Processo",IF(OR(LEFT(C8,2)="MG",LEFT(C8,2)="MF",LEFT(C8,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Atividade</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -1494,8 +1494,8 @@
         </is>
       </c>
       <c r="B9" s="8" t="str">
-        <f>=IF(LEFT(C9,2)="MG","Macroprocesso",IF(LEFT(C9,2)="MF","Macroprocesso",IF(LEFT(C9,2)="MS","Macroprocesso",IF(LEFT(C9,2)="PP","Processo",IF(OR(LEFT(C9,3)="SP-",ISNUMBER(SEARCH("/SP-",C9))),"Subprocesso",IF(LEFT(C9,2)="AT","Atividade",IF(LEFT(C9,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C9)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C9)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C9)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C9)),"Processo",IF(OR(LEFT(C9,2)="MG",LEFT(C9,2)="MF",LEFT(C9,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1525,8 +1525,8 @@
         </is>
       </c>
       <c r="B10" s="8" t="str">
-        <f>=IF(LEFT(C10,2)="MG","Macroprocesso",IF(LEFT(C10,2)="MF","Macroprocesso",IF(LEFT(C10,2)="MS","Macroprocesso",IF(LEFT(C10,2)="PP","Processo",IF(OR(LEFT(C10,3)="SP-",ISNUMBER(SEARCH("/SP-",C10))),"Subprocesso",IF(LEFT(C10,2)="AT","Atividade",IF(LEFT(C10,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C10)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C10)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C10)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C10)),"Processo",IF(OR(LEFT(C10,2)="MG",LEFT(C10,2)="MF",LEFT(C10,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -1556,8 +1556,8 @@
         </is>
       </c>
       <c r="B11" s="8" t="str">
-        <f>=IF(LEFT(C11,2)="MG","Macroprocesso",IF(LEFT(C11,2)="MF","Macroprocesso",IF(LEFT(C11,2)="MS","Macroprocesso",IF(LEFT(C11,2)="PP","Processo",IF(OR(LEFT(C11,3)="SP-",ISNUMBER(SEARCH("/SP-",C11))),"Subprocesso",IF(LEFT(C11,2)="AT","Atividade",IF(LEFT(C11,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C11)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C11)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C11)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C11)),"Processo",IF(OR(LEFT(C11,2)="MG",LEFT(C11,2)="MF",LEFT(C11,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1587,8 +1587,8 @@
         </is>
       </c>
       <c r="B12" s="8" t="str">
-        <f>=IF(LEFT(C12,2)="MG","Macroprocesso",IF(LEFT(C12,2)="MF","Macroprocesso",IF(LEFT(C12,2)="MS","Macroprocesso",IF(LEFT(C12,2)="PP","Processo",IF(OR(LEFT(C12,3)="SP-",ISNUMBER(SEARCH("/SP-",C12))),"Subprocesso",IF(LEFT(C12,2)="AT","Atividade",IF(LEFT(C12,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C12)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C12)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C12)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C12)),"Processo",IF(OR(LEFT(C12,2)="MG",LEFT(C12,2)="MF",LEFT(C12,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1618,8 +1618,8 @@
         </is>
       </c>
       <c r="B13" s="8" t="str">
-        <f>=IF(LEFT(C13,2)="MG","Macroprocesso",IF(LEFT(C13,2)="MF","Macroprocesso",IF(LEFT(C13,2)="MS","Macroprocesso",IF(LEFT(C13,2)="PP","Processo",IF(OR(LEFT(C13,3)="SP-",ISNUMBER(SEARCH("/SP-",C13))),"Subprocesso",IF(LEFT(C13,2)="AT","Atividade",IF(LEFT(C13,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C13)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C13)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C13)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C13)),"Processo",IF(OR(LEFT(C13,2)="MG",LEFT(C13,2)="MF",LEFT(C13,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -1649,8 +1649,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="str">
-        <f>=IF(LEFT(C14,2)="MG","Macroprocesso",IF(LEFT(C14,2)="MF","Macroprocesso",IF(LEFT(C14,2)="MS","Macroprocesso",IF(LEFT(C14,2)="PP","Processo",IF(OR(LEFT(C14,3)="SP-",ISNUMBER(SEARCH("/SP-",C14))),"Subprocesso",IF(LEFT(C14,2)="AT","Atividade",IF(LEFT(C14,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C14)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C14)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C14)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C14)),"Processo",IF(OR(LEFT(C14,2)="MG",LEFT(C14,2)="MF",LEFT(C14,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="str">
-        <f>=IF(LEFT(D2,2)="MG","Macroprocesso",IF(LEFT(D2,2)="MF","Macroprocesso",IF(LEFT(D2,2)="MS","Macroprocesso",IF(LEFT(D2,2)="PP","Processo",IF(OR(LEFT(D2,3)="SP-",ISNUMBER(SEARCH("/SP-",D2))),"Subprocesso",IF(LEFT(D2,2)="AT","Atividade",IF(LEFT(D2,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D2)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D2)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D2)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D2)),"Processo",IF(OR(LEFT(D2,2)="MG",LEFT(D2,2)="MF",LEFT(D2,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1784,8 +1784,8 @@
         </is>
       </c>
       <c r="C3" s="8" t="str">
-        <f>=IF(LEFT(D3,2)="MG","Macroprocesso",IF(LEFT(D3,2)="MF","Macroprocesso",IF(LEFT(D3,2)="MS","Macroprocesso",IF(LEFT(D3,2)="PP","Processo",IF(OR(LEFT(D3,3)="SP-",ISNUMBER(SEARCH("/SP-",D3))),"Subprocesso",IF(LEFT(D3,2)="AT","Atividade",IF(LEFT(D3,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D3)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D3)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D3)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D3)),"Processo",IF(OR(LEFT(D3,2)="MG",LEFT(D3,2)="MF",LEFT(D3,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -1820,8 +1820,8 @@
         </is>
       </c>
       <c r="C4" s="8" t="str">
-        <f>=IF(LEFT(D4,2)="MG","Macroprocesso",IF(LEFT(D4,2)="MF","Macroprocesso",IF(LEFT(D4,2)="MS","Macroprocesso",IF(LEFT(D4,2)="PP","Processo",IF(OR(LEFT(D4,3)="SP-",ISNUMBER(SEARCH("/SP-",D4))),"Subprocesso",IF(LEFT(D4,2)="AT","Atividade",IF(LEFT(D4,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D4)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D4)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D4)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D4)),"Processo",IF(OR(LEFT(D4,2)="MG",LEFT(D4,2)="MF",LEFT(D4,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -1856,8 +1856,8 @@
         </is>
       </c>
       <c r="C5" s="8" t="str">
-        <f>=IF(LEFT(D5,2)="MG","Macroprocesso",IF(LEFT(D5,2)="MF","Macroprocesso",IF(LEFT(D5,2)="MS","Macroprocesso",IF(LEFT(D5,2)="PP","Processo",IF(OR(LEFT(D5,3)="SP-",ISNUMBER(SEARCH("/SP-",D5))),"Subprocesso",IF(LEFT(D5,2)="AT","Atividade",IF(LEFT(D5,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",D5)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",D5)),"Atividade",IF(ISNUMBER(SEARCH("SP-",D5)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",D5)),"Processo",IF(OR(LEFT(D5,2)="MG",LEFT(D5,2)="MF",LEFT(D5,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Atividade</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -22556,8 +22556,8 @@
         </is>
       </c>
       <c r="D2" s="8" t="str">
-        <f>=IF(LEFT(E2,2)="MG","Macroprocesso",IF(LEFT(E2,2)="MF","Macroprocesso",IF(LEFT(E2,2)="MS","Macroprocesso",IF(LEFT(E2,2)="PP","Processo",IF(OR(LEFT(E2,3)="SP-",ISNUMBER(SEARCH("/SP-",E2))),"Subprocesso",IF(LEFT(E2,2)="AT","Atividade",IF(LEFT(E2,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E2)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E2)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E2)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E2)),"Processo",IF(OR(LEFT(E2,2)="MG",LEFT(E2,2)="MF",LEFT(E2,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
@@ -22610,8 +22610,8 @@
         </is>
       </c>
       <c r="D3" s="8" t="str">
-        <f>=IF(LEFT(E3,2)="MG","Macroprocesso",IF(LEFT(E3,2)="MF","Macroprocesso",IF(LEFT(E3,2)="MS","Macroprocesso",IF(LEFT(E3,2)="PP","Processo",IF(OR(LEFT(E3,3)="SP-",ISNUMBER(SEARCH("/SP-",E3))),"Subprocesso",IF(LEFT(E3,2)="AT","Atividade",IF(LEFT(E3,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E3)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E3)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E3)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E3)),"Processo",IF(OR(LEFT(E3,2)="MG",LEFT(E3,2)="MF",LEFT(E3,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -22659,8 +22659,8 @@
         </is>
       </c>
       <c r="D4" s="8" t="str">
-        <f>=IF(LEFT(E4,2)="MG","Macroprocesso",IF(LEFT(E4,2)="MF","Macroprocesso",IF(LEFT(E4,2)="MS","Macroprocesso",IF(LEFT(E4,2)="PP","Processo",IF(OR(LEFT(E4,3)="SP-",ISNUMBER(SEARCH("/SP-",E4))),"Subprocesso",IF(LEFT(E4,2)="AT","Atividade",IF(LEFT(E4,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E4)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E4)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E4)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E4)),"Processo",IF(OR(LEFT(E4,2)="MG",LEFT(E4,2)="MF",LEFT(E4,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
@@ -22703,8 +22703,8 @@
         </is>
       </c>
       <c r="D5" s="8" t="str">
-        <f>=IF(LEFT(E5,2)="MG","Macroprocesso",IF(LEFT(E5,2)="MF","Macroprocesso",IF(LEFT(E5,2)="MS","Macroprocesso",IF(LEFT(E5,2)="PP","Processo",IF(OR(LEFT(E5,3)="SP-",ISNUMBER(SEARCH("/SP-",E5))),"Subprocesso",IF(LEFT(E5,2)="AT","Atividade",IF(LEFT(E5,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E5)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E5)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E5)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E5)),"Processo",IF(OR(LEFT(E5,2)="MG",LEFT(E5,2)="MF",LEFT(E5,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -22752,8 +22752,8 @@
         </is>
       </c>
       <c r="D6" s="8" t="str">
-        <f>=IF(LEFT(E6,2)="MG","Macroprocesso",IF(LEFT(E6,2)="MF","Macroprocesso",IF(LEFT(E6,2)="MS","Macroprocesso",IF(LEFT(E6,2)="PP","Processo",IF(OR(LEFT(E6,3)="SP-",ISNUMBER(SEARCH("/SP-",E6))),"Subprocesso",IF(LEFT(E6,2)="AT","Atividade",IF(LEFT(E6,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E6)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E6)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E6)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E6)),"Processo",IF(OR(LEFT(E6,2)="MG",LEFT(E6,2)="MF",LEFT(E6,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -22796,8 +22796,8 @@
         </is>
       </c>
       <c r="D7" s="8" t="str">
-        <f>=IF(LEFT(E7,2)="MG","Macroprocesso",IF(LEFT(E7,2)="MF","Macroprocesso",IF(LEFT(E7,2)="MS","Macroprocesso",IF(LEFT(E7,2)="PP","Processo",IF(OR(LEFT(E7,3)="SP-",ISNUMBER(SEARCH("/SP-",E7))),"Subprocesso",IF(LEFT(E7,2)="AT","Atividade",IF(LEFT(E7,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E7)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E7)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E7)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E7)),"Processo",IF(OR(LEFT(E7,2)="MG",LEFT(E7,2)="MF",LEFT(E7,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -22840,8 +22840,8 @@
         </is>
       </c>
       <c r="D8" s="8" t="str">
-        <f>=IF(LEFT(E8,2)="MG","Macroprocesso",IF(LEFT(E8,2)="MF","Macroprocesso",IF(LEFT(E8,2)="MS","Macroprocesso",IF(LEFT(E8,2)="PP","Processo",IF(OR(LEFT(E8,3)="SP-",ISNUMBER(SEARCH("/SP-",E8))),"Subprocesso",IF(LEFT(E8,2)="AT","Atividade",IF(LEFT(E8,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E8)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E8)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E8)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E8)),"Processo",IF(OR(LEFT(E8,2)="MG",LEFT(E8,2)="MF",LEFT(E8,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         </is>
       </c>
       <c r="D9" s="8" t="str">
-        <f>=IF(LEFT(E9,2)="MG","Macroprocesso",IF(LEFT(E9,2)="MF","Macroprocesso",IF(LEFT(E9,2)="MS","Macroprocesso",IF(LEFT(E9,2)="PP","Processo",IF(OR(LEFT(E9,3)="SP-",ISNUMBER(SEARCH("/SP-",E9))),"Subprocesso",IF(LEFT(E9,2)="AT","Atividade",IF(LEFT(E9,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E9)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E9)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E9)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E9)),"Processo",IF(OR(LEFT(E9,2)="MG",LEFT(E9,2)="MF",LEFT(E9,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -22938,8 +22938,8 @@
         </is>
       </c>
       <c r="D10" s="8" t="str">
-        <f>=IF(LEFT(E10,2)="MG","Macroprocesso",IF(LEFT(E10,2)="MF","Macroprocesso",IF(LEFT(E10,2)="MS","Macroprocesso",IF(LEFT(E10,2)="PP","Processo",IF(OR(LEFT(E10,3)="SP-",ISNUMBER(SEARCH("/SP-",E10))),"Subprocesso",IF(LEFT(E10,2)="AT","Atividade",IF(LEFT(E10,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E10)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E10)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E10)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E10)),"Processo",IF(OR(LEFT(E10,2)="MG",LEFT(E10,2)="MF",LEFT(E10,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -22987,8 +22987,8 @@
         </is>
       </c>
       <c r="D11" s="8" t="str">
-        <f>=IF(LEFT(E11,2)="MG","Macroprocesso",IF(LEFT(E11,2)="MF","Macroprocesso",IF(LEFT(E11,2)="MS","Macroprocesso",IF(LEFT(E11,2)="PP","Processo",IF(OR(LEFT(E11,3)="SP-",ISNUMBER(SEARCH("/SP-",E11))),"Subprocesso",IF(LEFT(E11,2)="AT","Atividade",IF(LEFT(E11,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E11)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E11)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E11)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E11)),"Processo",IF(OR(LEFT(E11,2)="MG",LEFT(E11,2)="MF",LEFT(E11,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -23031,8 +23031,8 @@
         </is>
       </c>
       <c r="D12" s="8" t="str">
-        <f>=IF(LEFT(E12,2)="MG","Macroprocesso",IF(LEFT(E12,2)="MF","Macroprocesso",IF(LEFT(E12,2)="MS","Macroprocesso",IF(LEFT(E12,2)="PP","Processo",IF(OR(LEFT(E12,3)="SP-",ISNUMBER(SEARCH("/SP-",E12))),"Subprocesso",IF(LEFT(E12,2)="AT","Atividade",IF(LEFT(E12,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E12)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E12)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E12)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E12)),"Processo",IF(OR(LEFT(E12,2)="MG",LEFT(E12,2)="MF",LEFT(E12,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -23075,8 +23075,8 @@
         </is>
       </c>
       <c r="D13" s="8" t="str">
-        <f>=IF(LEFT(E13,2)="MG","Macroprocesso",IF(LEFT(E13,2)="MF","Macroprocesso",IF(LEFT(E13,2)="MS","Macroprocesso",IF(LEFT(E13,2)="PP","Processo",IF(OR(LEFT(E13,3)="SP-",ISNUMBER(SEARCH("/SP-",E13))),"Subprocesso",IF(LEFT(E13,2)="AT","Atividade",IF(LEFT(E13,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E13)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E13)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E13)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E13)),"Processo",IF(OR(LEFT(E13,2)="MG",LEFT(E13,2)="MF",LEFT(E13,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Atividade</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -23119,8 +23119,8 @@
         </is>
       </c>
       <c r="D14" s="8" t="str">
-        <f>=IF(LEFT(E14,2)="MG","Macroprocesso",IF(LEFT(E14,2)="MF","Macroprocesso",IF(LEFT(E14,2)="MS","Macroprocesso",IF(LEFT(E14,2)="PP","Processo",IF(OR(LEFT(E14,3)="SP-",ISNUMBER(SEARCH("/SP-",E14))),"Subprocesso",IF(LEFT(E14,2)="AT","Atividade",IF(LEFT(E14,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E14)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E14)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E14)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E14)),"Processo",IF(OR(LEFT(E14,2)="MG",LEFT(E14,2)="MF",LEFT(E14,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
@@ -23163,8 +23163,8 @@
         </is>
       </c>
       <c r="D15" s="8" t="str">
-        <f>=IF(LEFT(E15,2)="MG","Macroprocesso",IF(LEFT(E15,2)="MF","Macroprocesso",IF(LEFT(E15,2)="MS","Macroprocesso",IF(LEFT(E15,2)="PP","Processo",IF(OR(LEFT(E15,3)="SP-",ISNUMBER(SEARCH("/SP-",E15))),"Subprocesso",IF(LEFT(E15,2)="AT","Atividade",IF(LEFT(E15,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E15)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E15)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E15)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E15)),"Processo",IF(OR(LEFT(E15,2)="MG",LEFT(E15,2)="MF",LEFT(E15,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -23207,8 +23207,8 @@
         </is>
       </c>
       <c r="D16" s="8" t="str">
-        <f>=IF(LEFT(E16,2)="MG","Macroprocesso",IF(LEFT(E16,2)="MF","Macroprocesso",IF(LEFT(E16,2)="MS","Macroprocesso",IF(LEFT(E16,2)="PP","Processo",IF(OR(LEFT(E16,3)="SP-",ISNUMBER(SEARCH("/SP-",E16))),"Subprocesso",IF(LEFT(E16,2)="AT","Atividade",IF(LEFT(E16,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E16)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E16)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E16)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E16)),"Processo",IF(OR(LEFT(E16,2)="MG",LEFT(E16,2)="MF",LEFT(E16,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         </is>
       </c>
       <c r="D17" s="8" t="str">
-        <f>=IF(LEFT(E17,2)="MG","Macroprocesso",IF(LEFT(E17,2)="MF","Macroprocesso",IF(LEFT(E17,2)="MS","Macroprocesso",IF(LEFT(E17,2)="PP","Processo",IF(OR(LEFT(E17,3)="SP-",ISNUMBER(SEARCH("/SP-",E17))),"Subprocesso",IF(LEFT(E17,2)="AT","Atividade",IF(LEFT(E17,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E17)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E17)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E17)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E17)),"Processo",IF(OR(LEFT(E17,2)="MG",LEFT(E17,2)="MF",LEFT(E17,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -23310,7 +23310,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="str">
-        <f>=IF(LEFT(E18,2)="MG","Macroprocesso",IF(LEFT(E18,2)="MF","Macroprocesso",IF(LEFT(E18,2)="MS","Macroprocesso",IF(LEFT(E18,2)="PP","Processo",IF(OR(LEFT(E18,3)="SP-",ISNUMBER(SEARCH("/SP-",E18))),"Subprocesso",IF(LEFT(E18,2)="AT","Atividade",IF(LEFT(E18,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E18)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E18)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E18)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E18)),"Processo",IF(OR(LEFT(E18,2)="MG",LEFT(E18,2)="MF",LEFT(E18,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -23361,7 +23361,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="str">
-        <f>=IF(LEFT(E19,2)="MG","Macroprocesso",IF(LEFT(E19,2)="MF","Macroprocesso",IF(LEFT(E19,2)="MS","Macroprocesso",IF(LEFT(E19,2)="PP","Processo",IF(OR(LEFT(E19,3)="SP-",ISNUMBER(SEARCH("/SP-",E19))),"Subprocesso",IF(LEFT(E19,2)="AT","Atividade",IF(LEFT(E19,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E19)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E19)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E19)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E19)),"Processo",IF(OR(LEFT(E19,2)="MG",LEFT(E19,2)="MF",LEFT(E19,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -23412,7 +23412,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="str">
-        <f>=IF(LEFT(E20,2)="MG","Macroprocesso",IF(LEFT(E20,2)="MF","Macroprocesso",IF(LEFT(E20,2)="MS","Macroprocesso",IF(LEFT(E20,2)="PP","Processo",IF(OR(LEFT(E20,3)="SP-",ISNUMBER(SEARCH("/SP-",E20))),"Subprocesso",IF(LEFT(E20,2)="AT","Atividade",IF(LEFT(E20,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E20)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E20)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E20)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E20)),"Processo",IF(OR(LEFT(E20,2)="MG",LEFT(E20,2)="MF",LEFT(E20,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="str">
-        <f>=IF(LEFT(E21,2)="MG","Macroprocesso",IF(LEFT(E21,2)="MF","Macroprocesso",IF(LEFT(E21,2)="MS","Macroprocesso",IF(LEFT(E21,2)="PP","Processo",IF(OR(LEFT(E21,3)="SP-",ISNUMBER(SEARCH("/SP-",E21))),"Subprocesso",IF(LEFT(E21,2)="AT","Atividade",IF(LEFT(E21,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E21)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E21)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E21)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E21)),"Processo",IF(OR(LEFT(E21,2)="MG",LEFT(E21,2)="MF",LEFT(E21,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -23514,7 +23514,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="str">
-        <f>=IF(LEFT(E22,2)="MG","Macroprocesso",IF(LEFT(E22,2)="MF","Macroprocesso",IF(LEFT(E22,2)="MS","Macroprocesso",IF(LEFT(E22,2)="PP","Processo",IF(OR(LEFT(E22,3)="SP-",ISNUMBER(SEARCH("/SP-",E22))),"Subprocesso",IF(LEFT(E22,2)="AT","Atividade",IF(LEFT(E22,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E22)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E22)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E22)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E22)),"Processo",IF(OR(LEFT(E22,2)="MG",LEFT(E22,2)="MF",LEFT(E22,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -23560,7 +23560,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="str">
-        <f>=IF(LEFT(E23,2)="MG","Macroprocesso",IF(LEFT(E23,2)="MF","Macroprocesso",IF(LEFT(E23,2)="MS","Macroprocesso",IF(LEFT(E23,2)="PP","Processo",IF(OR(LEFT(E23,3)="SP-",ISNUMBER(SEARCH("/SP-",E23))),"Subprocesso",IF(LEFT(E23,2)="AT","Atividade",IF(LEFT(E23,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",E23)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",E23)),"Atividade",IF(ISNUMBER(SEARCH("SP-",E23)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",E23)),"Processo",IF(OR(LEFT(E23,2)="MG",LEFT(E23,2)="MF",LEFT(E23,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -23722,8 +23722,8 @@
         </is>
       </c>
       <c r="B2" s="8" t="str">
-        <f>=IF(LEFT(C2,2)="MG","Macroprocesso",IF(LEFT(C2,2)="MF","Macroprocesso",IF(LEFT(C2,2)="MS","Macroprocesso",IF(LEFT(C2,2)="PP","Processo",IF(OR(LEFT(C2,3)="SP-",ISNUMBER(SEARCH("/SP-",C2))),"Subprocesso",IF(LEFT(C2,2)="AT","Atividade",IF(LEFT(C2,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C2)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C2)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C2)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C2)),"Processo",IF(OR(LEFT(C2,2)="MG",LEFT(C2,2)="MF",LEFT(C2,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
@@ -23792,8 +23792,8 @@
         </is>
       </c>
       <c r="B3" s="8" t="str">
-        <f>=IF(LEFT(C3,2)="MG","Macroprocesso",IF(LEFT(C3,2)="MF","Macroprocesso",IF(LEFT(C3,2)="MS","Macroprocesso",IF(LEFT(C3,2)="PP","Processo",IF(OR(LEFT(C3,3)="SP-",ISNUMBER(SEARCH("/SP-",C3))),"Subprocesso",IF(LEFT(C3,2)="AT","Atividade",IF(LEFT(C3,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C3)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C3)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C3)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C3)),"Processo",IF(OR(LEFT(C3,2)="MG",LEFT(C3,2)="MF",LEFT(C3,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -23862,8 +23862,8 @@
         </is>
       </c>
       <c r="B4" s="8" t="str">
-        <f>=IF(LEFT(C4,2)="MG","Macroprocesso",IF(LEFT(C4,2)="MF","Macroprocesso",IF(LEFT(C4,2)="MS","Macroprocesso",IF(LEFT(C4,2)="PP","Processo",IF(OR(LEFT(C4,3)="SP-",ISNUMBER(SEARCH("/SP-",C4))),"Subprocesso",IF(LEFT(C4,2)="AT","Atividade",IF(LEFT(C4,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C4)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C4)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C4)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C4)),"Processo",IF(OR(LEFT(C4,2)="MG",LEFT(C4,2)="MF",LEFT(C4,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -23932,8 +23932,8 @@
         </is>
       </c>
       <c r="B5" s="8" t="str">
-        <f>=IF(LEFT(C5,2)="MG","Macroprocesso",IF(LEFT(C5,2)="MF","Macroprocesso",IF(LEFT(C5,2)="MS","Macroprocesso",IF(LEFT(C5,2)="PP","Processo",IF(OR(LEFT(C5,3)="SP-",ISNUMBER(SEARCH("/SP-",C5))),"Subprocesso",IF(LEFT(C5,2)="AT","Atividade",IF(LEFT(C5,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C5)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C5)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C5)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C5)),"Processo",IF(OR(LEFT(C5,2)="MG",LEFT(C5,2)="MF",LEFT(C5,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Subprocesso</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -24002,8 +24002,8 @@
         </is>
       </c>
       <c r="B6" s="8" t="str">
-        <f>=IF(LEFT(C6,2)="MG","Macroprocesso",IF(LEFT(C6,2)="MF","Macroprocesso",IF(LEFT(C6,2)="MS","Macroprocesso",IF(LEFT(C6,2)="PP","Processo",IF(OR(LEFT(C6,3)="SP-",ISNUMBER(SEARCH("/SP-",C6))),"Subprocesso",IF(LEFT(C6,2)="AT","Atividade",IF(LEFT(C6,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C6)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C6)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C6)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C6)),"Processo",IF(OR(LEFT(C6,2)="MG",LEFT(C6,2)="MF",LEFT(C6,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -24067,8 +24067,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="str">
-        <f>=IF(LEFT(C7,2)="MG","Macroprocesso",IF(LEFT(C7,2)="MF","Macroprocesso",IF(LEFT(C7,2)="MS","Macroprocesso",IF(LEFT(C7,2)="PP","Processo",IF(OR(LEFT(C7,3)="SP-",ISNUMBER(SEARCH("/SP-",C7))),"Subprocesso",IF(LEFT(C7,2)="AT","Atividade",IF(LEFT(C7,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C7)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C7)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C7)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C7)),"Processo",IF(OR(LEFT(C7,2)="MG",LEFT(C7,2)="MF",LEFT(C7,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="str">
-        <f>=IF(LEFT(C8,2)="MG","Macroprocesso",IF(LEFT(C8,2)="MF","Macroprocesso",IF(LEFT(C8,2)="MS","Macroprocesso",IF(LEFT(C8,2)="PP","Processo",IF(OR(LEFT(C8,3)="SP-",ISNUMBER(SEARCH("/SP-",C8))),"Subprocesso",IF(LEFT(C8,2)="AT","Atividade",IF(LEFT(C8,2)="TR","Tarefa","")))))))</f>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C8)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C8)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C8)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C8)),"Processo",IF(OR(LEFT(C8,2)="MG",LEFT(C8,2)="MF",LEFT(C8,2)="MS"),"Macroprocesso","")))))</f>
         <v>Macroprocesso</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -24202,8 +24202,8 @@
         </is>
       </c>
       <c r="B9" s="8" t="str">
-        <f>=IF(LEFT(C9,2)="MG","Macroprocesso",IF(LEFT(C9,2)="MF","Macroprocesso",IF(LEFT(C9,2)="MS","Macroprocesso",IF(LEFT(C9,2)="PP","Processo",IF(OR(LEFT(C9,3)="SP-",ISNUMBER(SEARCH("/SP-",C9))),"Subprocesso",IF(LEFT(C9,2)="AT","Atividade",IF(LEFT(C9,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C9)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C9)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C9)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C9)),"Processo",IF(OR(LEFT(C9,2)="MG",LEFT(C9,2)="MF",LEFT(C9,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Atividade</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -24272,8 +24272,8 @@
         </is>
       </c>
       <c r="B10" s="8" t="str">
-        <f>=IF(LEFT(C10,2)="MG","Macroprocesso",IF(LEFT(C10,2)="MF","Macroprocesso",IF(LEFT(C10,2)="MS","Macroprocesso",IF(LEFT(C10,2)="PP","Processo",IF(OR(LEFT(C10,3)="SP-",ISNUMBER(SEARCH("/SP-",C10))),"Subprocesso",IF(LEFT(C10,2)="AT","Atividade",IF(LEFT(C10,2)="TR","Tarefa","")))))))</f>
-        <v>Macroprocesso</v>
+        <f>=IF(ISNUMBER(SEARCH("TR-",C10)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C10)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C10)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C10)),"Processo",IF(OR(LEFT(C10,2)="MG",LEFT(C10,2)="MF",LEFT(C10,2)="MS"),"Macroprocesso","")))))</f>
+        <v>Processo</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -20734,12 +20734,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="J2:J300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="L2:L300">
       <formula1>Listas!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="B2:B300">
+      <formula1>Macroprocessos!$A$2:$A$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
+      <formula1>Processos!$C$2:$C$8</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -21756,9 +21762,18 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <dataValidations count="1">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>Listas!$I$2:$I$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="B2:B300">
+      <formula1>Macroprocessos!$A$2:$A$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
+      <formula1>Processos!$C$2:$C$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
+      <formula1>Subprocessos!$D$2:$D$7</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -22454,9 +22469,21 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
-  <dataValidations count="1">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>Listas!$J$2:$J$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="B2:B300">
+      <formula1>Macroprocessos!$A$2:$A$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="C2:C300">
+      <formula1>Processos!$C$2:$C$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="D2:D300">
+      <formula1>Subprocessos!$D$2:$D$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
+      <formula1>Atividades!$E$2:$E$16</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -201,7 +201,7 @@
   <sheetPr>
     <tabColor rgb="FF168821"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -216,6 +216,7 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -284,6 +285,11 @@
           <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -315,6 +321,11 @@
           <t xml:space="preserve">Média de dias entre o DFD e a homologação do certame.</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≤ 120 dias · Amarelo: 121–150 dias · Vermelho: &gt; 150 dias</t>
+        </is>
+      </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">dias</t>
@@ -336,6 +347,11 @@
       <c r="L2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σ(Data_Homologação − Data_DFD) / nº de processos concluídos no período</t>
         </is>
       </c>
     </row>
@@ -369,6 +385,11 @@
           <t xml:space="preserve">Média de dias úteis entre o DFD e a aprovação do ETP.</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≤ 30 dias · Amarelo: 31–45 dias · Vermelho: &gt; 45 dias</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">dias</t>
@@ -390,6 +411,11 @@
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σ(Data_Aprovação_ETP − Data_DFD) / nº de ETPs aprovados no período</t>
         </is>
       </c>
     </row>
@@ -423,6 +449,11 @@
           <t xml:space="preserve">Nº médio de impugnações recebidas por edital publicado.</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≤ 1 impugnação por edital · Amarelo: 1,1–2 · Vermelho: &gt; 2</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">nº</t>
@@ -444,6 +475,11 @@
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras.gov.br</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nº de impugnações recebidas / nº de editais publicados no período</t>
         </is>
       </c>
     </row>
@@ -477,6 +513,11 @@
           <t xml:space="preserve">% de contratos vigentes com fiscal formalmente designado.</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: = 100% · Amarelo: 90–99% · Vermelho: &lt; 90%</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">%</t>
@@ -498,6 +539,11 @@
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(nº de contratos vigentes com fiscal designado / nº total de contratos vigentes) × 100</t>
         </is>
       </c>
     </row>
@@ -531,6 +577,11 @@
           <t xml:space="preserve">Relação % entre volume faturado e volume captado no perímetro.</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≥ 75% · Amarelo: 65–74% · Vermelho: &lt; 65%</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">%</t>
@@ -552,6 +603,11 @@
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">SIG-Irrigação (fictício)</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(volume faturado / volume captado no perímetro) × 100</t>
         </is>
       </c>
     </row>
@@ -585,6 +641,11 @@
           <t xml:space="preserve">% de processos do macroprocesso com marco M9 concluído.</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≥ 95% · Amarelo: 80–94% · Vermelho: &lt; 80%</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">%</t>
@@ -606,6 +667,11 @@
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Painel de Processos</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(nº de processos com marco M9 = Sim / nº total de processos do macroprocesso) × 100</t>
         </is>
       </c>
     </row>
@@ -639,6 +705,11 @@
           <t xml:space="preserve">% de ações do plano com status atualizado no ciclo.</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≥ 95% · Amarelo: 80–94% · Vermelho: &lt; 80%</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">%</t>
@@ -660,6 +731,11 @@
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Painéis de BI</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(nº de ações do plano com status atualizado no ciclo / nº total de ações previstas) × 100</t>
         </is>
       </c>
     </row>
@@ -693,6 +769,11 @@
           <t xml:space="preserve">% de pesquisas de preços com três ou mais fontes admitidas.</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: = 100% · Amarelo: 90–99% · Vermelho: &lt; 90%</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">%</t>
@@ -714,6 +795,11 @@
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">e-Codevasf</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(nº de pesquisas com 3 ou mais fontes admitidas / nº total de pesquisas realizadas) × 100</t>
         </is>
       </c>
     </row>
@@ -747,6 +833,11 @@
           <t xml:space="preserve">Nº de nascentes com recuperação concluída no exercício.</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≥ 120 · Amarelo: 90–119 · Vermelho: &lt; 90</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">nº</t>
@@ -768,6 +859,11 @@
       <c r="L10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">GeoPortal (fictício)</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σ (nascentes com recuperação concluída no exercício)</t>
         </is>
       </c>
     </row>
@@ -793,12 +889,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nível de Serviço (SLA)</t>
+          <t xml:space="preserve">SLA</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Dias úteis entre o recebimento do DFD e o retorno inicial à área demandante.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≤ 5 dias úteis · Amarelo: 6–8 dias úteis · Vermelho: &gt; 8 dias úteis</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -827,6 +928,11 @@
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Acordado com as áreas demandantes em 2026.</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data_do_retorno_inicial − Data_de_recebimento_do_DFD, em dias úteis (média do período)</t>
         </is>
       </c>
     </row>
@@ -852,12 +958,17 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financeiro (ROI)</t>
+          <t xml:space="preserve">ROI</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(Economia de horas de trabalho convertida em custo − custo da ferramenta) / custo da ferramenta.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≥ 150% · Amarelo: 100–149% · Vermelho: &lt; 100%</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -888,15 +999,23 @@
           <t xml:space="preserve">Estimativa fictícia para demonstração.</t>
         </is>
       </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">((Economia_de_horas × custo/hora) − Custo_da_ferramenta) / Custo_da_ferramenta × 100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="I2:I300">
       <formula1>Listas!$R$2:$R$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="K2:K300">
       <formula1>Listas!$S$2:$S$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
+      <formula1>Listas!$Y$2:$Y$4</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -4151,7 +4270,7 @@
   <sheetPr>
     <tabColor rgb="FF0C326F"/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D231"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -6995,7 +7114,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sem exemplo)</t>
+          <t xml:space="preserve">Verde: ≤ 120 dias · Amarelo: 121–150 dias · Vermelho: &gt; 150 dias</t>
         </is>
       </c>
     </row>
@@ -7132,2048 +7251,2070 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σ(Data_Homologação − Data_DFD) / nº de processos concluídos no período</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MED-001</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Metrica_ID</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">IND-001</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Data_Medicao</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D140" s="6">
+      <c r="D141" s="6">
         <v>148</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Observacao</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Primeira apuração do trimestre.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">PAP-001</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-01/PP-01</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papel</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestor do processo</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Envolvimento</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Aprova (A)</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="4" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Pessoa</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="7" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">REG-001</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Alçada de aprovação por valor</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="7" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="4" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
         </is>
       </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Regra</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D152" s="6" t="inlineStr">
+      <c r="D153" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Operação</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Contratações acima de R$ 50.000 exigem aprovação da autoridade competente.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte_Normativa</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Lei nº 14.133/2021</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CULT-01</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B156" s="7" t="inlineStr">
+      <c r="B157" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D156" s="6">
+      <c r="D157" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Caracteristica</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Acordo geral sobre o que são os processos de negócio</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr">
+      <c r="B159" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Não avaliado</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Observacao</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="7" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="B161" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
+      <c r="D161" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">INI-001</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Data</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Titulo</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação da conferência de preços na pesquisa (PP-01)</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="4" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B164" s="7" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C164" s="6" t="inlineStr">
+      <c r="C165" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
+      <c r="D165" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">A equipe de TI usou o PRO e o roteiro de pesquisa de preços publicados no repositório (DOC-007) p...</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Processos_Relacionados</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Caminho completo dos processos relacionados, separados por ; quando houver mais de um.</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-01/PP-01</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B166" s="7" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C167" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D166" s="6">
+      <c r="D167" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Instancia</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Conselho de Administração</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B168" s="7" t="inlineStr">
+      <c r="B169" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Item_Normativo</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D168" s="6">
+      <c r="D169" s="6">
         <v>3.1</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Atribuicoes</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Garantir o apoio institucional para a gestão de processos.</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B170" s="7" t="inlineStr">
+      <c r="B171" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D170" s="6">
+      <c r="D171" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Descobrir</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="7" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B172" s="7" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D172" s="6" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Escuta e contextualização</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="4" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B174" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Duracao</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="C174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1–2 semanas</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="7" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B175" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
+      <c r="C175" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Compreender a dor real, o contexto e as expectativas de quem executa e de quem se beneficia do pr...</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Atividades_Chave</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Reunião de sensibilização com a unidade demandante; Entrevistas semiestruturadas com executores e...</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="7" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B177" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Quem_Faz</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP; Interlocutor da área; Dono do processo</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Entregaveis</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ata de reunião; Formulário preenchido; Mapa de partes interessadas</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sentimento_Usuario</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D178" s="6" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Curiosidade e ansiedade: “por que estão olhando meu trabalho?”</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">REP-001</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D180" s="6" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento oficial</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase_Ciclo</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Desenho</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="7" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B183" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Titulo</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Metodologia de Gerenciamento de Processos da Codevasf</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="4" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponí...</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B185" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte</t>
         </is>
       </c>
-      <c r="C184" s="6" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D184" s="6" t="inlineStr">
+      <c r="D185" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Codevasf</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Link</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D185" s="3" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://intraplone.codevasf.gov.br/documentos_normativos_referencia/governanca-e-gestao/copy_of_p...</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="7" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="B187" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D186" s="6">
+      <c r="D187" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr">
+      <c r="B188" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D187" s="3">
+      <c r="D188" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="7" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr">
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C188" s="6" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D189" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ricardo Nunes Vasconcelos</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr">
+      <c r="B190" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papel</t>
         </is>
       </c>
-      <c r="C189" s="3" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerente-Executivo da Área de Gestão Estratégica</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="7" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Sigla</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
+      <c r="C191" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">AE</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Nome</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="C192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Área de Gestão Estratégica</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="7" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B192" s="7" t="inlineStr">
+      <c r="B193" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Email</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D193" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ricardo.vasconcelos@codevasf.gov.br</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Telefone</t>
         </is>
       </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">(61) 2028-4400</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B195" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Foto</t>
         </is>
       </c>
-      <c r="C194" s="6" t="inlineStr">
+      <c r="C195" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D194" s="6" t="inlineStr">
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://randomuser.me/api/portraits/men/32.jpg</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B195" s="4" t="inlineStr">
+      <c r="B196" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Hierarquia</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D195" s="3">
+      <c r="D196" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="7" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B196" s="7" t="inlineStr">
+      <c r="B197" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Termo</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
+      <c r="C197" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D197" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Definicao</t>
         </is>
       </c>
-      <c r="C197" s="3" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Association of Business Process Management Professionals — entidade internacional sem fins lucrat...</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="7" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B199" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte</t>
         </is>
       </c>
-      <c r="C198" s="6" t="inlineStr">
+      <c r="C199" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D199" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="B200" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C199" s="3" t="inlineStr">
+      <c r="C200" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D199" s="3">
+      <c r="D200" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B200" s="7" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria</t>
         </is>
       </c>
-      <c r="C200" s="6" t="inlineStr">
+      <c r="C201" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D200" s="6" t="inlineStr">
+      <c r="D201" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Conceitos básicos</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="B202" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pergunta</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">O que é Gestão de Processos (BPM)?</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="7" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B202" s="7" t="inlineStr">
+      <c r="B203" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Resposta</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D202" s="6" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Process Management é uma disciplina gerencial integrada que combina técnicas, métodos e ...</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Siglas</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigla</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10ª/AJ</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="7" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Siglas</t>
         </is>
       </c>
-      <c r="B204" s="7" t="inlineStr">
+      <c r="B205" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C204" s="6" t="inlineStr">
+      <c r="C205" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D204" s="6" t="inlineStr">
+      <c r="D205" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Assessoria Jurídica Regional</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Parametros</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B206" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Chave</t>
         </is>
       </c>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Contato_Unidade</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="7" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Parametros</t>
         </is>
       </c>
-      <c r="B206" s="7" t="inlineStr">
+      <c r="B207" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor</t>
         </is>
       </c>
-      <c r="C206" s="6" t="inlineStr">
+      <c r="C207" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D207" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade de Gestão Normativa e de Processos (AE/GPE/UNP)</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B208" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Macroprocesso</t>
         </is>
       </c>
-      <c r="C207" s="3" t="inlineStr">
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerencial</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="7" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B208" s="7" t="inlineStr">
+      <c r="B209" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Mapeamento</t>
         </is>
       </c>
-      <c r="C208" s="6" t="inlineStr">
+      <c r="C209" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D208" s="6" t="inlineStr">
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Não iniciado</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
+      <c r="B210" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Prioridade</t>
         </is>
       </c>
-      <c r="C209" s="3" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D209" s="3" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="7" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B210" s="7" t="inlineStr">
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Complexidade</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="D211" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="B212" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Maturidade_Processo</t>
         </is>
       </c>
-      <c r="C211" s="3" t="inlineStr">
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicial</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="7" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="B213" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim_Nao</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D212" s="6" t="inlineStr">
+      <c r="D213" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B214" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Marco</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="C214" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="7" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B214" s="7" t="inlineStr">
+      <c r="B215" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nivel_Vinculo</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D215" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
+      <c r="B216" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Atividade</t>
         </is>
       </c>
-      <c r="C215" s="3" t="inlineStr">
+      <c r="C216" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Agregação de Valor</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="7" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B216" s="7" t="inlineStr">
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Tarefa</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="D217" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Documento</t>
         </is>
       </c>
-      <c r="C217" s="3" t="inlineStr">
+      <c r="C218" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="7" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B218" s="7" t="inlineStr">
+      <c r="B219" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao_Documento</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C219" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="D219" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Vigente</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Risco</t>
         </is>
       </c>
-      <c r="C219" s="3" t="inlineStr">
+      <c r="C220" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D219" s="3" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Operacional</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="7" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B220" s="7" t="inlineStr">
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Resposta_Risco</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D221" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mitigar</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Risco</t>
         </is>
       </c>
-      <c r="C221" s="3" t="inlineStr">
+      <c r="C222" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D221" s="3" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Aberto</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="7" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B222" s="7" t="inlineStr">
+      <c r="B223" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Envolvimento_RACI</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
+      <c r="C223" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D222" s="6" t="inlineStr">
+      <c r="D223" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Executa (R)</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Regra</t>
         </is>
       </c>
-      <c r="C223" s="3" t="inlineStr">
+      <c r="C224" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Operação</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="7" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B224" s="7" t="inlineStr">
+      <c r="B225" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Polaridade</t>
         </is>
       </c>
-      <c r="C224" s="6" t="inlineStr">
+      <c r="C225" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D224" s="6" t="inlineStr">
+      <c r="D225" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Maior melhor</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
+      <c r="B226" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Periodicidade</t>
         </is>
       </c>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="C226" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mensal</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="7" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B226" s="7" t="inlineStr">
+      <c r="B227" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao_Cultura</t>
         </is>
       </c>
-      <c r="C226" s="6" t="inlineStr">
+      <c r="C227" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D226" s="6" t="inlineStr">
+      <c r="D227" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
+      <c r="B228" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Iniciativa</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="C228" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D227" s="3" t="inlineStr">
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="7" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B228" s="7" t="inlineStr">
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Repositorio</t>
         </is>
       </c>
-      <c r="C228" s="6" t="inlineStr">
+      <c r="C229" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D228" s="6" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento oficial</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
+      <c r="B230" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase_Instrumento</t>
         </is>
       </c>
-      <c r="C229" s="3" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D229" s="3" t="inlineStr">
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Planejamento</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="7" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B230" s="7" t="inlineStr">
+      <c r="B231" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_FAQ</t>
         </is>
       </c>
-      <c r="C230" s="6" t="inlineStr">
+      <c r="C231" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D230" s="6" t="inlineStr">
+      <c r="D231" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Conceitos básicos</t>
         </is>
@@ -16934,7 +17075,7 @@
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:Y12"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -16960,6 +17101,7 @@
     <col min="22" max="22" width="21" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17083,6 +17225,11 @@
           <t xml:space="preserve">Categoria_FAQ</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_Metrica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -17205,6 +17352,11 @@
           <t xml:space="preserve">Conceitos básicos</t>
         </is>
       </c>
+      <c r="Y2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -17327,6 +17479,11 @@
           <t xml:space="preserve">Modelagem e SIPOC</t>
         </is>
       </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -17442,6 +17599,11 @@
       <c r="X4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Cadeia de Valor e governança</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROI</t>
         </is>
       </c>
     </row>

--- a/data/painel-processos-dados.xlsx
+++ b/data/painel-processos-dados.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Metricas" sheetId="10" r:id="rId10"/>
     <sheet name="Medicoes" sheetId="11" r:id="rId11"/>
     <sheet name="Papeis" sheetId="12" r:id="rId12"/>
+    <sheet name="Equipe_Processo" sheetId="25" r:id="rId26"/>
     <sheet name="Regras" sheetId="13" r:id="rId13"/>
     <sheet name="Cultura_Processos" sheetId="14" r:id="rId14"/>
     <sheet name="Iniciativas" sheetId="15" r:id="rId15"/>
@@ -26,7 +27,6 @@
     <sheet name="Siglas" sheetId="22" r:id="rId22"/>
     <sheet name="Parametros" sheetId="23" r:id="rId23"/>
     <sheet name="Listas" sheetId="24" r:id="rId24"/>
-    <sheet name="Equipe_Gerenciamento_Processos" sheetId="25" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -137,7 +137,7 @@
   <sheetPr>
     <tabColor rgb="FF0C326F"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
@@ -188,6 +188,18 @@
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Quando um Subprocesso é filho de OUTRO Subprocesso (em vez de um Processo), seu Código usa numeração decimal: {código do subprocesso pai}.{posição do filho} — ex.: o subprocesso SP-03 com 3 filhos aninhados vira SP-03.01, SP-03.02, SP-03.03. Isso diferencia visualmente um subprocesso aninhado de um subprocesso de 1º nível, mesmo sem abrir a Trilha. Se um desses filhos tiver, por sua vez, filhos, a mesma lógica se repete: SP-03.01.01, SP-03.01.02...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe de gerenciamento — uma por processo</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada processo tem a sua própria equipe de gerenciamento (RES 031/2025, item 3.7): ponto focal do Nugep, gestor(a) do processo e atores do processo. Cadastre os integrantes na aba Equipe_Processo, com a coluna Processo apontando para a Trilha do processo — não existe mais uma lista central de gestores.</t>
         </is>
       </c>
     </row>
@@ -870,7 +882,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MET-010</t>
+          <t xml:space="preserve">IND-010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -939,7 +951,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MET-011</t>
+          <t xml:space="preserve">IND-011</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1275,7 +1287,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MET-010</t>
+          <t xml:space="preserve">IND-010</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1295,7 +1307,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MET-010</t>
+          <t xml:space="preserve">IND-010</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1320,7 +1332,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MET-011</t>
+          <t xml:space="preserve">IND-011</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1347,7 +1359,7 @@
   <sheetPr>
     <tabColor rgb="FF168821"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1583,26 +1595,26 @@
       </c>
       <c r="B8" s="8" t="str">
         <f>=IF(ISNUMBER(SEARCH("TR-",C8)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C8)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C8)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C8)),"Processo",IF(OR(LEFT(C8,2)="MG",LEFT(C8,2)="MF",LEFT(C8,2)="MS"),"Macroprocesso","")))))</f>
-        <v>Atividade</v>
+        <v>Processo</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
+          <t xml:space="preserve">MS-01 › PP-02</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analista de planejamento da contratação</t>
+          <t xml:space="preserve">Gestor do processo</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Executa (R)</t>
+          <t xml:space="preserve">Aprova (A)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AR/GDT</t>
+          <t xml:space="preserve">Gerente de Licitações</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1630,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-02</t>
+          <t xml:space="preserve">MS-01 › PP-03</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1649,7 +1661,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-03</t>
+          <t xml:space="preserve">MF-02 › PP-01</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1664,7 +1676,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerente de Licitações</t>
+          <t xml:space="preserve">Gerente de Operação</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1692,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MF-02 › PP-01</t>
+          <t xml:space="preserve">MF-03 › PP-01</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1695,7 +1707,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerente de Operação</t>
+          <t xml:space="preserve">Gerente de Revitalização</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1723,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MF-03 › PP-01</t>
+          <t xml:space="preserve">MG-01 › PP-01</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1726,7 +1738,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerente de Revitalização</t>
+          <t xml:space="preserve">Gerente de Planejamento</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1754,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MG-01 › PP-01</t>
+          <t xml:space="preserve">MS-02 › PP-01</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1756,37 +1768,6 @@
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gerente de Planejamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAP-013</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="str">
-        <f>=IF(ISNUMBER(SEARCH("TR-",C14)),"Tarefa",IF(ISNUMBER(SEARCH("AT-",C14)),"Atividade",IF(ISNUMBER(SEARCH("SP-",C14)),"Subprocesso",IF(ISNUMBER(SEARCH("PP-",C14)),"Processo",IF(OR(LEFT(C14,2)="MG",LEFT(C14,2)="MF",LEFT(C14,2)="MS"),"Macroprocesso","")))))</f>
-        <v>Processo</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MS-02 › PP-01</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gestor do processo</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aprova (A)</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerente de Pessoas</t>
         </is>
@@ -4270,7 +4251,7 @@
   <sheetPr>
     <tabColor rgb="FF0C326F"/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D246"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -4382,8 +4363,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D5" s="3">
-        <v>1</v>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4416,17 +4399,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Siglas das unidades orgânicas que dividem a execução, separadas por ; . Sem lista suspensa, porque a célula aceita mais de um valor — as siglas válidas estão na aba Siglas.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formulação, desdobramento e monitoramento da estratégia corporativa, da governança e do desempenh...</t>
+          <t xml:space="preserve">AE/GAG; AT/GTI</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4421,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4448,7 +4431,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garantir que a atuação da Companhia esteja alinhada à estratégia, com decisões baseadas em evidên...</t>
+          <t xml:space="preserve">Formulação, desdobramento e monitoramento da estratégia corporativa, da governança e do desempenh...</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4443,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entregas</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -4470,7 +4453,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plano Estratégico; Plano de Ação Anual; Relatórios de desempenho</t>
+          <t xml:space="preserve">Garantir que a atuação da Companhia esteja alinhada à estratégia, com decisões baseadas em evidên...</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4465,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beneficiarios</t>
+          <t xml:space="preserve">Entregas</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4492,7 +4475,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diretoria Executiva; Conselho de Administração; Unidades internas</t>
+          <t xml:space="preserve">Plano Estratégico; Plano de Ação Anual; Relatórios de desempenho</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4487,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partes_Interessadas</t>
+          <t xml:space="preserve">Beneficiarios</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -4514,7 +4497,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ministério supervisor; Órgãos de controle; Sociedade</t>
+          <t xml:space="preserve">Diretoria Executiva; Conselho de Administração; Unidades internas</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4509,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Partes_Interessadas</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4536,7 +4519,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
+          <t xml:space="preserve">Ministério supervisor; Órgãos de controle; Sociedade</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4531,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4558,7 +4541,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sem exemplo)</t>
+          <t xml:space="preserve">e-Codevasf; Painéis de BI</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4553,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4580,7 +4563,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4575,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trilha</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -4602,14 +4585,14 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MG-01</t>
+          <t xml:space="preserve">Macroprocesso priorizado no ciclo 2026 de mapeamento.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processos</t>
+          <t xml:space="preserve">Macroprocessos</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -4624,7 +4607,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-01</t>
+          <t xml:space="preserve">MG-01</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4619,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -4646,7 +4629,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
     </row>
@@ -4658,17 +4641,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -4680,17 +4663,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planejamento da Contratação</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4685,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -4712,7 +4695,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Da identificação da necessidade (DFD) até a aprovação do ETP, TR e pesquisa de preços que instrue...</t>
+          <t xml:space="preserve">Planejamento da Contratação</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4707,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4734,7 +4717,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instruir as contratações com estudos e artefatos completos, reduzindo retrabalho e impugnações.</t>
+          <t xml:space="preserve">Da identificação da necessidade (DFD) até a aprovação do ETP, TR e pesquisa de preços que instrue...</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4729,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -4756,7 +4739,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC</t>
+          <t xml:space="preserve">Instruir as contratações com estudos e artefatos completos, reduzindo retrabalho e impugnações.</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4751,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ponto_Focal_Nugep</t>
+          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4778,7 +4761,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -4790,17 +4773,17 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prioridade</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Siglas das unidades orgânicas que dividem a execução, separadas por ; . Sem lista suspensa, porque a célula aceita mais de um valor — as siglas válidas estão na aba Siglas.</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alta</t>
+          <t xml:space="preserve">AT/GTI</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4795,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complexidade</t>
+          <t xml:space="preserve">Ponto_Focal_Nugep</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4822,7 +4805,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alta</t>
+          <t xml:space="preserve">Carlos Eduardo Lima (UNP)</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4817,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maturidade</t>
+          <t xml:space="preserve">Prioridade</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -4844,7 +4827,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definido</t>
+          <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4839,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status_Mapeamento</t>
+          <t xml:space="preserve">Complexidade</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4866,7 +4849,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concluído</t>
+          <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4861,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Percentual</t>
+          <t xml:space="preserve">Maturidade</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -4886,8 +4869,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D28" s="6">
-        <v>1</v>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definido</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4898,7 +4883,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inicio_Mapeamento</t>
+          <t xml:space="preserve">Status_Mapeamento</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4908,7 +4893,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
+          <t xml:space="preserve">Concluído</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4905,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prazo_Previsto</t>
+          <t xml:space="preserve">Percentual</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -4930,7 +4915,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">29/05/2026</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4927,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data_Conclusao</t>
+          <t xml:space="preserve">Inicio_Mapeamento</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4952,7 +4937,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/05/2026</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4949,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultima_Atualizacao</t>
+          <t xml:space="preserve">Prazo_Previsto</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -4974,7 +4959,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/07/2026</t>
+          <t xml:space="preserve">29/05/2026</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4971,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M1_Conhecer_Processo</t>
+          <t xml:space="preserve">Data_Conclusao</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4996,7 +4981,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim</t>
+          <t xml:space="preserve">18/05/2026</t>
         </is>
       </c>
     </row>
@@ -5008,7 +4993,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M2_Processo_Modelado</t>
+          <t xml:space="preserve">Ultima_Atualizacao</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -5018,7 +5003,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim</t>
+          <t xml:space="preserve">10/07/2026</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5015,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3_Subprocessos_Modelados</t>
+          <t xml:space="preserve">M1_Conhecer_Processo</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5052,7 +5037,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4_ASIS_Modelado</t>
+          <t xml:space="preserve">M2_Processo_Modelado</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -5074,7 +5059,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M5_ASIS_Validado</t>
+          <t xml:space="preserve">M3_Subprocessos_Modelados</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -5096,7 +5081,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6_Procedimento_Aprovado</t>
+          <t xml:space="preserve">M4_ASIS_Modelado</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5118,7 +5103,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M7_Processo_Publicado</t>
+          <t xml:space="preserve">M5_ASIS_Validado</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -5140,7 +5125,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M8_TOBE_Elaborado</t>
+          <t xml:space="preserve">M6_Procedimento_Aprovado</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5162,7 +5147,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">M9_TOBE_Aprovado</t>
+          <t xml:space="preserve">M7_Processo_Publicado</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5184,7 +5169,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M10_Processo_Transformado</t>
+          <t xml:space="preserve">M8_TOBE_Elaborado</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5206,7 +5191,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fornecedores</t>
+          <t xml:space="preserve">M9_TOBE_Aprovado</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5216,7 +5201,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Áreas demandantes; Painel de Preços; Fornecedores (cotações)</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5213,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">M10_Processo_Transformado</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5238,7 +5223,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD; Plano de Contratações Anual; Requisitos da área</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5235,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Fornecedores</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5260,7 +5245,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado; TR aprovado; Pesquisa de preços validada</t>
+          <t xml:space="preserve">Áreas demandantes; Painel de Preços; Fornecedores (cotações)</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5257,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beneficiarios</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5282,7 +5267,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC (Seleção do Fornecedor); Assessoria Jurídica</t>
+          <t xml:space="preserve">DFD; Plano de Contratações Anual; Requisitos da área</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5279,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5304,7 +5289,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
+          <t xml:space="preserve">ETP aprovado; TR aprovado; Pesquisa de preços validada</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5301,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo_ECodevasf</t>
+          <t xml:space="preserve">Beneficiarios</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5326,7 +5311,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">59500.000123/2026-11</t>
+          <t xml:space="preserve">AA/GLC (Seleção do Fornecedor); Assessoria Jurídica</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5323,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo_ECodevasf_Link</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5348,7 +5333,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=5950000012...</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br; Painel de Preços</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5345,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Processo_ECodevasf</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5370,7 +5355,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://fluxosti.codevasf.gov.br/incidentes/</t>
+          <t xml:space="preserve">59500.000123/2026-11</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5367,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competencias_Necessarias</t>
+          <t xml:space="preserve">Processo_ECodevasf_Link</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5392,7 +5377,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração de estudos técnicos e termos de referência; Conhecimento da Lei nº 14.133/2021; Pesqui...</t>
+          <t xml:space="preserve">https://e-processo.codevasf.gov.br/sei/controlador.php?acao=procedimento_visualizar&amp;id=5950000012...</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5389,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontes_Dados</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5414,7 +5399,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Painel de Preços; PNCP</t>
+          <t xml:space="preserve">https://fluxosti.codevasf.gov.br/incidentes/</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5411,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proxima_Acao</t>
+          <t xml:space="preserve">Competencias_Necessarias</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -5436,7 +5421,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
+          <t xml:space="preserve">Elaboração de estudos técnicos e termos de referência; Conhecimento da Lei nº 14.133/2021; Pesqui...</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5433,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendencia</t>
+          <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -5458,19 +5443,19 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
+          <t xml:space="preserve">e-Codevasf; Painel de Preços; PNCP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trilha</t>
+          <t xml:space="preserve">Proxima_Acao</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5480,19 +5465,19 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-01 › SP-01</t>
+          <t xml:space="preserve">Monitorar indicadores do processo e revisar o PRO em 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Pendencia</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5502,95 +5487,95 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">Pendente retorno da área sobre fluxo de recursos administrativos.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">Gestor_Nome</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Pessoa que responde pelo processo no dia a dia — titular da unidade orgânica responsável ou, na ausência dele, o demandante. Distinta do ponto focal do Nugep, que acompanha o mapeamento.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Gestor_Email</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
+          <t xml:space="preserve">E-mail do gestor(a) do processo.</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Gestor_Telefone</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Telefone do gestor(a) do processo.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estudo Técnico Preliminar (ETP)</t>
+          <t xml:space="preserve">(61) 2028-4521</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocessos</t>
+          <t xml:space="preserve">Processos</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Pai</t>
+          <t xml:space="preserve">Gestor_Unidade_Organica</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Sigla da unidade orgânica do gestor(a) do processo (lista suspensa da aba Siglas).</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5587,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -5610,8 +5595,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D61" s="3">
-        <v>1</v>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -5622,7 +5609,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -5632,7 +5619,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caracterização da necessidade, análise de soluções de mercado e demonstração da viabilidade da co...</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5631,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objetivo</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5654,7 +5641,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fundamentar tecnicamente a melhor solução para a necessidade.</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -5666,17 +5653,17 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AA/GLC</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5675,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reutilizavel</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -5698,7 +5685,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim</t>
+          <t xml:space="preserve">Estudo Técnico Preliminar (ETP)</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5697,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reutilizado_Em</t>
+          <t xml:space="preserve">Vinculo_Pai</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -5720,7 +5707,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-02; MF-02/PP-01</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5719,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -5742,7 +5729,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5741,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -5764,7 +5751,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
+          <t xml:space="preserve">Caracterização da necessidade, análise de soluções de mercado e demonstração da viabilidade da co...</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5763,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -5786,7 +5773,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
+          <t xml:space="preserve">Fundamentar tecnicamente a melhor solução para a necessidade.</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5785,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontes_Dados</t>
+          <t xml:space="preserve">Unidade_Organica_Responsavel</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -5808,7 +5795,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf</t>
+          <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
@@ -5820,29 +5807,29 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imagem_Bizagi</t>
+          <t xml:space="preserve">Unidades_Organicas_Corresponsaveis</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Siglas das unidades orgânicas que dividem a execução, separadas por ; . Sem lista suspensa, porque a célula aceita mais de um valor — as siglas válidas estão na aba Siglas.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sem exemplo)</t>
+          <t xml:space="preserve">AR/GDT</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trilha</t>
+          <t xml:space="preserve">Reutilizavel</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -5852,19 +5839,19 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Reutilizado_Em</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5874,19 +5861,19 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">MS-01/PP-02; MF-02/PP-01</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -5896,19 +5883,19 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">DFD; Levantamento de soluções de mercado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocesso</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5918,41 +5905,41 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">ETP aprovado no e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AT-01</t>
+          <t xml:space="preserve">e-Codevasf; Compras.gov.br</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Fontes_Dados</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -5962,19 +5949,19 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formalizar a necessidade (DFD)</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividades</t>
+          <t xml:space="preserve">Subprocessos</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Pai</t>
+          <t xml:space="preserve">Imagem_Bizagi</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -5984,7 +5971,7 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5983,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6004,8 +5991,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D79" s="3">
-        <v>1</v>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -6016,7 +6005,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Atividade</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -6026,7 +6015,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agregação de Valor</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6027,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -6048,7 +6037,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A área demandante registra a necessidade de contratação no Documento de Formalização da Demanda (...</t>
+          <t xml:space="preserve">PP-01</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6049,7 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entradas</t>
+          <t xml:space="preserve">Subprocesso</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -6070,7 +6059,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Necessidade identificada; Plano de Contratações Anual</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6071,17 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saidas</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DFD assinado no e-Codevasf</t>
+          <t xml:space="preserve">AT-01</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6093,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistemas</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -6114,19 +6103,19 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-Codevasf</t>
+          <t xml:space="preserve">Formalizar a necessidade (DFD)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trilha</t>
+          <t xml:space="preserve">Vinculo_Pai</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6136,19 +6125,19 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01 › TR-01</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -6158,19 +6147,19 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">Tipo_Atividade</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6180,19 +6169,19 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PP-01</t>
+          <t xml:space="preserve">Agregação de Valor</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subprocesso</t>
+          <t xml:space="preserve">Descricao</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -6202,19 +6191,19 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">A área demandante registra a necessidade de contratação no Documento de Formalização da Demanda (...</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atividade</t>
+          <t xml:space="preserve">Entradas</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6224,41 +6213,41 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AT-01</t>
+          <t xml:space="preserve">Necessidade identificada; Plano de Contratações Anual</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codigo</t>
+          <t xml:space="preserve">Saidas</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR-01</t>
+          <t xml:space="preserve">DFD assinado no e-Codevasf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas</t>
+          <t xml:space="preserve">Atividades</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Sistemas</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6268,7 +6257,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reunir informações da demanda</t>
+          <t xml:space="preserve">e-Codevasf</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6269,7 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordem</t>
+          <t xml:space="preserve">Trilha</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -6288,8 +6277,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D92" s="6">
-        <v>1</v>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01 › SP-01 › AT-01 › TR-01</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -6300,7 +6291,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Tarefa</t>
+          <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6310,7 +6301,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6313,7 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duracao_Estimada</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -6330,8 +6321,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D94" s="6">
-        <v>4</v>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PP-01</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -6342,7 +6335,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Subprocesso</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6352,19 +6345,19 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelo DOC-006/DOC-012.</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Atividade</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -6374,41 +6367,41 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOC-001</t>
+          <t xml:space="preserve">AT-01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titulo</t>
+          <t xml:space="preserve">Codigo</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Identificador sequencial dentro do nível, reiniciado a cada vínculo com o pai. Quando um Subprocesso está dentro de outro Subprocesso, o código do filho usa numeração decimal (ex. "SP-03.01", "SP-03.02"...) — o número do pai + "." + a posição do filho — para diferenciá-lo visualmente de um subprocesso de 1º nível.</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRO 06.01 — Planejamento da Contratação</t>
+          <t xml:space="preserve">TR-01</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo_Documento</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -6418,19 +6411,19 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimento (PRO)</t>
+          <t xml:space="preserve">Reunir informações da demanda</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Ordem</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -6440,41 +6433,41 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Tipo_Tarefa</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">Manual</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Versao</t>
+          <t xml:space="preserve">Duracao_Estimada</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -6482,19 +6475,21 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D101" s="3">
-        <v>2</v>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documentos</t>
+          <t xml:space="preserve">Tarefas</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -6504,7 +6499,7 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/05/2026</t>
+          <t xml:space="preserve">Modelo DOC-006/DOC-012.</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6511,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situacao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6526,7 +6521,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigente</t>
+          <t xml:space="preserve">DOC-001</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6533,7 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ato_Aprovacao</t>
+          <t xml:space="preserve">Titulo</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6548,7 +6543,7 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolução nº 812, de 18/05/2026 (Diretoria Executiva)</t>
+          <t xml:space="preserve">PRO 06.01 — Planejamento da Contratação</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6555,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link</t>
+          <t xml:space="preserve">Tipo_Documento</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -6570,7 +6565,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://exemplo.codevasf.gov.br/repositorio/pop-06-01.pdf</t>
+          <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6577,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6592,41 +6587,41 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publicado após validação do TO-BE.</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01 › PP-01" ou "MS-01 › PP-01 › SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIS-001</t>
+          <t xml:space="preserve">MS-01 › PP-01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Versao</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6636,41 +6631,41 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Data</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
+          <t xml:space="preserve">18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao_Risco</t>
+          <t xml:space="preserve">Situacao</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6680,19 +6675,19 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimativas de preço defasadas gerando sobrepreço ou licitação deserta.</t>
+          <t xml:space="preserve">Vigente</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">Ato_Aprovacao</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6702,19 +6697,19 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operacional</t>
+          <t xml:space="preserve">Resolução nº 812, de 18/05/2026 (Diretoria Executiva)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatores</t>
+          <t xml:space="preserve">Link</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6724,19 +6719,19 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sem exemplo)</t>
+          <t xml:space="preserve">https://exemplo.codevasf.gov.br/repositorio/pop-06-01.pdf</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riscos</t>
+          <t xml:space="preserve">Documentos</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cronograma_Risco</t>
+          <t xml:space="preserve">Observacoes</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6746,7 +6741,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sem exemplo)</t>
+          <t xml:space="preserve">Publicado após validação do TO-BE.</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6753,7 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data_Identificacao</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -6768,7 +6763,7 @@
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">05/01/2026</t>
+          <t xml:space="preserve">RIS-001</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6775,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Probabilidade_1a5</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -6788,8 +6783,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D115" s="3">
-        <v>4</v>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6800,16 +6797,18 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impacto_1a5</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
-        </is>
-      </c>
-      <c r="D116" s="6">
-        <v>4</v>
+          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01 › PP-01" ou "MS-01 › PP-01 › SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6820,7 +6819,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nivel_PxI</t>
+          <t xml:space="preserve">Descricao_Risco</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -6828,8 +6827,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D117" s="3">
-        <v>16</v>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estimativas de preço defasadas gerando sobrepreço ou licitação deserta.</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6840,7 +6841,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Classificacao</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -6850,7 +6851,7 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alto</t>
+          <t xml:space="preserve">Operacional</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6863,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resposta</t>
+          <t xml:space="preserve">Fatores</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -6872,7 +6873,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mitigar</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6885,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controles_Tratamento</t>
+          <t xml:space="preserve">Cronograma_Risco</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6894,7 +6895,7 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roteiro de pesquisa com múltiplas fontes (Painel de Preços, PNCP) e revisão pela UNP.</t>
+          <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6907,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prazo_Tratamento</t>
+          <t xml:space="preserve">Data_Identificacao</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6916,7 +6917,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30/09/2026</t>
+          <t xml:space="preserve">05/01/2026</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6929,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responsavel</t>
+          <t xml:space="preserve">Probabilidade_1a5</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -6938,7 +6939,7 @@
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ricardo Nogueira</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6951,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status</t>
+          <t xml:space="preserve">Impacto_1a5</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -6960,19 +6961,19 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Em tratamento</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Nivel_PxI</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -6982,19 +6983,19 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">IND-001</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nome</t>
+          <t xml:space="preserve">Classificacao</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -7004,19 +7005,19 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tempo médio do ciclo de contratação</t>
+          <t xml:space="preserve">Alto</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Nivel</t>
+          <t xml:space="preserve">Resposta</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -7026,41 +7027,41 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macroprocesso</t>
+          <t xml:space="preserve">Mitigar</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinculo_Codigo</t>
+          <t xml:space="preserve">Controles_Tratamento</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MS-01</t>
+          <t xml:space="preserve">Roteiro de pesquisa com múltiplas fontes (Painel de Preços, PNCP) e revisão pela UNP.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Categoria</t>
+          <t xml:space="preserve">Prazo_Tratamento</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7070,19 +7071,19 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processo</t>
+          <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descricao_Formula</t>
+          <t xml:space="preserve">Responsavel</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -7092,19 +7093,19 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Média de dias entre o DFD e a homologação do certame.</t>
+          <t xml:space="preserve">Ricardo Nogueira</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metricas</t>
+          <t xml:space="preserve">Riscos</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criterios_Desempenho</t>
+          <t xml:space="preserve">Status</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7114,7 +7115,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verde: ≤ 120 dias · Amarelo: 121–150 dias · Vermelho: &gt; 150 dias</t>
+          <t xml:space="preserve">Em tratamento</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7127,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unidade</t>
+          <t xml:space="preserve">ID</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -7136,7 +7137,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dias</t>
+          <t xml:space="preserve">IND-001</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7149,7 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Polaridade</t>
+          <t xml:space="preserve">Nome</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7158,7 +7159,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menor melhor</t>
+          <t xml:space="preserve">Tempo médio do ciclo de contratação</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7171,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meta</t>
+          <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -7178,8 +7179,10 @@
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D133" s="3">
-        <v>120</v>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macroprocesso</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -7190,17 +7193,17 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Periodicidade</t>
+          <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01 › PP-01" ou "MS-01 › PP-01 › SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trimestral</t>
+          <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7215,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fonte</t>
+          <t xml:space="preserve">Categoria</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -7222,7 +7225,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras.gov.br</t>
+          <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7237,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observacoes</t>
+          <t xml:space="preserve">Descricao_Formula</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7244,7 +7247,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acordado com as áreas demandantes em 2026.</t>
+          <t xml:space="preserve">Média de dias entre o DFD e a homologação do certame.</t>
         </is>
       </c>
     </row>
@@ -7256,2067 +7259,2415 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Criterios_Desempenho</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verde: ≤ 120 dias · Amarelo: 121–150 dias · Vermelho: &gt; 150 dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidade</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polaridade</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menor melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meta</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodicidade</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trimestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fonte</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras.gov.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observacoes</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acordado com as áreas demandantes em 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metricas</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Formula</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Σ(Data_Homologação − Data_DFD) / nº de processos concluídos no período</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">MED-001</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Metrica_ID</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">IND-001</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Data_Medicao</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">30/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B148" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D141" s="6">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medicoes</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Observacao</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Primeira apuração do trimestre.</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B150" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
+      <c r="D150" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">PAP-001</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Processo</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B152" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01 › PP-01" ou "MS-01 › PP-01 › SP-03"), ou o código isolado de um Macroprocesso (já único). Papéis valem para Macroprocesso, Processo e Subprocesso — Atividade e Tarefa não têm papéis próprios. Mais de um: separe com ; .</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papel</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Gestor do processo</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Envolvimento</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Aprova (A)</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Papeis</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Pessoa</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AE/GAG</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="7" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identificador do integrante da equipe de gerenciamento do processo.</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trilha do processo a que a equipe pertence (lista suspensa com os processos cadastrados). Cada processo tem a sua própria equipe — não existe lista central de gestores.</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordem</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ordem de exibição do integrante dentro da equipe do processo.</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nome do integrante: ponto focal do Nugep, gestor(a) do processo e atores do processo (RES 031/2025, item 3.7).</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-mail de contato do integrante.</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telefone</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telefone de contato do integrante.</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipe_Processo</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Area</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área (unidade orgânica) em que o integrante está lotado — sigla da aba Siglas.</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">REG-001</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="4" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C164" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D164" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Alçada de aprovação por valor</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Nivel</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B166" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Vinculo_Codigo</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01/PP-01" ou "MS-01/PP-01/SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caminho completo do item vinculado (ex. "MS-01 › PP-01" ou "MS-01 › PP-01 › SP-03"), ou o código isolado de um Macroprocesso (já único). Mais de um: separe com ; .</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-01</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Regra</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Operação</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B168" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C168" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D168" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Contratações acima de R$ 50.000 exigem aprovação da autoridade competente.</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Regras</t>
         </is>
       </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte_Normativa</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lei nº 14.133/2021</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B170" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C170" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D170" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">CULT-01</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="7" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B157" s="7" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D157" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Caracteristica</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C172" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D172" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Acordo geral sobre o que são os processos de negócio</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Não avaliado</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cultura_Processos</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Observacao</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(sem exemplo)</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B161" s="7" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">INI-001</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B176" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Data</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">20/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="7" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Titulo</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
+      <c r="C177" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação da conferência de preços na pesquisa (PP-01)</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A equipe de TI usou o PRO e o roteiro de pesquisa de preços publicados no repositório (DOC-007) p...</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Iniciativas</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Processos_Relacionados</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Caminho completo dos processos relacionados, separados por ; quando houver mais de um.</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MS-01/PP-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr">
+      <c r="C181" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D167" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Instancia</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D182" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Conselho de Administração</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Item_Normativo</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D169" s="6">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Competencias</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B184" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Atribuicoes</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D184" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Garantir o apoio institucional para a gestão de processos.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="7" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C171" s="6" t="inlineStr">
+      <c r="C185" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D171" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B186" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase</t>
         </is>
       </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D186" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Descobrir</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="7" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Escuta e contextualização</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Duracao</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1–2 semanas</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="7" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Compreender a dor real, o contexto e as expectativas de quem executa e de quem se beneficia do pr...</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Atividades_Chave</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C190" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D190" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Reunião de sensibilização com a unidade demandante; Entrevistas semiestruturadas com executores e...</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Quem_Faz</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP; Interlocutor da área; Dono do processo</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Entregaveis</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C192" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="D192" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ata de reunião; Formulário preenchido; Mapa de partes interessadas</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="7" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Jornada</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sentimento_Usuario</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C193" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Curiosidade e ansiedade: “por que estão olhando meu trabalho?”</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ID</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">REP-001</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="7" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento oficial</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B196" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase_Ciclo</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr">
+      <c r="C196" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D196" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Desenho</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="7" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Titulo</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D183" s="6" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Metodologia de Gerenciamento de Processos da Codevasf</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B198" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Descricao</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento normativo que institui a metodologia corporativa de gerenciamento de processos (disponí...</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="7" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Codevasf</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="4" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B200" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Link</t>
         </is>
       </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D186" s="3" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://intraplone.codevasf.gov.br/documentos_normativos_referencia/governanca-e-gestao/copy_of_p...</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Repositorio</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B201" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D187" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B188" s="4" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C188" s="3" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D188" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="7" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ricardo Nunes Vasconcelos</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="4" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B190" s="4" t="inlineStr">
+      <c r="B204" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Papel</t>
         </is>
       </c>
-      <c r="C190" s="3" t="inlineStr">
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D190" s="3" t="inlineStr">
+      <c r="D204" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerente-Executivo da Área de Gestão Estratégica</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="7" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="B205" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Sigla</t>
         </is>
       </c>
-      <c r="C191" s="6" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">AE</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
+      <c r="B206" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade_Nome</t>
         </is>
       </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D192" s="3" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Área de Gestão Estratégica</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="7" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B193" s="7" t="inlineStr">
+      <c r="B207" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Email</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D193" s="6" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ricardo.vasconcelos@codevasf.gov.br</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B194" s="4" t="inlineStr">
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Telefone</t>
         </is>
       </c>
-      <c r="C194" s="3" t="inlineStr">
+      <c r="C208" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D194" s="3" t="inlineStr">
+      <c r="D208" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(61) 2028-4400</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="7" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B209" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Foto</t>
         </is>
       </c>
-      <c r="C195" s="6" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://randomuser.me/api/portraits/men/32.jpg</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">NUGEP</t>
         </is>
       </c>
-      <c r="B196" s="4" t="inlineStr">
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Hierarquia</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D196" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="7" t="inlineStr">
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B211" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Termo</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Definicao</t>
         </is>
       </c>
-      <c r="C198" s="3" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D198" s="3" t="inlineStr">
+      <c r="D212" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Association of Business Process Management Professionals — entidade internacional sem fins lucrat...</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="7" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Glossario</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B213" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fonte</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ABPMP</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B200" s="4" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D200" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="7" t="inlineStr">
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B215" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D201" s="6" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Conceitos básicos</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Pergunta</t>
         </is>
       </c>
-      <c r="C202" s="3" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D202" s="3" t="inlineStr">
+      <c r="D216" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">O que é Gestão de Processos (BPM)?</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="7" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FAQ</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="B217" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Resposta</t>
         </is>
       </c>
-      <c r="C203" s="6" t="inlineStr">
+      <c r="C217" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Process Management é uma disciplina gerencial integrada que combina técnicas, métodos e ...</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Siglas</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigla</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="C218" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="D218" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10ª/AJ</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="7" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Siglas</t>
         </is>
       </c>
-      <c r="B205" s="7" t="inlineStr">
+      <c r="B219" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C205" s="6" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D205" s="6" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Assessoria Jurídica Regional</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Parametros</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
+      <c r="B220" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Chave</t>
         </is>
       </c>
-      <c r="C206" s="3" t="inlineStr">
+      <c r="C220" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D206" s="3" t="inlineStr">
+      <c r="D220" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Contato_Unidade</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="7" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Parametros</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Valor</t>
         </is>
       </c>
-      <c r="C207" s="6" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D207" s="6" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Unidade de Gestão Normativa e de Processos (AE/GPE/UNP)</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B222" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Macroprocesso</t>
         </is>
       </c>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="C222" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D208" s="3" t="inlineStr">
+      <c r="D222" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerencial</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="7" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Mapeamento</t>
         </is>
       </c>
-      <c r="C209" s="6" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D209" s="6" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Não iniciado</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="B224" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Prioridade</t>
         </is>
       </c>
-      <c r="C210" s="3" t="inlineStr">
+      <c r="C224" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D210" s="3" t="inlineStr">
+      <c r="D224" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="7" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Complexidade</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
+      <c r="C225" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D211" s="6" t="inlineStr">
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Alta</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B212" s="4" t="inlineStr">
+      <c r="B226" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Maturidade_Processo</t>
         </is>
       </c>
-      <c r="C212" s="3" t="inlineStr">
+      <c r="C226" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D212" s="3" t="inlineStr">
+      <c r="D226" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Inicial</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="7" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B227" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim_Nao</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
+      <c r="C227" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D213" s="6" t="inlineStr">
+      <c r="D227" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="B228" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Marco</t>
         </is>
       </c>
-      <c r="C214" s="3" t="inlineStr">
+      <c r="C228" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D214" s="3" t="inlineStr">
+      <c r="D228" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="7" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="B229" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nivel_Vinculo</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
+      <c r="C229" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="D229" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Macroprocesso</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B230" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Atividade</t>
         </is>
       </c>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="C230" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D230" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Agregação de Valor</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="7" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B217" s="7" t="inlineStr">
+      <c r="B231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Tarefa</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C231" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="D231" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Manual</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B218" s="4" t="inlineStr">
+      <c r="B232" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Documento</t>
         </is>
       </c>
-      <c r="C218" s="3" t="inlineStr">
+      <c r="C232" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D218" s="3" t="inlineStr">
+      <c r="D232" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Procedimento (PRO)</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="7" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B219" s="7" t="inlineStr">
+      <c r="B233" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao_Documento</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D219" s="6" t="inlineStr">
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Vigente</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Risco</t>
         </is>
       </c>
-      <c r="C220" s="3" t="inlineStr">
+      <c r="C234" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D220" s="3" t="inlineStr">
+      <c r="D234" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Operacional</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="7" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B221" s="7" t="inlineStr">
+      <c r="B235" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Resposta_Risco</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C235" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D221" s="6" t="inlineStr">
+      <c r="D235" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mitigar</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B236" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Status_Risco</t>
         </is>
       </c>
-      <c r="C222" s="3" t="inlineStr">
+      <c r="C236" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D222" s="3" t="inlineStr">
+      <c r="D236" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Aberto</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="7" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B223" s="7" t="inlineStr">
+      <c r="B237" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Envolvimento_RACI</t>
         </is>
       </c>
-      <c r="C223" s="6" t="inlineStr">
+      <c r="C237" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D223" s="6" t="inlineStr">
+      <c r="D237" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Executa (R)</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
+      <c r="B238" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Regra</t>
         </is>
       </c>
-      <c r="C224" s="3" t="inlineStr">
+      <c r="C238" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D224" s="3" t="inlineStr">
+      <c r="D238" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Operação</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="7" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="B239" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Polaridade</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
+      <c r="C239" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D225" s="6" t="inlineStr">
+      <c r="D239" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Maior melhor</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
+      <c r="B240" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Periodicidade</t>
         </is>
       </c>
-      <c r="C226" s="3" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D226" s="3" t="inlineStr">
+      <c r="D240" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mensal</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="7" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B227" s="7" t="inlineStr">
+      <c r="B241" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Situacao_Cultura</t>
         </is>
       </c>
-      <c r="C227" s="6" t="inlineStr">
+      <c r="C241" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D227" s="6" t="inlineStr">
+      <c r="D241" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Sim</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B228" s="4" t="inlineStr">
+      <c r="B242" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo_Iniciativa</t>
         </is>
       </c>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="C242" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D228" s="3" t="inlineStr">
+      <c r="D242" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Automação</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="7" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B229" s="7" t="inlineStr">
+      <c r="B243" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_Repositorio</t>
         </is>
       </c>
-      <c r="C229" s="6" t="inlineStr">
+      <c r="C243" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D229" s="6" t="inlineStr">
+      <c r="D243" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Documento oficial</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B244" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Fase_Instrumento</t>
         </is>
       </c>
-      <c r="C230" s="3" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D230" s="3" t="inlineStr">
+      <c r="D244" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Planejamento</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="7" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Listas</t>
         </is>
       </c>
-      <c r="B231" s="7" t="inlineStr">
+      <c r="B245" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria_FAQ</t>
         </is>
       </c>
-      <c r="C231" s="6" t="inlineStr">
+      <c r="C245" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
         </is>
       </c>
-      <c r="D231" s="6" t="inlineStr">
+      <c r="D245" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Conceitos básicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listas</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoria_Metrica</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campo de preenchimento livre ou calculado — ver aba anterior.</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLA</t>
         </is>
       </c>
     </row>
@@ -17791,173 +18142,413 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF155BCB"/>
+    <tabColor rgb="FF168821"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G11"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ordem</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Telefone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unidade_Organica</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Area</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Vanessa Torres Almeida</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">(61) 2028-4521</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">AA/GLC</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+      <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlos Eduardo Lima</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carlos.lima@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4408</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+      <c r="C4" s="7">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fernanda Ribeiro Alves</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fernanda.alves@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4635</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AR/GDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-01</t>
+        </is>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thiago Menezes Barbosa</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thiago.barbosa@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4712</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT/GTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-02</t>
+        </is>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanessa Torres Almeida</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanessa.almeida@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4521</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AA/GLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlos Eduardo Lima</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carlos.lima@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4408</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-01 › PP-02</t>
+        </is>
+      </c>
+      <c r="C8" s="7">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juliana Campos Teixeira</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juliana.teixeira@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4550</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MF-02 › PP-01</t>
+        </is>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Marcelo Andrade Costa</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">marcelo.costa@codevasf.gov.br</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">(61) 2028-4710</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MF-02 › PP-01</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eduardo Martins</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eduardo.martins@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(61) 2028-4412</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AE/GPE/UNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQP-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MF-02 › PP-01</t>
+        </is>
+      </c>
+      <c r="C11" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luciana Ferreira Dias</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">luciana.dias@codevasf.gov.br</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(61) 2028-4820</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR/GRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patrícia Moreira Lopes</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patricia.lopes@codevasf.gov.br</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(61) 2028-4430</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AE/GPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rodrigo Nascimento Farias</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rodrigo.farias@codevasf.gov.br</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(61) 2028-4900</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AG/GGP</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sérgio Aguiar Nogueira</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sergio.nogueira@codevasf.gov.br</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(87) 3866-4120</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI/GOM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="E2:E300">
+  <autoFilter ref="A1:G1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="B2:B300">
+      <formula1>Processos!$A$2:$A$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" showInputMessage="1" errorTitle="Valor fora da lista" error="Escolha uma das opções da lista. A lista completa está na aba Listas." promptTitle="Lista de opções" prompt="Clique na seta ao lado da célula e escolha uma das opções." sqref="G2:G300">
       <formula1>Siglas!$A$2:$A$421</formula1>
     </dataValidation>
   </dataValidations>
